--- a/aussendienst/electronica_2026_Aussendienst.xlsx
+++ b/aussendienst/electronica_2026_Aussendienst.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zielfirmen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baden-Württemberg" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bayern" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baden-Württemberg (Stefan)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bayern (Dietmar)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rest DE - NL" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eher nicht (kein Bereich)" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nicht ansprechen" sheetId="6" state="visible" r:id="rId6"/>
@@ -18,10 +18,10 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Zielfirmen'!$A$4:$K$205</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Zielfirmen'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Baden-Württemberg'!$A$4:$K$58</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Baden-Württemberg'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Bayern'!$A$4:$K$51</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Bayern'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Baden-Württemberg (Stefan)'!$A$4:$K$58</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Baden-Württemberg (Stefan)'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Bayern (Dietmar)'!$A$4:$K$51</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Bayern (Dietmar)'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rest DE - NL'!$A$4:$K$104</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Rest DE - NL'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Eher nicht (kein Bereich)'!$A$4:$I$295</definedName>
@@ -10550,7 +10550,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zielfirmen electronica 2026 – Baden-Württemberg</t>
+          <t>Zielfirmen electronica 2026 – Baden-Württemberg (Stefan)</t>
         </is>
       </c>
     </row>
@@ -10636,7 +10636,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -11420,7 +11420,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -11567,7 +11567,7 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
@@ -11910,7 +11910,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
@@ -12400,7 +12400,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -12645,7 +12645,7 @@
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
@@ -12694,7 +12694,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -12743,7 +12743,7 @@
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
@@ -12890,7 +12890,7 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -13135,7 +13135,7 @@
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -13233,7 +13233,7 @@
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
@@ -13296,7 +13296,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zielfirmen electronica 2026 – Bayern</t>
+          <t>Zielfirmen electronica 2026 – Bayern (Dietmar)</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -13529,7 +13529,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -13578,7 +13578,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -13627,7 +13627,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -13774,7 +13774,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -13872,7 +13872,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -13921,7 +13921,7 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -14019,7 +14019,7 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -14117,7 +14117,7 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -14166,7 +14166,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -14215,7 +14215,7 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -14264,7 +14264,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -14362,7 +14362,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -14411,7 +14411,7 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -14460,7 +14460,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -14607,7 +14607,7 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
@@ -14656,7 +14656,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
@@ -14852,7 +14852,7 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
@@ -14950,7 +14950,7 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -15097,7 +15097,7 @@
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
@@ -15146,7 +15146,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -15195,7 +15195,7 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
@@ -15244,7 +15244,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -15391,7 +15391,7 @@
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
@@ -15538,7 +15538,7 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
@@ -15636,7 +15636,7 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -34538,7 +34538,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -34585,7 +34585,7 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -34960,7 +34960,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -35007,7 +35007,7 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -35140,7 +35140,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -35187,7 +35187,7 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -35320,7 +35320,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -35562,7 +35562,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -35656,7 +35656,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -35703,7 +35703,7 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
@@ -35750,7 +35750,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -35797,7 +35797,7 @@
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
@@ -35938,7 +35938,7 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -35985,7 +35985,7 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
@@ -36032,7 +36032,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -36157,7 +36157,7 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
@@ -36290,7 +36290,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -36337,7 +36337,7 @@
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
@@ -36384,7 +36384,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -36509,7 +36509,7 @@
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
@@ -36728,7 +36728,7 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -36775,7 +36775,7 @@
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
@@ -37002,7 +37002,7 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -37049,7 +37049,7 @@
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
@@ -37096,7 +37096,7 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -37143,7 +37143,7 @@
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
@@ -37190,7 +37190,7 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -37237,7 +37237,7 @@
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
@@ -37284,7 +37284,7 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -37331,7 +37331,7 @@
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
@@ -37378,7 +37378,7 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -37503,7 +37503,7 @@
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
@@ -38011,7 +38011,7 @@
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
@@ -38292,7 +38292,7 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -38378,7 +38378,7 @@
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -38511,7 +38511,7 @@
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
@@ -38558,7 +38558,7 @@
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -38890,7 +38890,7 @@
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -39078,7 +39078,7 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -39211,7 +39211,7 @@
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
@@ -39258,7 +39258,7 @@
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -39305,7 +39305,7 @@
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
@@ -39352,7 +39352,7 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -39704,7 +39704,7 @@
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -39790,7 +39790,7 @@
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -40083,7 +40083,7 @@
       <c r="C132" s="10" t="inlineStr"/>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
@@ -40130,7 +40130,7 @@
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -40255,7 +40255,7 @@
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
@@ -40341,7 +40341,7 @@
       </c>
       <c r="D138" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
@@ -40685,7 +40685,7 @@
       </c>
       <c r="D146" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E146" s="11" t="inlineStr">
@@ -40849,7 +40849,7 @@
       </c>
       <c r="D150" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E150" s="11" t="inlineStr">
@@ -40935,7 +40935,7 @@
       </c>
       <c r="D152" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
@@ -41146,7 +41146,7 @@
       </c>
       <c r="D157" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -41318,7 +41318,7 @@
       </c>
       <c r="D161" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -41412,7 +41412,7 @@
       </c>
       <c r="D163" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -41553,7 +41553,7 @@
       </c>
       <c r="D166" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E166" s="11" t="inlineStr">
@@ -41811,7 +41811,7 @@
       </c>
       <c r="D172" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E172" s="11" t="inlineStr">
@@ -41999,7 +41999,7 @@
       </c>
       <c r="D176" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E176" s="11" t="inlineStr">
@@ -42124,7 +42124,7 @@
       </c>
       <c r="D179" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
@@ -42210,7 +42210,7 @@
       </c>
       <c r="D181" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -42335,7 +42335,7 @@
       </c>
       <c r="D184" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E184" s="11" t="inlineStr">
@@ -42382,7 +42382,7 @@
       </c>
       <c r="D185" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
@@ -42507,7 +42507,7 @@
       </c>
       <c r="D188" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E188" s="11" t="inlineStr">
@@ -42593,7 +42593,7 @@
       </c>
       <c r="D190" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E190" s="11" t="inlineStr">
@@ -42687,7 +42687,7 @@
       </c>
       <c r="D192" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E192" s="11" t="inlineStr">
@@ -42734,7 +42734,7 @@
       </c>
       <c r="D193" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
@@ -42867,7 +42867,7 @@
       </c>
       <c r="D196" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E196" s="11" t="inlineStr">
@@ -43008,7 +43008,7 @@
       </c>
       <c r="D199" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
@@ -43133,7 +43133,7 @@
       </c>
       <c r="D202" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E202" s="11" t="inlineStr">
@@ -43219,7 +43219,7 @@
       </c>
       <c r="D204" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E204" s="11" t="inlineStr">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="D206" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E206" s="11" t="inlineStr">
@@ -43438,7 +43438,7 @@
       </c>
       <c r="D209" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
@@ -43524,7 +43524,7 @@
       </c>
       <c r="D211" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
@@ -43571,7 +43571,7 @@
       </c>
       <c r="D212" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E212" s="11" t="inlineStr">
@@ -43888,7 +43888,7 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>Pro Vertriebsgebiet ein Blatt (Baden-Württemberg, Bayern, Rest DE / NL, ggf. Österreich/außerhalb; nur Prio A/B/C). Gebiet nach Fertigungs- bzw. Firmensitz laut Tom/Tina. Das Blatt "Zielfirmen" enthält alle zusammen.</t>
+          <t>Pro Vertriebsgebiet ein Blatt (Baden-Württemberg, Bayern, Rest DE / NL, ggf. Österreich/außerhalb; nur Prio A/B/C). Gebiet nach Fertigungs- bzw. Firmensitz laut Tom/Tina. Zuständig: Stefan = Baden-Württemberg, Dietmar = Bayern. Das Blatt "Zielfirmen" enthält alle zusammen.</t>
         </is>
       </c>
     </row>

--- a/aussendienst/electronica_2026_Aussendienst.xlsx
+++ b/aussendienst/electronica_2026_Aussendienst.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zielfirmen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baden-Württemberg (Stefan)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bayern (Dietmar)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rest DE - NL" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rest DE - NL (Manuel)" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eher nicht (kein Bereich)" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nicht ansprechen" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hinweise" sheetId="7" state="visible" r:id="rId7"/>
@@ -22,8 +22,8 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Baden-Württemberg (Stefan)'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Bayern (Dietmar)'!$A$4:$K$51</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Bayern (Dietmar)'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rest DE - NL'!$A$4:$K$104</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Rest DE - NL'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rest DE - NL (Manuel)'!$A$4:$K$104</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Rest DE - NL (Manuel)'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Eher nicht (kein Bereich)'!$A$4:$I$295</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Eher nicht (kein Bereich)'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Nicht ansprechen'!$A$4:$I$215</definedName>
@@ -15699,7 +15699,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zielfirmen electronica 2026 – Rest DE / NL</t>
+          <t>Zielfirmen electronica 2026 – Rest DE / NL (Manuel)</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -15883,7 +15883,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -15981,7 +15981,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -16030,7 +16030,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -16079,7 +16079,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -16128,7 +16128,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -16177,7 +16177,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -16275,7 +16275,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -16471,7 +16471,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -16618,7 +16618,7 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -16667,7 +16667,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -16716,7 +16716,7 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -16765,7 +16765,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -16863,7 +16863,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -16912,7 +16912,7 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
@@ -16961,7 +16961,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
@@ -17059,7 +17059,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -17108,7 +17108,7 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
@@ -17157,7 +17157,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
@@ -17255,7 +17255,7 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
@@ -17353,7 +17353,7 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
@@ -17451,7 +17451,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -17500,7 +17500,7 @@
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
@@ -17549,7 +17549,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -17598,7 +17598,7 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
@@ -17647,7 +17647,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -17696,7 +17696,7 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
@@ -17745,7 +17745,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
@@ -17941,7 +17941,7 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -17990,7 +17990,7 @@
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
@@ -18039,7 +18039,7 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -18088,7 +18088,7 @@
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -18186,7 +18186,7 @@
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
@@ -18333,7 +18333,7 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -18382,7 +18382,7 @@
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
@@ -18431,7 +18431,7 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -18480,7 +18480,7 @@
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
@@ -18529,7 +18529,7 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -18578,7 +18578,7 @@
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
@@ -18627,7 +18627,7 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -18676,7 +18676,7 @@
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
@@ -18823,7 +18823,7 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -18872,7 +18872,7 @@
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
@@ -18921,7 +18921,7 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
@@ -19019,7 +19019,7 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
@@ -19117,7 +19117,7 @@
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
@@ -19215,7 +19215,7 @@
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
@@ -19313,7 +19313,7 @@
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -19362,7 +19362,7 @@
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
@@ -19411,7 +19411,7 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -19460,7 +19460,7 @@
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
@@ -19509,7 +19509,7 @@
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -19558,7 +19558,7 @@
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
@@ -19607,7 +19607,7 @@
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -19656,7 +19656,7 @@
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
@@ -19705,7 +19705,7 @@
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -19852,7 +19852,7 @@
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -19950,7 +19950,7 @@
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
@@ -19999,7 +19999,7 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -20048,7 +20048,7 @@
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -20146,7 +20146,7 @@
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
@@ -20195,7 +20195,7 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
@@ -20293,7 +20293,7 @@
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -20342,7 +20342,7 @@
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
@@ -20391,7 +20391,7 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -20440,7 +20440,7 @@
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
@@ -20489,7 +20489,7 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -20538,7 +20538,7 @@
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
@@ -20587,7 +20587,7 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -20636,7 +20636,7 @@
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
@@ -34632,7 +34632,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -34679,7 +34679,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -35093,7 +35093,7 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -35273,7 +35273,7 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -35609,7 +35609,7 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
@@ -35844,7 +35844,7 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -36243,7 +36243,7 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
@@ -36595,7 +36595,7 @@
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
@@ -36681,7 +36681,7 @@
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
@@ -36822,7 +36822,7 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -36908,7 +36908,7 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -36955,7 +36955,7 @@
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
@@ -37589,7 +37589,7 @@
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
@@ -37714,7 +37714,7 @@
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -37878,7 +37878,7 @@
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -37964,7 +37964,7 @@
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -38425,7 +38425,7 @@
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
@@ -38757,7 +38757,7 @@
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
@@ -38804,7 +38804,7 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -38937,7 +38937,7 @@
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
@@ -38984,7 +38984,7 @@
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -39031,7 +39031,7 @@
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
@@ -39164,7 +39164,7 @@
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -39399,7 +39399,7 @@
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
@@ -39446,7 +39446,7 @@
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -39610,7 +39610,7 @@
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -39657,7 +39657,7 @@
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
@@ -39837,7 +39837,7 @@
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
@@ -39923,7 +39923,7 @@
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr">
@@ -40427,7 +40427,7 @@
       </c>
       <c r="D140" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E140" s="11" t="inlineStr">
@@ -40474,7 +40474,7 @@
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -41099,7 +41099,7 @@
       </c>
       <c r="D156" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E156" s="11" t="inlineStr">
@@ -41271,7 +41271,7 @@
       </c>
       <c r="D160" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E160" s="11" t="inlineStr">
@@ -41365,7 +41365,7 @@
       </c>
       <c r="D162" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E162" s="11" t="inlineStr">
@@ -41459,7 +41459,7 @@
       </c>
       <c r="D164" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E164" s="11" t="inlineStr">
@@ -41506,7 +41506,7 @@
       </c>
       <c r="D165" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -41600,7 +41600,7 @@
       </c>
       <c r="D167" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -41725,7 +41725,7 @@
       </c>
       <c r="D170" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E170" s="11" t="inlineStr">
@@ -41858,7 +41858,7 @@
       </c>
       <c r="D173" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
@@ -41905,7 +41905,7 @@
       </c>
       <c r="D174" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E174" s="11" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="D175" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
@@ -42640,7 +42640,7 @@
       </c>
       <c r="D191" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
@@ -42820,7 +42820,7 @@
       </c>
       <c r="D195" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
@@ -42914,7 +42914,7 @@
       </c>
       <c r="D197" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
@@ -42961,7 +42961,7 @@
       </c>
       <c r="D198" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E198" s="11" t="inlineStr">
@@ -43391,7 +43391,7 @@
       </c>
       <c r="D208" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E208" s="11" t="inlineStr">
@@ -43657,7 +43657,7 @@
       </c>
       <c r="D214" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E214" s="11" t="inlineStr">
@@ -43888,7 +43888,7 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>Pro Vertriebsgebiet ein Blatt (Baden-Württemberg, Bayern, Rest DE / NL, ggf. Österreich/außerhalb; nur Prio A/B/C). Gebiet nach Fertigungs- bzw. Firmensitz laut Tom/Tina. Zuständig: Stefan = Baden-Württemberg, Dietmar = Bayern. Das Blatt "Zielfirmen" enthält alle zusammen.</t>
+          <t>Pro Vertriebsgebiet ein Blatt (Baden-Württemberg, Bayern, Rest DE / NL, ggf. Österreich/außerhalb; nur Prio A/B/C). Gebiet nach Fertigungs- bzw. Firmensitz laut Tom/Tina. Zuständig: Stefan = Baden-Württemberg, Dietmar = Bayern, Manuel = Rest DE / NL. Das Blatt "Zielfirmen" enthält alle zusammen.</t>
         </is>
       </c>
     </row>

--- a/aussendienst/electronica_2026_Aussendienst.xlsx
+++ b/aussendienst/electronica_2026_Aussendienst.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Impressum/Standortseite 2e-mechatronic.de lesen (V für Sitz = Fertigungsort); Datenblatt Neigungssensor (Schutzart, Vergussmasse im Gehäuse?); Stellenanzeige Montage/Produktion Kirchheim; Patente Anmelder "2E mechatronic" in …</t>
+          <t>Impressum/Standortseite 2e-mechatronic.de lesen; Datenblatt Neigungssensor (Schutzart, Vergussmasse im Gehäuse?); Stellenanzeige Montage/Produktion Kirchheim; Patente Anmelder "2E mechatronic" in …</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Spektrumanalysatoren (SPECTRAN), Mess- und Richtantennen (IsoLOG 3D, HyperLOG), Drohnendetektion/-abwehr AARTOS, HF-Schirmmaterialien .</t>
+          <t>Spektrumanalysatoren (SPECTRAN), Mess- und Richtantennen (IsoLOG 3D, HyperLOG), Drohnendetektion/-abwehr AARTOS, HF-Schirmmaterialien.</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Drucksensoren und analoge Signalaufbereitungs-ICs ("Frame ASICs") .</t>
+          <t>Drucksensoren und analoge Signalaufbereitungs-ICs ("Frame ASICs").</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Maschinen (Ätz-, Laminier-, Bohr-/Fräsmaschinen, Durchkontaktierung), fotobeschichtetes Basismaterial und Verbrauchsmaterial für Leiterplatten-Kleinserien .</t>
+          <t>Maschinen (Ätz-, Laminier-, Bohr-/Fräsmaschinen, Durchkontaktierung), fotobeschichtetes Basismaterial und Verbrauchsmaterial für Leiterplatten-Kleinserien.</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>Impressum/Standort colandis.com, Stellenanzeigen Montage Kahla (V für Fertigungsort); (b) Datenblatt FFM-C/-E: Dichtung (PU/Klebung), Lüfter-/Regelelektronik vergossen? Schutzart; (c) Patent-/Schutzrechtsnummern …</t>
+          <t>Impressum/Standort colandis.com, Stellenanzeigen Montage Kahla; (b) Datenblatt FFM-C/-E: Dichtung (PU/Klebung), Lüfter-/Regelelektronik vergossen? Schutzart; (c) Patent-/Schutzrechtsnummern …</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Komponenten und Systeme der Mensch-Maschine-Interaktion: Kartenleser (Kontakt/kontaktlos), Schalter, Encoder, Ticketing-Systeme .</t>
+          <t>Komponenten und Systeme der Mensch-Maschine-Interaktion: Kartenleser (Kontakt/kontaktlos), Schalter, Encoder, Ticketing-Systeme.</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Industriedisplays von 7-Segment- bis Farb-Touch-Displays, Displays mit und ohne Touch, Optical Bonding, Touch-Lösungen und Assembly Services .</t>
+          <t>Industriedisplays von 7-Segment- bis Farb-Touch-Displays, Displays mit und ohne Touch, Optical Bonding, Touch-Lösungen und Assembly Services.</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>LED-Chips, SMD- und Through-Hole-LEDs sowie Photodioden von 200 nm (UV-C) bis 2300 nm (SWIR), Monolithic Displays, Serien in kleinen und mittleren Mengen .</t>
+          <t>LED-Chips, SMD- und Through-Hole-LEDs sowie Photodioden von 200 nm (UV-C) bis 2300 nm (SWIR), Monolithic Displays, Serien in kleinen und mittleren Mengen.</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Batch-Nassprozessanlagen für Ätzen und Reinigen (Wet Benches), Chemie-Versorgungs- und Entsorgungssysteme, Carrier .</t>
+          <t>Batch-Nassprozessanlagen für Ätzen und Reinigen (Wet Benches), Chemie-Versorgungs- und Entsorgungssysteme, Carrier.</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Impressum und Produktseiten der Firmenwebsite (Domain unbekannt) lesen: Fertigung Neumarkt (V), Steuerung/Sensorik Eigenbau oder Zukauf; Stellenanzeigen Neumarkt (Montage, Elektro).</t>
+          <t>Impressum und Produktseiten der Firmenwebsite (Domain unbekannt) lesen: Fertigung Neumarkt, Steuerung/Sensorik Eigenbau oder Zukauf; Stellenanzeigen Neumarkt (Montage, Elektro).</t>
         </is>
       </c>
       <c r="I18" s="11" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>"intelligente Elektronik für mobile Energieversorgung, Messtechnik, Trafoschaltrelais" sowie EMS (E2MS) .</t>
+          <t>"intelligente Elektronik für mobile Energieversorgung, Messtechnik, Trafoschaltrelais" sowie EMS (E2MS).</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>Schalter, Drucktaster, Not-Halt-Schalter, Kontaktgeber, Bedieneinheiten, Gehäuse, Klemmen, Endschalter, RFID-Systeme, Bus-Lösungen .</t>
+          <t>Schalter, Drucktaster, Not-Halt-Schalter, Kontaktgeber, Bedieneinheiten, Gehäuse, Klemmen, Endschalter, RFID-Systeme, Bus-Lösungen.</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>Tragbare und stationäre Gasmessgeräte, Gassensoren, Mehrgasmessgeräte mit Mikroprozessor, Systemlösungen .</t>
+          <t>Tragbare und stationäre Gasmessgeräte, Gassensoren, Mehrgasmessgeräte mit Mikroprozessor, Systemlösungen.</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>Messgeräte für Schichtdicke, Materialanalyse (Röntgenfluoreszenz), Materialprüfung und Mikrohärte, von Handgeräten bis zu Inline-Systemen .</t>
+          <t>Messgeräte für Schichtdicke, Materialanalyse (Röntgenfluoreszenz), Materialprüfung und Mikrohärte, von Handgeräten bis zu Inline-Systemen.</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>Standort-/Karriereseite helmut-fischer.com: Fertigung Sindelfingen und mögliche weitere Werke (V). (b) Werden Messsonden vergossen oder verklebt (Datenblatt/Stellenanzeige Sondenbau, Patentbeschreibung WO2012160132 …</t>
+          <t>Standort-/Karriereseite helmut-fischer.com: Fertigung Sindelfingen und mögliche weitere Werke. (b) Werden Messsonden vergossen oder verklebt (Datenblatt/Stellenanzeige Sondenbau, Patentbeschreibung WO2012160132 …</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>ASICs, optische und magnetische Encoder-ICs, Interpolatoren, Sensor-ICs sowie Mikrosysteme in Chip-on-Board-Technik und optoBGA/QFN-Gehäusen .</t>
+          <t>ASICs, optische und magnetische Encoder-ICs, Interpolatoren, Sensor-ICs sowie Mikrosysteme in Chip-on-Board-Technik und optoBGA/QFN-Gehäusen.</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>Kabeleinführungssysteme (teilbare Rahmen/Platten mit Tüllen), Kabelverschraubungen, EMV-Schirmanschlüsse, vorkonfigurierte Leitungen .</t>
+          <t>Kabeleinführungssysteme (teilbare Rahmen/Platten mit Tüllen), Kabelverschraubungen, EMV-Schirmanschlüsse, vorkonfigurierte Leitungen.</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>Standortseite/Impressum und "about us" im Browser lesen (V für Dillenburg als Fertigungsort für Messmodule, Ausschluss weiterer Werke); IVT-MODular-/IVT-S-Datenblatt auf Gehäuse "vergossen/Potting" lesen; Karriereseite Dillenburg …</t>
+          <t>Standortseite/Impressum und "about us" im Browser lesen; IVT-MODular-/IVT-S-Datenblatt auf Gehäuse "vergossen/Potting" lesen; Karriereseite Dillenburg …</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>„Entwicklung, Herstellung, Planung und der Handel mit elektrischen und optischen Steckverbindern und Systemgeräten“ plus Verkabelung .</t>
+          <t>„Entwicklung, Herstellung, Planung und der Handel mit elektrischen und optischen Steckverbindern und Systemgeräten“ plus Verkabelung.</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>Standard-Kunststoffgehäuse für Elektronik (Mini-Data-Box, NET-BOX, Smart-Box IP65/IP66, EVOTEC, SLIM-CASE), Drehknöpfe, Zubehör .</t>
+          <t>Standard-Kunststoffgehäuse für Elektronik (Mini-Data-Box, NET-BOX, Smart-Box IP65/IP66, EVOTEC, SLIM-CASE), Drehknöpfe, Zubehör.</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>stationäre Infrarot-Thermometer/Pyrometer (CT-, CTLaser-, CTi-Serien, über eine Million verkauft), Infrarot-Kameras, Handgeräte, Kalibrierquellen, Zubehör und Software .</t>
+          <t>stationäre Infrarot-Thermometer/Pyrometer (CT-, CTLaser-, CTi-Serien, über eine Million verkauft), Infrarot-Kameras, Handgeräte, Kalibrierquellen, Zubehör und Software.</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>Impressum und Gesellschafterstruktur polytec.com lesen (keine Verbindung zu Bostik/Arkema, V); aktuelle Stellenanzeige Montage Waldbronn (V für Fertigungsort, alte Anzeige 2022); Datenblatt IVS-500 (IP-Klasse, Verguss) und …</t>
+          <t>Impressum und Gesellschafterstruktur polytec.com lesen (keine Verbindung zu Bostik/Arkema, V); aktuelle Stellenanzeige Montage Waldbronn; Datenblatt IVS-500 (IP-Klasse, Verguss) und …</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>SAW-Filter und -Resonatoren (Serie), SAW-Sensoren, RFID-Tags, kundenspezifische Entwicklung und SAW-Wafer-Foundry .</t>
+          <t>SAW-Filter und -Resonatoren (Serie), SAW-Sensoren, RFID-Tags, kundenspezifische Entwicklung und SAW-Wafer-Foundry.</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>Hoch- und Niederspannungssicherungen (HH, NH), Sicherungen für Leistungselektronik, Miniatursicherungen, Sicherungshalter und -einsätze .</t>
+          <t>Hoch- und Niederspannungssicherungen (HH, NH), Sicherungen für Leistungselektronik, Miniatursicherungen, Sicherungshalter und -einsätze.</t>
         </is>
       </c>
       <c r="G42" s="11" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>elektrodynamische Schwingprüfsysteme (Shaker von 9 N bis 300 kN, wassergekühlt), Modalerreger, Wuchtmaschinen, Materialprüfsysteme .</t>
+          <t>elektrodynamische Schwingprüfsysteme (Shaker von 9 N bis 300 kN, wassergekühlt), Modalerreger, Wuchtmaschinen, Materialprüfsysteme.</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>Konzern: Präzisions-Stromversorgungen für Plasmaprozesse (Halbleiter, Dünnschicht), Industrie/Medizin, Datacenter, Telekom .</t>
+          <t>Konzern: Präzisions-Stromversorgungen für Plasmaprozesse (Halbleiter, Dünnschicht), Industrie/Medizin, Datacenter, Telekom.</t>
         </is>
       </c>
       <c r="G52" s="11" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>Drucksensoren (Messzellen, SMD-Sensoren, Transmitter, 5 mbar bis 600 bar), Feuchte-, Temperatur- und Neigungssensoren .</t>
+          <t>Drucksensoren (Messzellen, SMD-Sensoren, Transmitter, 5 mbar bis 600 bar), Feuchte-, Temperatur- und Neigungssensoren.</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>individuelle Kunststoffgehäuse vom Prototyp über Kleinserien bis mehrere tausend Stück, auch ohne Werkzeugkosten .</t>
+          <t>individuelle Kunststoffgehäuse vom Prototyp über Kleinserien bis mehrere tausend Stück, auch ohne Werkzeugkosten.</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>EMS: Flachbaugruppen und Geräte, Muster bis Serie, SMD, THT, AOI, ICT, Funktionstest, Dampfphasenlöten .</t>
+          <t>EMS: Flachbaugruppen und Geräte, Muster bis Serie, SMD, THT, AOI, ICT, Funktionstest, Dampfphasenlöten.</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>Computer- und Netzwerkstecker, IC-Sockel, Stiftleisten/Jumper, Klemmen, Kühlkörper/Strangpressprofile, Netzkabel, Modular-/USB-Kabelkonfektion, Audio-/Video-Kabel .</t>
+          <t>Computer- und Netzwerkstecker, IC-Sockel, Stiftleisten/Jumper, Klemmen, Kühlkörper/Strangpressprofile, Netzkabel, Modular-/USB-Kabelkonfektion, Audio-/Video-Kabel.</t>
         </is>
       </c>
       <c r="G60" s="11" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>Massendurchflussregler und -messer .</t>
+          <t>Massendurchflussregler und -messer.</t>
         </is>
       </c>
       <c r="G62" s="11" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>Dienstleistungen rund um elektronische Bauteile: Komponentenmanagement, Logistik, Programmierung, Test, Montage, Langzeitlagerung .</t>
+          <t>Dienstleistungen rund um elektronische Bauteile: Komponentenmanagement, Logistik, Programmierung, Test, Montage, Langzeitlagerung.</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>externe AC/DC-Netzteile, Wandstecker- und Tischnetzteile 5 bis 76 V, bis 330 W, für Büroelektronik, Set-Top-Boxen, Netzwerk, POS .</t>
+          <t>externe AC/DC-Netzteile, Wandstecker- und Tischnetzteile 5 bis 76 V, bis 330 W, für Büroelektronik, Set-Top-Boxen, Netzwerk, POS.</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>Präzisions-Messgeräte, automatische Testsysteme, programmierbare DC-Stromversorgungen (62000P), Batterie-/Netz-Simulatoren, MES .</t>
+          <t>Präzisions-Messgeräte, automatische Testsysteme, programmierbare DC-Stromversorgungen (62000P), Batterie-/Netz-Simulatoren, MES.</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>Luftbefeuchtung und Verdunstungskühlung: Elektroden-Dampfbefeuchter (Condair EL, RS, RM, GS), Direkt-Raumbefeuchtung, Wasseraufbereitung .</t>
+          <t>Luftbefeuchtung und Verdunstungskühlung: Elektroden-Dampfbefeuchter (Condair EL, RS, RM, GS), Direkt-Raumbefeuchtung, Wasseraufbereitung.</t>
         </is>
       </c>
       <c r="G70" s="11" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>EMS: Beschaffung, Bestückung von Leiterplatten, komplexe Baugruppen und Fertiggeräte (Box Build), Kabel/Kabelbäume, Prototyping, Test, ATEX-Zulassung .</t>
+          <t>EMS: Beschaffung, Bestückung von Leiterplatten, komplexe Baugruppen und Fertiggeräte (Box Build), Kabel/Kabelbäume, Prototyping, Test, ATEX-Zulassung.</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>EMS-Anbieter für Leiterplattenbestückung, Baugruppenmontage und Systembau .</t>
+          <t>EMS-Anbieter für Leiterplattenbestückung, Baugruppenmontage und Systembau.</t>
         </is>
       </c>
       <c r="G74" s="11" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>Wird in Rülzheim durch DBK EMS vergossen, verklebt, gedichtet oder lackiert, und gibt es einen Fertigungsbeleg in Stufe V?</t>
+          <t>Wird in Rülzheim durch DBK EMS vergossen, verklebt, gedichtet oder lackiert, und gibt es einen Fertigungsbeleg belegt?</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>Netzteile, Steckernetzteile, LED-Netzteile und LED-Treiber, laut Verzeichnis Fokus auf Vertrieb und Beschaffung .</t>
+          <t>Netzteile, Steckernetzteile, LED-Netzteile und LED-Treiber, laut Verzeichnis Fokus auf Vertrieb und Beschaffung.</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>Wird die Elektronik in Furth im Wald gefertigt (Stufe V), und werden dort Baugruppen vergossen, dosiert oder lackiert?</t>
+          <t>Wird die Elektronik in Furth im Wald gefertigt, und werden dort Baugruppen vergossen, dosiert oder lackiert?</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>Mess- und Datenerfassungssysteme für Test &amp; Messung, modulare Messtechnik .</t>
+          <t>Mess- und Datenerfassungssysteme für Test &amp; Messung, modulare Messtechnik.</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>Kupferlackdraht, Backlackdraht (Selfbonding), voll isolierter Draht und Hochfrequenzlitze .</t>
+          <t>Kupferlackdraht, Backlackdraht (Selfbonding), voll isolierter Draht und Hochfrequenzlitze.</t>
         </is>
       </c>
       <c r="G80" s="11" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>Thermopile- und pyroelektrische Sensoren, Hochleistungssensoren, gepulste Laser (LiDAR/3D), Fotodioden für Rauchmelder, Photon-Counting-Module, industrielle Blitzlampen .</t>
+          <t>Thermopile- und pyroelektrische Sensoren, Hochleistungssensoren, gepulste Laser (LiDAR/3D), Fotodioden für Rauchmelder, Photon-Counting-Module, industrielle Blitzlampen.</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>Federkontaktstifte (ICT/FCT, Fine-Pitch, Hochstrom, Kabelbaum), Prüfadapter, Wafer-Probe-Cards, Kontaktiersysteme für Leiterplatten, Kabelbäume, Steckverbinder .</t>
+          <t>Federkontaktstifte (ICT/FCT, Fine-Pitch, Hochstrom, Kabelbaum), Prüfadapter, Wafer-Probe-Cards, Kontaktiersysteme für Leiterplatten, Kabelbäume, Steckverbinder.</t>
         </is>
       </c>
       <c r="G86" s="11" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>Mil-Spec-Rundsteckverbinder, Rechtecksteckverbinder, Backshells, Kabelkonfektion .</t>
+          <t>Mil-Spec-Rundsteckverbinder, Rechtecksteckverbinder, Backshells, Kabelkonfektion.</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>Ladegeräte, Adapter, Schaltnetzteile von 1 bis 3000 Watt, Transformatoren, OEM/ODM-Fertigung .</t>
+          <t>Ladegeräte, Adapter, Schaltnetzteile von 1 bis 3000 Watt, Transformatoren, OEM/ODM-Fertigung.</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>RFID-Reader (LFM Loadport Reader, HFM-6X, HFS-SL, E84) für Halbleiterfabriken, Software-/Track-and-Trace-Plattformen, Schaltanlagen und Schaltschränke .</t>
+          <t>RFID-Reader (LFM Loadport Reader, HFM-6X, HFS-SL, E84) für Halbleiterfabriken, Software-/Track-and-Trace-Plattformen, Schaltanlagen und Schaltschränke.</t>
         </is>
       </c>
       <c r="G92" s="11" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>Kunststoff-Ventilatoren (Gehäuse PE, Laufrad PP), Zu- und Abluftanlagen, Abluftwäscher, Behälter, Kunststoff-Wärmetauscher, Schalldämpfer .</t>
+          <t>Kunststoff-Ventilatoren (Gehäuse PE, Laufrad PP), Zu- und Abluftanlagen, Abluftwäscher, Behälter, Kunststoff-Wärmetauscher, Schalldämpfer.</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>Lecksuchgeräte (Helium-/Wasserstoff-Schnüffler XL3000flex, Sentrac mit Sensistor-Sensor), Vakuum-Messtechnik, Sensortechnologien .</t>
+          <t>Lecksuchgeräte (Helium-/Wasserstoff-Schnüffler XL3000flex, Sentrac mit Sensistor-Sensor), Vakuum-Messtechnik, Sensortechnologien.</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>Halbleiter für Gigabit-Datenkommunikation (APIX3), ISELED-LED-Treiber/Controller (INLC10AQ), ILaS-Kabeltransceiver .</t>
+          <t>Halbleiter für Gigabit-Datenkommunikation (APIX3), ISELED-LED-Treiber/Controller (INLC10AQ), ILaS-Kabeltransceiver.</t>
         </is>
       </c>
       <c r="G98" s="11" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>Elektronikschränke (19-Zoll), Gehäuse, Baugruppenträger, Einschubkassetten, Netzwerkschränke .</t>
+          <t>Elektronikschränke (19-Zoll), Gehäuse, Baugruppenträger, Einschubkassetten, Netzwerkschränke.</t>
         </is>
       </c>
       <c r="G100" s="11" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>Wird in Darmstadt gefertigt oder zugekauft (Fertigungsbeleg)? (b) Gehört die Firma zu einer Gruppe (Regel M)? (c) Werden Gehäuse mit Dichtungen (aufgeschäumt/dosiert) geliefert?</t>
+          <t>Wird in Darmstadt gefertigt oder zugekauft (Fertigungsbeleg)? (b) Gehört die Firma zu einer Gruppe (Konzern?)? (c) Werden Gehäuse mit Dichtungen (aufgeschäumt/dosiert) geliefert?</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="F103" s="8" t="inlineStr">
         <is>
-          <t>Keramikfolien nach eigenem Verfahren auf kontinuierlichen Linien , Produktbereiche Thermal Management, Ceramic Tapes &amp; Substrates, Filterkeramik, SOFC .</t>
+          <t>Keramikfolien nach eigenem Verfahren auf kontinuierlichen Linien , Produktbereiche Thermal Management, Ceramic Tapes &amp; Substrates, Filterkeramik, SOFC.</t>
         </is>
       </c>
       <c r="G103" s="8" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>Mess- und Prüftechnik für Digital/Photonik/Netzwerk, Automotive-Energy-Solutions-Sparte mit Sitz in Böblingen .</t>
+          <t>Mess- und Prüftechnik für Digital/Photonik/Netzwerk, Automotive-Energy-Solutions-Sparte mit Sitz in Böblingen.</t>
         </is>
       </c>
       <c r="G104" s="11" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>Gruppe: DC-/AC-Netzgeräte, elektronische Lasten, Hipot-/Isolationsprüfgeräte .</t>
+          <t>Gruppe: DC-/AC-Netzgeräte, elektronische Lasten, Hipot-/Isolationsprüfgeräte.</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>Wird in Pforzheim gefertigt (V) und welche Baugruppen/Produkte werden dort verklebt, gedichtet, vergossen (Hybrid-Teile mit Dichtfunktion, Sensor-/Leistungselektronik-Baugruppen)?</t>
+          <t>Wird in Pforzheim gefertigt und welche Baugruppen/Produkte werden dort verklebt, gedichtet, vergossen (Hybrid-Teile mit Dichtfunktion, Sensor-/Leistungselektronik-Baugruppen)?</t>
         </is>
       </c>
       <c r="I108" s="11" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="H109" s="8" t="inlineStr">
         <is>
-          <t>Werden Thermostate/Heizsysteme in Lauda-Königshofen gefertigt oder montiert (V)?</t>
+          <t>Werden Thermostate/Heizsysteme in Lauda-Königshofen gefertigt oder montiert?</t>
         </is>
       </c>
       <c r="I109" s="8" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F111" s="8" t="inlineStr">
         <is>
-          <t>Hybridbaugruppen aus Kunststoff und Metall (Spritzguss mit Stanzteilen), Sondermaschinenbau für die eigene Produktion, Kontaktpins/Stanzkontakte .</t>
+          <t>Hybridbaugruppen aus Kunststoff und Metall (Spritzguss mit Stanzteilen), Sondermaschinenbau für die eigene Produktion, Kontaktpins/Stanzkontakte.</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
-          <t>Lasersysteme für Leiterplatten-Prototyping und Depaneling, IC-Packaging, Schablonen, Laser Direct Structuring (LDS), Kunststoffschweißen, Solar- und Batteriefertigung .</t>
+          <t>Lasersysteme für Leiterplatten-Prototyping und Depaneling, IC-Packaging, Schablonen, Laser Direct Structuring (LDS), Kunststoffschweißen, Solar- und Batteriefertigung.</t>
         </is>
       </c>
       <c r="G114" s="11" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="F120" s="11" t="inlineStr">
         <is>
-          <t>Kunststoffgehäuse "von der Einzelanfertigung bis zur Serie", Folien- und Silikontastaturen, Touch-Displays, Acrylglas-Teile .</t>
+          <t>Kunststoffgehäuse "von der Einzelanfertigung bis zur Serie", Folien- und Silikontastaturen, Touch-Displays, Acrylglas-Teile.</t>
         </is>
       </c>
       <c r="G120" s="11" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
-          <t>Anschlusstechnik: Klemmen, Leiterplattensteckverbinder, Board-to-Board, Patchfelder, Wanddosen, Relais und Koppelmodule .</t>
+          <t>Anschlusstechnik: Klemmen, Leiterplattensteckverbinder, Board-to-Board, Patchfelder, Wanddosen, Relais und Koppelmodule.</t>
         </is>
       </c>
       <c r="G122" s="11" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="F123" s="8" t="inlineStr">
         <is>
-          <t>EMS-Dienstleistungen: elektronische und mechatronische Baugruppen, Projektmanagement, Werkzeugbau, Materiallogistik, After-Sales .</t>
+          <t>EMS-Dienstleistungen: elektronische und mechatronische Baugruppen, Projektmanagement, Werkzeugbau, Materiallogistik, After-Sales.</t>
         </is>
       </c>
       <c r="G123" s="8" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="F129" s="8" t="inlineStr">
         <is>
-          <t>Koordinatenmessgeräte, optische CMM, 3D-Laserscanner, Röntgen-/CT-Systeme, Messmikroskope, Large-Volume-Metrology .</t>
+          <t>Koordinatenmessgeräte, optische CMM, 3D-Laserscanner, Röntgen-/CT-Systeme, Messmikroskope, Large-Volume-Metrology.</t>
         </is>
       </c>
       <c r="G129" s="8" t="inlineStr">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="F132" s="11" t="inlineStr">
         <is>
-          <t>Gehäuse, Schränke, Subracks, Backplanes, Stromversorgungen, vormontierte Chassis für Telekommunikation, Rechenzentren und Verkehrstechnik .</t>
+          <t>Gehäuse, Schränke, Subracks, Backplanes, Stromversorgungen, vormontierte Chassis für Telekommunikation, Rechenzentren und Verkehrstechnik.</t>
         </is>
       </c>
       <c r="G132" s="11" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="F134" s="11" t="inlineStr">
         <is>
-          <t>Reedschalter, SMD-Reedschalter, Reedsensoren, Füllstandssensoren, Magnete, kundenspezifische Sensoren mit Stecker/Kabel und Leiterplattenbaugruppen .</t>
+          <t>Reedschalter, SMD-Reedschalter, Reedsensoren, Füllstandssensoren, Magnete, kundenspezifische Sensoren mit Stecker/Kabel und Leiterplattenbaugruppen.</t>
         </is>
       </c>
       <c r="G134" s="11" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="F136" s="11" t="inlineStr">
         <is>
-          <t>aktive und passive Tastköpfe, Hochspannungstastköpfe, Stromtastköpfe und Stromwandler, Kalibriergeneratoren, Hochspannungsgeräte, Netzteile, Zubehör .</t>
+          <t>aktive und passive Tastköpfe, Hochspannungstastköpfe, Stromtastköpfe und Stromwandler, Kalibriergeneratoren, Hochspannungsgeräte, Netzteile, Zubehör.</t>
         </is>
       </c>
       <c r="G136" s="11" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -7204,7 +7204,7 @@
       </c>
       <c r="D138" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="D140" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E140" s="11" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="D142" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E142" s="11" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="D144" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E144" s="11" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="F144" s="11" t="inlineStr">
         <is>
-          <t>Antennen: Planarantennen für GSM/GPS, Fahrzeugantennen, Basisstationsantennen, kombinierte Mobilfunk-/Telematikantennen für Autos .</t>
+          <t>Antennen: Planarantennen für GSM/GPS, Fahrzeugantennen, Basisstationsantennen, kombinierte Mobilfunk-/Telematikantennen für Autos.</t>
         </is>
       </c>
       <c r="G144" s="11" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D146" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E146" s="11" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="F147" s="8" t="inlineStr">
         <is>
-          <t>HF-Koaxialsteckverbinder, HF-Messtechnik, HF-Steckverbinder-Systeme für Automobil-Elektronik, Medizintechnik und Industrieelektronik, Fiberoptik, Kabel-Assemblies .</t>
+          <t>HF-Koaxialsteckverbinder, HF-Messtechnik, HF-Steckverbinder-Systeme für Automobil-Elektronik, Medizintechnik und Industrieelektronik, Fiberoptik, Kabel-Assemblies.</t>
         </is>
       </c>
       <c r="G147" s="8" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="D148" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E148" s="11" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="F149" s="8" t="inlineStr">
         <is>
-          <t>EMS-Dienstleistungen: Leiterplattenbestückung, Chip-on-Board, mechanische Montage, Systemintegration, Entwicklung, Prototyping, Prüfmittelentwicklung, Reparatur .</t>
+          <t>EMS-Dienstleistungen: Leiterplattenbestückung, Chip-on-Board, mechanische Montage, Systemintegration, Entwicklung, Prototyping, Prüfmittelentwicklung, Reparatur.</t>
         </is>
       </c>
       <c r="G149" s="8" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="D150" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E150" s="11" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="D151" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="D152" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="F152" s="11" t="inlineStr">
         <is>
-          <t>Präzisions-Stanzwerkzeuge, Stanz-Biegeteile und komplette Baugruppen für Automotive-Elektrik, Elektronik und Telekommunikation, enge Toleranzen .</t>
+          <t>Präzisions-Stanzwerkzeuge, Stanz-Biegeteile und komplette Baugruppen für Automotive-Elektrik, Elektronik und Telekommunikation, enge Toleranzen.</t>
         </is>
       </c>
       <c r="G152" s="11" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="D154" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="D155" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="D156" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E156" s="11" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="D157" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="F157" s="8" t="inlineStr">
         <is>
-          <t>Drahtlos-LAN-Module, System-on-Modules (Qualcomm, NXP i.MX9), Access Points, Device Server, Print Server .</t>
+          <t>Drahtlos-LAN-Module, System-on-Modules (Qualcomm, NXP i.MX9), Access Points, Device Server, Print Server.</t>
         </is>
       </c>
       <c r="G157" s="8" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="D158" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E158" s="11" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="D159" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="F159" s="8" t="inlineStr">
         <is>
-          <t>Leiterplattenbestückung (SMD und THT, Muster bis Serie) bis zu Gerätesystemen, Elektronikfertigung/EMS, ISO 9001 seit 2001 .</t>
+          <t>Leiterplattenbestückung (SMD und THT, Muster bis Serie) bis zu Gerätesystemen, Elektronikfertigung/EMS, ISO 9001 seit 2001.</t>
         </is>
       </c>
       <c r="G159" s="8" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="D160" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E160" s="11" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="D161" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="D162" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E162" s="11" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D163" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="F163" s="8" t="inlineStr">
         <is>
-          <t>Fernseher, Digitalradios (DAB+), Satelliten-/Kabel-Receiver, Wallboxen (TECHNIVOLT), Zubehör .</t>
+          <t>Fernseher, Digitalradios (DAB+), Satelliten-/Kabel-Receiver, Wallboxen (TECHNIVOLT), Zubehör.</t>
         </is>
       </c>
       <c r="G163" s="8" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="D164" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E164" s="11" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="F164" s="11" t="inlineStr">
         <is>
-          <t>Steckverbinder (HF-Koax, RJ45, M12-Rundsteckverbinder, DIN-41622, 4.3-10 auch für Glasfaser), Netzwerkkomponenten, Spritzguss, Industrial Electronics, Kabelkonfektion .</t>
+          <t>Steckverbinder (HF-Koax, RJ45, M12-Rundsteckverbinder, DIN-41622, 4.3-10 auch für Glasfaser), Netzwerkkomponenten, Spritzguss, Industrial Electronics, Kabelkonfektion.</t>
         </is>
       </c>
       <c r="G164" s="11" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="D165" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="D166" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E166" s="11" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="D167" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="F167" s="8" t="inlineStr">
         <is>
-          <t>Embedded-Compute-Module (COM-HPC, COM Express, Qseven, SMARC, OSM) und komplette Systeme einschließlich Design- und Fertigungsdienstleistung für Industrie-OEMs .</t>
+          <t>Embedded-Compute-Module (COM-HPC, COM Express, Qseven, SMARC, OSM) und komplette Systeme einschließlich Design- und Fertigungsdienstleistung für Industrie-OEMs.</t>
         </is>
       </c>
       <c r="G167" s="8" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D168" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E168" s="11" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="D169" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="F169" s="8" t="inlineStr">
         <is>
-          <t>Leiterplatten-Steckverbinder (Stiftleisten, Buchsenleisten, D-Sub, IC-Fassungen, Modular Jacks, LED- und Power-Steckverbinder), über 20.000 Varianten .</t>
+          <t>Leiterplatten-Steckverbinder (Stiftleisten, Buchsenleisten, D-Sub, IC-Fassungen, Modular Jacks, LED- und Power-Steckverbinder), über 20.000 Varianten.</t>
         </is>
       </c>
       <c r="G169" s="8" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="D170" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E170" s="11" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="D171" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
@@ -8870,7 +8870,7 @@
       </c>
       <c r="D172" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E172" s="11" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="F172" s="11" t="inlineStr">
         <is>
-          <t>Industrie-PCs, ruggedized Fahrzeugterminals (DLT-V-Serie, IP65, vibrations- und stoßfest, Heizung, Weitbereichs-Netzteil), Tablets .</t>
+          <t>Industrie-PCs, ruggedized Fahrzeugterminals (DLT-V-Serie, IP65, vibrations- und stoßfest, Heizung, Weitbereichs-Netzteil), Tablets.</t>
         </is>
       </c>
       <c r="G172" s="11" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="D173" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="F173" s="8" t="inlineStr">
         <is>
-          <t>Elektrifizierung des Antriebsstrangs, Leistungselektronik, Produktgruppen elektrischer Antriebsstrang, passive und aktive Komponenten .</t>
+          <t>Elektrifizierung des Antriebsstrangs, Leistungselektronik, Produktgruppen elektrischer Antriebsstrang, passive und aktive Komponenten.</t>
         </is>
       </c>
       <c r="G173" s="8" t="inlineStr">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="D174" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E174" s="11" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="F174" s="11" t="inlineStr">
         <is>
-          <t>programmierbare DC-Netzteile 30 W bis 150 kW und AC-Quellen 800 VA bis 480 kVA, Marken Sorensen, Elgar, California Instruments .</t>
+          <t>programmierbare DC-Netzteile 30 W bis 150 kW und AC-Quellen 800 VA bis 480 kVA, Marken Sorensen, Elgar, California Instruments.</t>
         </is>
       </c>
       <c r="G174" s="11" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="D175" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="F175" s="8" t="inlineStr">
         <is>
-          <t>Sensorlösungen, Displays, Brems- und Komfortsysteme, Software .</t>
+          <t>Sensorlösungen, Displays, Brems- und Komfortsysteme, Software.</t>
         </is>
       </c>
       <c r="G175" s="8" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="D176" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E176" s="11" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="D177" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="D178" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E178" s="11" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="F178" s="11" t="inlineStr">
         <is>
-          <t>Verzeichnis beschreibt DETAKTA als Spezialisten für den Handel mit innovativen Isolierstoffen für industrielle Anwendungen .</t>
+          <t>Verzeichnis beschreibt DETAKTA als Spezialisten für den Handel mit innovativen Isolierstoffen für industrielle Anwendungen.</t>
         </is>
       </c>
       <c r="G178" s="11" t="inlineStr">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="D179" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="F179" s="8" t="inlineStr">
         <is>
-          <t>kundenspezifische Displaylösungen seit 1989, passive Displays bis TFT, AMOLED, PMOLED, e-Paper .</t>
+          <t>kundenspezifische Displaylösungen seit 1989, passive Displays bis TFT, AMOLED, PMOLED, e-Paper.</t>
         </is>
       </c>
       <c r="G179" s="8" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="D180" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E180" s="11" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="D181" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="D182" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E182" s="11" t="inlineStr">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="D183" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
@@ -9419,7 +9419,7 @@
       </c>
       <c r="F183" s="8" t="inlineStr">
         <is>
-          <t>Hochleistungs-LEDs, SMD-LEDs, Lampen, LED-Lichtmodule, Anzeigen, Optokoppler, Infrarotbauteile .</t>
+          <t>Hochleistungs-LEDs, SMD-LEDs, Lampen, LED-Lichtmodule, Anzeigen, Optokoppler, Infrarotbauteile.</t>
         </is>
       </c>
       <c r="G183" s="8" t="inlineStr">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="D184" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E184" s="11" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="D185" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="D186" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E186" s="11" t="inlineStr">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="D187" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="D188" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E188" s="11" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="F188" s="11" t="inlineStr">
         <is>
-          <t>Branchenbucheintrag "Metallwarenfabrik" .</t>
+          <t>Branchenbucheintrag "Metallwarenfabrik".</t>
         </is>
       </c>
       <c r="G188" s="11" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="D189" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="F189" s="8" t="inlineStr">
         <is>
-          <t>2025 aus Bosch ausgegliederte Sicherheits- und Kommunikationsgruppe (Triton), Geschäfte Intrusion &amp; Access, Video, Audio, EMS .</t>
+          <t>2025 aus Bosch ausgegliederte Sicherheits- und Kommunikationsgruppe (Triton), Geschäfte Intrusion &amp; Access, Video, Audio, EMS.</t>
         </is>
       </c>
       <c r="G189" s="8" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D190" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E190" s="11" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="D191" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="D192" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E192" s="11" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="D193" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="D194" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E194" s="11" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="D195" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="F195" s="8" t="inlineStr">
         <is>
-          <t>Umwälzthermostate, Kältemaschinen/Chiller und dynamische Temperiersysteme .</t>
+          <t>Umwälzthermostate, Kältemaschinen/Chiller und dynamische Temperiersysteme.</t>
         </is>
       </c>
       <c r="G195" s="8" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="D196" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E196" s="11" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="D197" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
@@ -10144,7 +10144,7 @@
       </c>
       <c r="D198" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E198" s="11" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="D199" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="F199" s="8" t="inlineStr">
         <is>
-          <t>Anbieter professioneller Stromversorgungen: AC/DC, DC/DC, elektronische Lasten, Bordnetz-Simulation, Laserdiodentreiber, Hochspannung, Wechselrichter .</t>
+          <t>Anbieter professioneller Stromversorgungen: AC/DC, DC/DC, elektronische Lasten, Bordnetz-Simulation, Laserdiodentreiber, Hochspannung, Wechselrichter.</t>
         </is>
       </c>
       <c r="G199" s="8" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="D200" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E200" s="11" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="F200" s="11" t="inlineStr">
         <is>
-          <t>Wire and Cable für Automotive, Kabelkonfektion für Medizin, Flexible Flat Cable für Consumer/Automotive .</t>
+          <t>Wire and Cable für Automotive, Kabelkonfektion für Medizin, Flexible Flat Cable für Consumer/Automotive.</t>
         </is>
       </c>
       <c r="G200" s="11" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="D201" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="D202" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E202" s="11" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="D203" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="F203" s="8" t="inlineStr">
         <is>
-          <t>Gruppe entwickelt und fertigt elektromechanische Relais (Automotive, General Purpose, Industrial, Zubehör), Hochstrom-/Hochvolt-Relais für Solar und E-Mobility .</t>
+          <t>Gruppe entwickelt und fertigt elektromechanische Relais (Automotive, General Purpose, Industrial, Zubehör), Hochstrom-/Hochvolt-Relais für Solar und E-Mobility.</t>
         </is>
       </c>
       <c r="G203" s="8" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="D204" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E204" s="11" t="inlineStr">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="F204" s="11" t="inlineStr">
         <is>
-          <t>Steckverbinder für E-Mobility, Industrie und Medizintechnik: Batterie-Steckverbinder (Feder- und Messerkontakt) ab Lager und kundenspezifische Entwicklung .</t>
+          <t>Steckverbinder für E-Mobility, Industrie und Medizintechnik: Batterie-Steckverbinder (Feder- und Messerkontakt) ab Lager und kundenspezifische Entwicklung.</t>
         </is>
       </c>
       <c r="G204" s="11" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="D205" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Impressum/Standortseite 2e-mechatronic.de lesen (V für Sitz = Fertigungsort); Datenblatt Neigungssensor (Schutzart, Vergussmasse im Gehäuse?); Stellenanzeige Montage/Produktion Kirchheim; Patente Anmelder "2E mechatronic" in …</t>
+          <t>Impressum/Standortseite 2e-mechatronic.de lesen; Datenblatt Neigungssensor (Schutzart, Vergussmasse im Gehäuse?); Stellenanzeige Montage/Produktion Kirchheim; Patente Anmelder "2E mechatronic" in …</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Komponenten und Systeme der Mensch-Maschine-Interaktion: Kartenleser (Kontakt/kontaktlos), Schalter, Encoder, Ticketing-Systeme .</t>
+          <t>Komponenten und Systeme der Mensch-Maschine-Interaktion: Kartenleser (Kontakt/kontaktlos), Schalter, Encoder, Ticketing-Systeme.</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>"intelligente Elektronik für mobile Energieversorgung, Messtechnik, Trafoschaltrelais" sowie EMS (E2MS) .</t>
+          <t>"intelligente Elektronik für mobile Energieversorgung, Messtechnik, Trafoschaltrelais" sowie EMS (E2MS).</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Schalter, Drucktaster, Not-Halt-Schalter, Kontaktgeber, Bedieneinheiten, Gehäuse, Klemmen, Endschalter, RFID-Systeme, Bus-Lösungen .</t>
+          <t>Schalter, Drucktaster, Not-Halt-Schalter, Kontaktgeber, Bedieneinheiten, Gehäuse, Klemmen, Endschalter, RFID-Systeme, Bus-Lösungen.</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Messgeräte für Schichtdicke, Materialanalyse (Röntgenfluoreszenz), Materialprüfung und Mikrohärte, von Handgeräten bis zu Inline-Systemen .</t>
+          <t>Messgeräte für Schichtdicke, Materialanalyse (Röntgenfluoreszenz), Materialprüfung und Mikrohärte, von Handgeräten bis zu Inline-Systemen.</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>Standort-/Karriereseite helmut-fischer.com: Fertigung Sindelfingen und mögliche weitere Werke (V). (b) Werden Messsonden vergossen oder verklebt (Datenblatt/Stellenanzeige Sondenbau, Patentbeschreibung WO2012160132 …</t>
+          <t>Standort-/Karriereseite helmut-fischer.com: Fertigung Sindelfingen und mögliche weitere Werke. (b) Werden Messsonden vergossen oder verklebt (Datenblatt/Stellenanzeige Sondenbau, Patentbeschreibung WO2012160132 …</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Kabeleinführungssysteme (teilbare Rahmen/Platten mit Tüllen), Kabelverschraubungen, EMV-Schirmanschlüsse, vorkonfigurierte Leitungen .</t>
+          <t>Kabeleinführungssysteme (teilbare Rahmen/Platten mit Tüllen), Kabelverschraubungen, EMV-Schirmanschlüsse, vorkonfigurierte Leitungen.</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Standard-Kunststoffgehäuse für Elektronik (Mini-Data-Box, NET-BOX, Smart-Box IP65/IP66, EVOTEC, SLIM-CASE), Drehknöpfe, Zubehör .</t>
+          <t>Standard-Kunststoffgehäuse für Elektronik (Mini-Data-Box, NET-BOX, Smart-Box IP65/IP66, EVOTEC, SLIM-CASE), Drehknöpfe, Zubehör.</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>Impressum und Gesellschafterstruktur polytec.com lesen (keine Verbindung zu Bostik/Arkema, V); aktuelle Stellenanzeige Montage Waldbronn (V für Fertigungsort, alte Anzeige 2022); Datenblatt IVS-500 (IP-Klasse, Verguss) und …</t>
+          <t>Impressum und Gesellschafterstruktur polytec.com lesen (keine Verbindung zu Bostik/Arkema, V); aktuelle Stellenanzeige Montage Waldbronn; Datenblatt IVS-500 (IP-Klasse, Verguss) und …</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>Konzern: Präzisions-Stromversorgungen für Plasmaprozesse (Halbleiter, Dünnschicht), Industrie/Medizin, Datacenter, Telekom .</t>
+          <t>Konzern: Präzisions-Stromversorgungen für Plasmaprozesse (Halbleiter, Dünnschicht), Industrie/Medizin, Datacenter, Telekom.</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
@@ -11332,7 +11332,7 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>Mess- und Datenerfassungssysteme für Test &amp; Messung, modulare Messtechnik .</t>
+          <t>Mess- und Datenerfassungssysteme für Test &amp; Messung, modulare Messtechnik.</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>Federkontaktstifte (ICT/FCT, Fine-Pitch, Hochstrom, Kabelbaum), Prüfadapter, Wafer-Probe-Cards, Kontaktiersysteme für Leiterplatten, Kabelbäume, Steckverbinder .</t>
+          <t>Federkontaktstifte (ICT/FCT, Fine-Pitch, Hochstrom, Kabelbaum), Prüfadapter, Wafer-Probe-Cards, Kontaktiersysteme für Leiterplatten, Kabelbäume, Steckverbinder.</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>Mess- und Prüftechnik für Digital/Photonik/Netzwerk, Automotive-Energy-Solutions-Sparte mit Sitz in Böblingen .</t>
+          <t>Mess- und Prüftechnik für Digital/Photonik/Netzwerk, Automotive-Energy-Solutions-Sparte mit Sitz in Böblingen.</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>Wird in Pforzheim gefertigt (V) und welche Baugruppen/Produkte werden dort verklebt, gedichtet, vergossen (Hybrid-Teile mit Dichtfunktion, Sensor-/Leistungselektronik-Baugruppen)?</t>
+          <t>Wird in Pforzheim gefertigt und welche Baugruppen/Produkte werden dort verklebt, gedichtet, vergossen (Hybrid-Teile mit Dichtfunktion, Sensor-/Leistungselektronik-Baugruppen)?</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>Werden Thermostate/Heizsysteme in Lauda-Königshofen gefertigt oder montiert (V)?</t>
+          <t>Werden Thermostate/Heizsysteme in Lauda-Königshofen gefertigt oder montiert?</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>Hybridbaugruppen aus Kunststoff und Metall (Spritzguss mit Stanzteilen), Sondermaschinenbau für die eigene Produktion, Kontaktpins/Stanzkontakte .</t>
+          <t>Hybridbaugruppen aus Kunststoff und Metall (Spritzguss mit Stanzteilen), Sondermaschinenbau für die eigene Produktion, Kontaktpins/Stanzkontakte.</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>Anschlusstechnik: Klemmen, Leiterplattensteckverbinder, Board-to-Board, Patchfelder, Wanddosen, Relais und Koppelmodule .</t>
+          <t>Anschlusstechnik: Klemmen, Leiterplattensteckverbinder, Board-to-Board, Patchfelder, Wanddosen, Relais und Koppelmodule.</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>Gehäuse, Schränke, Subracks, Backplanes, Stromversorgungen, vormontierte Chassis für Telekommunikation, Rechenzentren und Verkehrstechnik .</t>
+          <t>Gehäuse, Schränke, Subracks, Backplanes, Stromversorgungen, vormontierte Chassis für Telekommunikation, Rechenzentren und Verkehrstechnik.</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
@@ -12410,7 +12410,7 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>Präzisions-Stanzwerkzeuge, Stanz-Biegeteile und komplette Baugruppen für Automotive-Elektrik, Elektronik und Telekommunikation, enge Toleranzen .</t>
+          <t>Präzisions-Stanzwerkzeuge, Stanz-Biegeteile und komplette Baugruppen für Automotive-Elektrik, Elektronik und Telekommunikation, enge Toleranzen.</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Steckverbinder (HF-Koax, RJ45, M12-Rundsteckverbinder, DIN-41622, 4.3-10 auch für Glasfaser), Netzwerkkomponenten, Spritzguss, Industrial Electronics, Kabelkonfektion .</t>
+          <t>Steckverbinder (HF-Koax, RJ45, M12-Rundsteckverbinder, DIN-41622, 4.3-10 auch für Glasfaser), Netzwerkkomponenten, Spritzguss, Industrial Electronics, Kabelkonfektion.</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
@@ -12704,7 +12704,7 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Embedded-Compute-Module (COM-HPC, COM Express, Qseven, SMARC, OSM) und komplette Systeme einschließlich Design- und Fertigungsdienstleistung für Industrie-OEMs .</t>
+          <t>Embedded-Compute-Module (COM-HPC, COM Express, Qseven, SMARC, OSM) und komplette Systeme einschließlich Design- und Fertigungsdienstleistung für Industrie-OEMs.</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>kundenspezifische Displaylösungen seit 1989, passive Displays bis TFT, AMOLED, PMOLED, e-Paper .</t>
+          <t>kundenspezifische Displaylösungen seit 1989, passive Displays bis TFT, AMOLED, PMOLED, e-Paper.</t>
         </is>
       </c>
       <c r="G48" s="11" t="inlineStr">
@@ -12949,7 +12949,7 @@
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>Hochleistungs-LEDs, SMD-LEDs, Lampen, LED-Lichtmodule, Anzeigen, Optokoppler, Infrarotbauteile .</t>
+          <t>Hochleistungs-LEDs, SMD-LEDs, Lampen, LED-Lichtmodule, Anzeigen, Optokoppler, Infrarotbauteile.</t>
         </is>
       </c>
       <c r="G52" s="11" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>Branchenbucheintrag "Metallwarenfabrik" .</t>
+          <t>Branchenbucheintrag "Metallwarenfabrik".</t>
         </is>
       </c>
       <c r="G54" s="11" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>Umwälzthermostate, Kältemaschinen/Chiller und dynamische Temperiersysteme .</t>
+          <t>Umwälzthermostate, Kältemaschinen/Chiller und dynamische Temperiersysteme.</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
@@ -13145,7 +13145,7 @@
       </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
-          <t>Anbieter professioneller Stromversorgungen: AC/DC, DC/DC, elektronische Lasten, Bordnetz-Simulation, Laserdiodentreiber, Hochspannung, Wechselrichter .</t>
+          <t>Anbieter professioneller Stromversorgungen: AC/DC, DC/DC, elektronische Lasten, Bordnetz-Simulation, Laserdiodentreiber, Hochspannung, Wechselrichter.</t>
         </is>
       </c>
       <c r="G56" s="11" t="inlineStr">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Industriedisplays von 7-Segment- bis Farb-Touch-Displays, Displays mit und ohne Touch, Optical Bonding, Touch-Lösungen und Assembly Services .</t>
+          <t>Industriedisplays von 7-Segment- bis Farb-Touch-Displays, Displays mit und ohne Touch, Optical Bonding, Touch-Lösungen und Assembly Services.</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
@@ -13539,7 +13539,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Batch-Nassprozessanlagen für Ätzen und Reinigen (Wet Benches), Chemie-Versorgungs- und Entsorgungssysteme, Carrier .</t>
+          <t>Batch-Nassprozessanlagen für Ätzen und Reinigen (Wet Benches), Chemie-Versorgungs- und Entsorgungssysteme, Carrier.</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -13549,7 +13549,7 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>Impressum und Produktseiten der Firmenwebsite (Domain unbekannt) lesen: Fertigung Neumarkt (V), Steuerung/Sensorik Eigenbau oder Zukauf; Stellenanzeigen Neumarkt (Montage, Elektro).</t>
+          <t>Impressum und Produktseiten der Firmenwebsite (Domain unbekannt) lesen: Fertigung Neumarkt, Steuerung/Sensorik Eigenbau oder Zukauf; Stellenanzeigen Neumarkt (Montage, Elektro).</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
@@ -14029,7 +14029,7 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>EMS: Flachbaugruppen und Geräte, Muster bis Serie, SMD, THT, AOI, ICT, Funktionstest, Dampfphasenlöten .</t>
+          <t>EMS: Flachbaugruppen und Geräte, Muster bis Serie, SMD, THT, AOI, ICT, Funktionstest, Dampfphasenlöten.</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
@@ -14127,7 +14127,7 @@
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>Präzisions-Messgeräte, automatische Testsysteme, programmierbare DC-Stromversorgungen (62000P), Batterie-/Netz-Simulatoren, MES .</t>
+          <t>Präzisions-Messgeräte, automatische Testsysteme, programmierbare DC-Stromversorgungen (62000P), Batterie-/Netz-Simulatoren, MES.</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
@@ -14235,7 +14235,7 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>Wird die Elektronik in Furth im Wald gefertigt (Stufe V), und werden dort Baugruppen vergossen, dosiert oder lackiert?</t>
+          <t>Wird die Elektronik in Furth im Wald gefertigt, und werden dort Baugruppen vergossen, dosiert oder lackiert?</t>
         </is>
       </c>
       <c r="I22" s="11" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>RFID-Reader (LFM Loadport Reader, HFM-6X, HFS-SL, E84) für Halbleiterfabriken, Software-/Track-and-Trace-Plattformen, Schaltanlagen und Schaltschränke .</t>
+          <t>RFID-Reader (LFM Loadport Reader, HFM-6X, HFS-SL, E84) für Halbleiterfabriken, Software-/Track-and-Trace-Plattformen, Schaltanlagen und Schaltschränke.</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
@@ -14372,7 +14372,7 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>Halbleiter für Gigabit-Datenkommunikation (APIX3), ISELED-LED-Treiber/Controller (INLC10AQ), ILaS-Kabeltransceiver .</t>
+          <t>Halbleiter für Gigabit-Datenkommunikation (APIX3), ISELED-LED-Treiber/Controller (INLC10AQ), ILaS-Kabeltransceiver.</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>Keramikfolien nach eigenem Verfahren auf kontinuierlichen Linien , Produktbereiche Thermal Management, Ceramic Tapes &amp; Substrates, Filterkeramik, SOFC .</t>
+          <t>Keramikfolien nach eigenem Verfahren auf kontinuierlichen Linien , Produktbereiche Thermal Management, Ceramic Tapes &amp; Substrates, Filterkeramik, SOFC.</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
@@ -14617,7 +14617,7 @@
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>Kunststoffgehäuse "von der Einzelanfertigung bis zur Serie", Folien- und Silikontastaturen, Touch-Displays, Acrylglas-Teile .</t>
+          <t>Kunststoffgehäuse "von der Einzelanfertigung bis zur Serie", Folien- und Silikontastaturen, Touch-Displays, Acrylglas-Teile.</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>Reedschalter, SMD-Reedschalter, Reedsensoren, Füllstandssensoren, Magnete, kundenspezifische Sensoren mit Stecker/Kabel und Leiterplattenbaugruppen .</t>
+          <t>Reedschalter, SMD-Reedschalter, Reedsensoren, Füllstandssensoren, Magnete, kundenspezifische Sensoren mit Stecker/Kabel und Leiterplattenbaugruppen.</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>HF-Koaxialsteckverbinder, HF-Messtechnik, HF-Steckverbinder-Systeme für Automobil-Elektronik, Medizintechnik und Industrieelektronik, Fiberoptik, Kabel-Assemblies .</t>
+          <t>HF-Koaxialsteckverbinder, HF-Messtechnik, HF-Steckverbinder-Systeme für Automobil-Elektronik, Medizintechnik und Industrieelektronik, Fiberoptik, Kabel-Assemblies.</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>Industrie-PCs, ruggedized Fahrzeugterminals (DLT-V-Serie, IP65, vibrations- und stoßfest, Heizung, Weitbereichs-Netzteil), Tablets .</t>
+          <t>Industrie-PCs, ruggedized Fahrzeugterminals (DLT-V-Serie, IP65, vibrations- und stoßfest, Heizung, Weitbereichs-Netzteil), Tablets.</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>Elektrifizierung des Antriebsstrangs, Leistungselektronik, Produktgruppen elektrischer Antriebsstrang, passive und aktive Komponenten .</t>
+          <t>Elektrifizierung des Antriebsstrangs, Leistungselektronik, Produktgruppen elektrischer Antriebsstrang, passive und aktive Komponenten.</t>
         </is>
       </c>
       <c r="G42" s="11" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Sensorlösungen, Displays, Brems- und Komfortsysteme, Software .</t>
+          <t>Sensorlösungen, Displays, Brems- und Komfortsysteme, Software.</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
@@ -15450,7 +15450,7 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>2025 aus Bosch ausgegliederte Sicherheits- und Kommunikationsgruppe (Triton), Geschäfte Intrusion &amp; Access, Video, Audio, EMS .</t>
+          <t>2025 aus Bosch ausgegliederte Sicherheits- und Kommunikationsgruppe (Triton), Geschäfte Intrusion &amp; Access, Video, Audio, EMS.</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>Steckverbinder für E-Mobility, Industrie und Medizintechnik: Batterie-Steckverbinder (Feder- und Messerkontakt) ab Lager und kundenspezifische Entwicklung .</t>
+          <t>Steckverbinder für E-Mobility, Industrie und Medizintechnik: Batterie-Steckverbinder (Feder- und Messerkontakt) ab Lager und kundenspezifische Entwicklung.</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
@@ -15795,7 +15795,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Spektrumanalysatoren (SPECTRAN), Mess- und Richtantennen (IsoLOG 3D, HyperLOG), Drohnendetektion/-abwehr AARTOS, HF-Schirmmaterialien .</t>
+          <t>Spektrumanalysatoren (SPECTRAN), Mess- und Richtantennen (IsoLOG 3D, HyperLOG), Drohnendetektion/-abwehr AARTOS, HF-Schirmmaterialien.</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
@@ -15844,7 +15844,7 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Drucksensoren und analoge Signalaufbereitungs-ICs ("Frame ASICs") .</t>
+          <t>Drucksensoren und analoge Signalaufbereitungs-ICs ("Frame ASICs").</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -15942,7 +15942,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Maschinen (Ätz-, Laminier-, Bohr-/Fräsmaschinen, Durchkontaktierung), fotobeschichtetes Basismaterial und Verbrauchsmaterial für Leiterplatten-Kleinserien .</t>
+          <t>Maschinen (Ätz-, Laminier-, Bohr-/Fräsmaschinen, Durchkontaktierung), fotobeschichtetes Basismaterial und Verbrauchsmaterial für Leiterplatten-Kleinserien.</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -16001,7 +16001,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Impressum/Standort colandis.com, Stellenanzeigen Montage Kahla (V für Fertigungsort); (b) Datenblatt FFM-C/-E: Dichtung (PU/Klebung), Lüfter-/Regelelektronik vergossen? Schutzart; (c) Patent-/Schutzrechtsnummern …</t>
+          <t>Impressum/Standort colandis.com, Stellenanzeigen Montage Kahla; (b) Datenblatt FFM-C/-E: Dichtung (PU/Klebung), Lüfter-/Regelelektronik vergossen? Schutzart; (c) Patent-/Schutzrechtsnummern …</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
@@ -16040,7 +16040,7 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>LED-Chips, SMD- und Through-Hole-LEDs sowie Photodioden von 200 nm (UV-C) bis 2300 nm (SWIR), Monolithic Displays, Serien in kleinen und mittleren Mengen .</t>
+          <t>LED-Chips, SMD- und Through-Hole-LEDs sowie Photodioden von 200 nm (UV-C) bis 2300 nm (SWIR), Monolithic Displays, Serien in kleinen und mittleren Mengen.</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
@@ -16138,7 +16138,7 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Tragbare und stationäre Gasmessgeräte, Gassensoren, Mehrgasmessgeräte mit Mikroprozessor, Systemlösungen .</t>
+          <t>Tragbare und stationäre Gasmessgeräte, Gassensoren, Mehrgasmessgeräte mit Mikroprozessor, Systemlösungen.</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -16187,7 +16187,7 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>ASICs, optische und magnetische Encoder-ICs, Interpolatoren, Sensor-ICs sowie Mikrosysteme in Chip-on-Board-Technik und optoBGA/QFN-Gehäusen .</t>
+          <t>ASICs, optische und magnetische Encoder-ICs, Interpolatoren, Sensor-ICs sowie Mikrosysteme in Chip-on-Board-Technik und optoBGA/QFN-Gehäusen.</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -16295,7 +16295,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>Standortseite/Impressum und "about us" im Browser lesen (V für Dillenburg als Fertigungsort für Messmodule, Ausschluss weiterer Werke); IVT-MODular-/IVT-S-Datenblatt auf Gehäuse "vergossen/Potting" lesen; Karriereseite Dillenburg …</t>
+          <t>Standortseite/Impressum und "about us" im Browser lesen; IVT-MODular-/IVT-S-Datenblatt auf Gehäuse "vergossen/Potting" lesen; Karriereseite Dillenburg …</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
@@ -16334,7 +16334,7 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>„Entwicklung, Herstellung, Planung und der Handel mit elektrischen und optischen Steckverbindern und Systemgeräten“ plus Verkabelung .</t>
+          <t>„Entwicklung, Herstellung, Planung und der Handel mit elektrischen und optischen Steckverbindern und Systemgeräten“ plus Verkabelung.</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
@@ -16530,7 +16530,7 @@
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>stationäre Infrarot-Thermometer/Pyrometer (CT-, CTLaser-, CTi-Serien, über eine Million verkauft), Infrarot-Kameras, Handgeräte, Kalibrierquellen, Zubehör und Software .</t>
+          <t>stationäre Infrarot-Thermometer/Pyrometer (CT-, CTLaser-, CTi-Serien, über eine Million verkauft), Infrarot-Kameras, Handgeräte, Kalibrierquellen, Zubehör und Software.</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
@@ -16677,7 +16677,7 @@
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>SAW-Filter und -Resonatoren (Serie), SAW-Sensoren, RFID-Tags, kundenspezifische Entwicklung und SAW-Wafer-Foundry .</t>
+          <t>SAW-Filter und -Resonatoren (Serie), SAW-Sensoren, RFID-Tags, kundenspezifische Entwicklung und SAW-Wafer-Foundry.</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>Hoch- und Niederspannungssicherungen (HH, NH), Sicherungen für Leistungselektronik, Miniatursicherungen, Sicherungshalter und -einsätze .</t>
+          <t>Hoch- und Niederspannungssicherungen (HH, NH), Sicherungen für Leistungselektronik, Miniatursicherungen, Sicherungshalter und -einsätze.</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
@@ -16873,7 +16873,7 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>elektrodynamische Schwingprüfsysteme (Shaker von 9 N bis 300 kN, wassergekühlt), Modalerreger, Wuchtmaschinen, Materialprüfsysteme .</t>
+          <t>elektrodynamische Schwingprüfsysteme (Shaker von 9 N bis 300 kN, wassergekühlt), Modalerreger, Wuchtmaschinen, Materialprüfsysteme.</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -17020,7 +17020,7 @@
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>Drucksensoren (Messzellen, SMD-Sensoren, Transmitter, 5 mbar bis 600 bar), Feuchte-, Temperatur- und Neigungssensoren .</t>
+          <t>Drucksensoren (Messzellen, SMD-Sensoren, Transmitter, 5 mbar bis 600 bar), Feuchte-, Temperatur- und Neigungssensoren.</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
@@ -17118,7 +17118,7 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>individuelle Kunststoffgehäuse vom Prototyp über Kleinserien bis mehrere tausend Stück, auch ohne Werkzeugkosten .</t>
+          <t>individuelle Kunststoffgehäuse vom Prototyp über Kleinserien bis mehrere tausend Stück, auch ohne Werkzeugkosten.</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>Computer- und Netzwerkstecker, IC-Sockel, Stiftleisten/Jumper, Klemmen, Kühlkörper/Strangpressprofile, Netzkabel, Modular-/USB-Kabelkonfektion, Audio-/Video-Kabel .</t>
+          <t>Computer- und Netzwerkstecker, IC-Sockel, Stiftleisten/Jumper, Klemmen, Kühlkörper/Strangpressprofile, Netzkabel, Modular-/USB-Kabelkonfektion, Audio-/Video-Kabel.</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
@@ -17265,7 +17265,7 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>Massendurchflussregler und -messer .</t>
+          <t>Massendurchflussregler und -messer.</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
@@ -17314,7 +17314,7 @@
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>Dienstleistungen rund um elektronische Bauteile: Komponentenmanagement, Logistik, Programmierung, Test, Montage, Langzeitlagerung .</t>
+          <t>Dienstleistungen rund um elektronische Bauteile: Komponentenmanagement, Logistik, Programmierung, Test, Montage, Langzeitlagerung.</t>
         </is>
       </c>
       <c r="G36" s="11" t="inlineStr">
@@ -17363,7 +17363,7 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>externe AC/DC-Netzteile, Wandstecker- und Tischnetzteile 5 bis 76 V, bis 330 W, für Büroelektronik, Set-Top-Boxen, Netzwerk, POS .</t>
+          <t>externe AC/DC-Netzteile, Wandstecker- und Tischnetzteile 5 bis 76 V, bis 330 W, für Büroelektronik, Set-Top-Boxen, Netzwerk, POS.</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
@@ -17510,7 +17510,7 @@
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>Luftbefeuchtung und Verdunstungskühlung: Elektroden-Dampfbefeuchter (Condair EL, RS, RM, GS), Direkt-Raumbefeuchtung, Wasseraufbereitung .</t>
+          <t>Luftbefeuchtung und Verdunstungskühlung: Elektroden-Dampfbefeuchter (Condair EL, RS, RM, GS), Direkt-Raumbefeuchtung, Wasseraufbereitung.</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">
@@ -17559,7 +17559,7 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>EMS: Beschaffung, Bestückung von Leiterplatten, komplexe Baugruppen und Fertiggeräte (Box Build), Kabel/Kabelbäume, Prototyping, Test, ATEX-Zulassung .</t>
+          <t>EMS: Beschaffung, Bestückung von Leiterplatten, komplexe Baugruppen und Fertiggeräte (Box Build), Kabel/Kabelbäume, Prototyping, Test, ATEX-Zulassung.</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
@@ -17657,7 +17657,7 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>EMS-Anbieter für Leiterplattenbestückung, Baugruppenmontage und Systembau .</t>
+          <t>EMS-Anbieter für Leiterplattenbestückung, Baugruppenmontage und Systembau.</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
@@ -17667,7 +17667,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>Wird in Rülzheim durch DBK EMS vergossen, verklebt, gedichtet oder lackiert, und gibt es einen Fertigungsbeleg in Stufe V?</t>
+          <t>Wird in Rülzheim durch DBK EMS vergossen, verklebt, gedichtet oder lackiert, und gibt es einen Fertigungsbeleg belegt?</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
@@ -17706,7 +17706,7 @@
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>Netzteile, Steckernetzteile, LED-Netzteile und LED-Treiber, laut Verzeichnis Fokus auf Vertrieb und Beschaffung .</t>
+          <t>Netzteile, Steckernetzteile, LED-Netzteile und LED-Treiber, laut Verzeichnis Fokus auf Vertrieb und Beschaffung.</t>
         </is>
       </c>
       <c r="G44" s="11" t="inlineStr">
@@ -17853,7 +17853,7 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Kupferlackdraht, Backlackdraht (Selfbonding), voll isolierter Draht und Hochfrequenzlitze .</t>
+          <t>Kupferlackdraht, Backlackdraht (Selfbonding), voll isolierter Draht und Hochfrequenzlitze.</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
@@ -18049,7 +18049,7 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>Thermopile- und pyroelektrische Sensoren, Hochleistungssensoren, gepulste Laser (LiDAR/3D), Fotodioden für Rauchmelder, Photon-Counting-Module, industrielle Blitzlampen .</t>
+          <t>Thermopile- und pyroelektrische Sensoren, Hochleistungssensoren, gepulste Laser (LiDAR/3D), Fotodioden für Rauchmelder, Photon-Counting-Module, industrielle Blitzlampen.</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
@@ -18147,7 +18147,7 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>Mil-Spec-Rundsteckverbinder, Rechtecksteckverbinder, Backshells, Kabelkonfektion .</t>
+          <t>Mil-Spec-Rundsteckverbinder, Rechtecksteckverbinder, Backshells, Kabelkonfektion.</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
@@ -18196,7 +18196,7 @@
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>Ladegeräte, Adapter, Schaltnetzteile von 1 bis 3000 Watt, Transformatoren, OEM/ODM-Fertigung .</t>
+          <t>Ladegeräte, Adapter, Schaltnetzteile von 1 bis 3000 Watt, Transformatoren, OEM/ODM-Fertigung.</t>
         </is>
       </c>
       <c r="G54" s="11" t="inlineStr">
@@ -18245,7 +18245,7 @@
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>Kunststoff-Ventilatoren (Gehäuse PE, Laufrad PP), Zu- und Abluftanlagen, Abluftwäscher, Behälter, Kunststoff-Wärmetauscher, Schalldämpfer .</t>
+          <t>Kunststoff-Ventilatoren (Gehäuse PE, Laufrad PP), Zu- und Abluftanlagen, Abluftwäscher, Behälter, Kunststoff-Wärmetauscher, Schalldämpfer.</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>Lecksuchgeräte (Helium-/Wasserstoff-Schnüffler XL3000flex, Sentrac mit Sensistor-Sensor), Vakuum-Messtechnik, Sensortechnologien .</t>
+          <t>Lecksuchgeräte (Helium-/Wasserstoff-Schnüffler XL3000flex, Sentrac mit Sensistor-Sensor), Vakuum-Messtechnik, Sensortechnologien.</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
@@ -18490,7 +18490,7 @@
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>Elektronikschränke (19-Zoll), Gehäuse, Baugruppenträger, Einschubkassetten, Netzwerkschränke .</t>
+          <t>Elektronikschränke (19-Zoll), Gehäuse, Baugruppenträger, Einschubkassetten, Netzwerkschränke.</t>
         </is>
       </c>
       <c r="G60" s="11" t="inlineStr">
@@ -18500,7 +18500,7 @@
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>Wird in Darmstadt gefertigt oder zugekauft (Fertigungsbeleg)? (b) Gehört die Firma zu einer Gruppe (Regel M)? (c) Werden Gehäuse mit Dichtungen (aufgeschäumt/dosiert) geliefert?</t>
+          <t>Wird in Darmstadt gefertigt oder zugekauft (Fertigungsbeleg)? (b) Gehört die Firma zu einer Gruppe (Konzern?)? (c) Werden Gehäuse mit Dichtungen (aufgeschäumt/dosiert) geliefert?</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
@@ -18588,7 +18588,7 @@
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>Gruppe: DC-/AC-Netzgeräte, elektronische Lasten, Hipot-/Isolationsprüfgeräte .</t>
+          <t>Gruppe: DC-/AC-Netzgeräte, elektronische Lasten, Hipot-/Isolationsprüfgeräte.</t>
         </is>
       </c>
       <c r="G62" s="11" t="inlineStr">
@@ -18735,7 +18735,7 @@
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>Lasersysteme für Leiterplatten-Prototyping und Depaneling, IC-Packaging, Schablonen, Laser Direct Structuring (LDS), Kunststoffschweißen, Solar- und Batteriefertigung .</t>
+          <t>Lasersysteme für Leiterplatten-Prototyping und Depaneling, IC-Packaging, Schablonen, Laser Direct Structuring (LDS), Kunststoffschweißen, Solar- und Batteriefertigung.</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
@@ -18980,7 +18980,7 @@
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>EMS-Dienstleistungen: elektronische und mechatronische Baugruppen, Projektmanagement, Werkzeugbau, Materiallogistik, After-Sales .</t>
+          <t>EMS-Dienstleistungen: elektronische und mechatronische Baugruppen, Projektmanagement, Werkzeugbau, Materiallogistik, After-Sales.</t>
         </is>
       </c>
       <c r="G70" s="11" t="inlineStr">
@@ -19225,7 +19225,7 @@
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>Koordinatenmessgeräte, optische CMM, 3D-Laserscanner, Röntgen-/CT-Systeme, Messmikroskope, Large-Volume-Metrology .</t>
+          <t>Koordinatenmessgeräte, optische CMM, 3D-Laserscanner, Röntgen-/CT-Systeme, Messmikroskope, Large-Volume-Metrology.</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
@@ -19372,7 +19372,7 @@
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>aktive und passive Tastköpfe, Hochspannungstastköpfe, Stromtastköpfe und Stromwandler, Kalibriergeneratoren, Hochspannungsgeräte, Netzteile, Zubehör .</t>
+          <t>aktive und passive Tastköpfe, Hochspannungstastköpfe, Stromtastköpfe und Stromwandler, Kalibriergeneratoren, Hochspannungsgeräte, Netzteile, Zubehör.</t>
         </is>
       </c>
       <c r="G78" s="11" t="inlineStr">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>Antennen: Planarantennen für GSM/GPS, Fahrzeugantennen, Basisstationsantennen, kombinierte Mobilfunk-/Telematikantennen für Autos .</t>
+          <t>Antennen: Planarantennen für GSM/GPS, Fahrzeugantennen, Basisstationsantennen, kombinierte Mobilfunk-/Telematikantennen für Autos.</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
@@ -19617,7 +19617,7 @@
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>EMS-Dienstleistungen: Leiterplattenbestückung, Chip-on-Board, mechanische Montage, Systemintegration, Entwicklung, Prototyping, Prüfmittelentwicklung, Reparatur .</t>
+          <t>EMS-Dienstleistungen: Leiterplattenbestückung, Chip-on-Board, mechanische Montage, Systemintegration, Entwicklung, Prototyping, Prüfmittelentwicklung, Reparatur.</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
@@ -19715,7 +19715,7 @@
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>Drahtlos-LAN-Module, System-on-Modules (Qualcomm, NXP i.MX9), Access Points, Device Server, Print Server .</t>
+          <t>Drahtlos-LAN-Module, System-on-Modules (Qualcomm, NXP i.MX9), Access Points, Device Server, Print Server.</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
@@ -19813,7 +19813,7 @@
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>Leiterplattenbestückung (SMD und THT, Muster bis Serie) bis zu Gerätesystemen, Elektronikfertigung/EMS, ISO 9001 seit 2001 .</t>
+          <t>Leiterplattenbestückung (SMD und THT, Muster bis Serie) bis zu Gerätesystemen, Elektronikfertigung/EMS, ISO 9001 seit 2001.</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
@@ -19911,7 +19911,7 @@
       </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>Fernseher, Digitalradios (DAB+), Satelliten-/Kabel-Receiver, Wallboxen (TECHNIVOLT), Zubehör .</t>
+          <t>Fernseher, Digitalradios (DAB+), Satelliten-/Kabel-Receiver, Wallboxen (TECHNIVOLT), Zubehör.</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
@@ -20009,7 +20009,7 @@
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>Leiterplatten-Steckverbinder (Stiftleisten, Buchsenleisten, D-Sub, IC-Fassungen, Modular Jacks, LED- und Power-Steckverbinder), über 20.000 Varianten .</t>
+          <t>Leiterplatten-Steckverbinder (Stiftleisten, Buchsenleisten, D-Sub, IC-Fassungen, Modular Jacks, LED- und Power-Steckverbinder), über 20.000 Varianten.</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
@@ -20107,7 +20107,7 @@
       </c>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>programmierbare DC-Netzteile 30 W bis 150 kW und AC-Quellen 800 VA bis 480 kVA, Marken Sorensen, Elgar, California Instruments .</t>
+          <t>programmierbare DC-Netzteile 30 W bis 150 kW und AC-Quellen 800 VA bis 480 kVA, Marken Sorensen, Elgar, California Instruments.</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
@@ -20205,7 +20205,7 @@
       </c>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>Verzeichnis beschreibt DETAKTA als Spezialisten für den Handel mit innovativen Isolierstoffen für industrielle Anwendungen .</t>
+          <t>Verzeichnis beschreibt DETAKTA als Spezialisten für den Handel mit innovativen Isolierstoffen für industrielle Anwendungen.</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr">
@@ -20548,7 +20548,7 @@
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>Wire and Cable für Automotive, Kabelkonfektion für Medizin, Flexible Flat Cable für Consumer/Automotive .</t>
+          <t>Wire and Cable für Automotive, Kabelkonfektion für Medizin, Flexible Flat Cable für Consumer/Automotive.</t>
         </is>
       </c>
       <c r="G102" s="11" t="inlineStr">
@@ -20646,7 +20646,7 @@
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>Gruppe entwickelt und fertigt elektromechanische Relais (Automotive, General Purpose, Industrial, Zubehör), Hochstrom-/Hochvolt-Relais für Solar und E-Mobility .</t>
+          <t>Gruppe entwickelt und fertigt elektromechanische Relais (Automotive, General Purpose, Industrial, Zubehör), Hochstrom-/Hochvolt-Relais für Solar und E-Mobility.</t>
         </is>
       </c>
       <c r="G104" s="11" t="inlineStr">
@@ -20773,7 +20773,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -20820,7 +20820,7 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -20867,7 +20867,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -20914,7 +20914,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -20961,7 +20961,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -21018,7 +21018,7 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Angebot: Testwafer 50 bis 300 mm Silizium, Blanket-/Pattern-Wafer-Service, Verbrauchsmaterial, Vakuumkomponenten .</t>
+          <t>Angebot: Testwafer 50 bis 300 mm Silizium, Blanket-/Pattern-Wafer-Service, Verbrauchsmaterial, Vakuumkomponenten.</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
@@ -21055,7 +21055,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -21102,7 +21102,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -21149,7 +21149,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -21196,7 +21196,7 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -21243,7 +21243,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -21290,7 +21290,7 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -21337,7 +21337,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -21384,7 +21384,7 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -21431,7 +21431,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -21441,7 +21441,7 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>Altium Designer, Software für PCB-Design .</t>
+          <t>Altium Designer, Software für PCB-Design.</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -21478,7 +21478,7 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -21488,7 +21488,7 @@
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>Altium Designer, Software für PCB-Design .</t>
+          <t>Altium Designer, Software für PCB-Design.</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
@@ -21525,7 +21525,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -21619,7 +21619,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -21666,7 +21666,7 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -21713,7 +21713,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -21760,7 +21760,7 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -21807,7 +21807,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -21817,7 +21817,7 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>Spezialchemie und Anlagen für Galvanik/Elektrolytische Metallabscheidung .</t>
+          <t>Spezialchemie und Anlagen für Galvanik/Elektrolytische Metallabscheidung.</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
@@ -21864,7 +21864,7 @@
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>nichts, Vertrieb von Verbindungs-, passiven, elektromechanischen Bauteilen, Stromversorgungen, Batterien, Funk und Sensoren .</t>
+          <t>nichts, Vertrieb von Verbindungs-, passiven, elektromechanischen Bauteilen, Stromversorgungen, Batterien, Funk und Sensoren.</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
@@ -21901,7 +21901,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -21911,7 +21911,7 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>nichts, Halbleiter-Vertrieb .</t>
+          <t>nichts, Halbleiter-Vertrieb.</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
@@ -21921,7 +21921,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>wie Nr. 62 (E2-Beleg in Stufe V); Nr. 62 und 63 gemeinsam in einem Durchgang erledigen.</t>
+          <t>wie Nr. 62 (E2-Beleg belegt); Nr. 62 und 63 gemeinsam in einem Durchgang erledigen.</t>
         </is>
       </c>
       <c r="I29" s="8" t="inlineStr">
@@ -21948,7 +21948,7 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
@@ -21995,7 +21995,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -22042,7 +22042,7 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
@@ -22052,7 +22052,7 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>USB-Programmiergeräte für Mikrocontroller/EPROM (BX-Serie, Batego), Hersteller und zugleich Händler von Mess- und Löttechnik .</t>
+          <t>USB-Programmiergeräte für Mikrocontroller/EPROM (BX-Serie, Batego), Hersteller und zugleich Händler von Mess- und Löttechnik.</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
@@ -22089,7 +22089,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -22136,7 +22136,7 @@
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
@@ -22183,7 +22183,7 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -22230,7 +22230,7 @@
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
@@ -22277,7 +22277,7 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -22324,7 +22324,7 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
@@ -22371,7 +22371,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -22381,7 +22381,7 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>laut Stellenanzeige-Text individuelle Montagelinien, Produktions-Software und Arbeitsplatzsysteme für Elektrolabore und Ausbildungsstätten .</t>
+          <t>laut Stellenanzeige-Text individuelle Montagelinien, Produktions-Software und Arbeitsplatzsysteme für Elektrolabore und Ausbildungsstätten.</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
@@ -22418,7 +22418,7 @@
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
@@ -22465,7 +22465,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -22512,7 +22512,7 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
@@ -22522,7 +22522,7 @@
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>Abfüllung von Chlorwasserstoff-(HCl-)Gas, Kunden vor allem Chemie und Pharma, Zielmarkt Halbleiter/Elektronik als Gaslieferant .</t>
+          <t>Abfüllung von Chlorwasserstoff-(HCl-)Gas, Kunden vor allem Chemie und Pharma, Zielmarkt Halbleiter/Elektronik als Gaslieferant.</t>
         </is>
       </c>
       <c r="G42" s="11" t="inlineStr">
@@ -22559,7 +22559,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Federkontaktstifte (Pogo-Pins), Test-Sockel (QFN, QFP, BGA), Koaxial- und Fine-Pitch-Prüfstifte, Hochstrom-Steckverbinder .</t>
+          <t>Federkontaktstifte (Pogo-Pins), Test-Sockel (QFN, QFP, BGA), Koaxial- und Fine-Pitch-Prüfstifte, Hochstrom-Steckverbinder.</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
@@ -22606,7 +22606,7 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
@@ -22653,7 +22653,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -22700,7 +22700,7 @@
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
@@ -22747,7 +22747,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -22794,7 +22794,7 @@
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
@@ -22804,7 +22804,7 @@
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>unbekannt .</t>
+          <t>unbekannt.</t>
         </is>
       </c>
       <c r="G48" s="11" t="inlineStr">
@@ -22841,7 +22841,7 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -22888,7 +22888,7 @@
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
@@ -22935,7 +22935,7 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -22982,7 +22982,7 @@
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
@@ -23029,7 +23029,7 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -23076,7 +23076,7 @@
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
@@ -23123,7 +23123,7 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -23133,7 +23133,7 @@
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>Fachmedien (Markt&amp;Technik, Elektronik, elektroniknet.de) und Veranstaltungen, Teil von NürnbergMesse laut einem Verzeichnis .</t>
+          <t>Fachmedien (Markt&amp;Technik, Elektronik, elektroniknet.de) und Veranstaltungen, Teil von NürnbergMesse laut einem Verzeichnis.</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
@@ -23170,7 +23170,7 @@
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
-          <t>Unabhängiger Distributor elektronischer Bauteile (CAS), früher 'Zillner Elektronik' .</t>
+          <t>Unabhängiger Distributor elektronischer Bauteile (CAS), früher 'Zillner Elektronik'.</t>
         </is>
       </c>
       <c r="G56" s="11" t="inlineStr">
@@ -23217,7 +23217,7 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>Vertrieb von Komponenten (HF, Transceiver, Elektromechanik, Quarze, Antennen/GNSS) verschiedener Hersteller .</t>
+          <t>Vertrieb von Komponenten (HF, Transceiver, Elektromechanik, Quarze, Antennen/GNSS) verschiedener Hersteller.</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
@@ -23264,7 +23264,7 @@
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
@@ -23274,7 +23274,7 @@
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>Software (COMSOL Multiphysics, physikbasierte Simulation) .</t>
+          <t>Software (COMSOL Multiphysics, physikbasierte Simulation).</t>
         </is>
       </c>
       <c r="G58" s="11" t="inlineStr">
@@ -23311,7 +23311,7 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -23358,7 +23358,7 @@
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
@@ -23405,7 +23405,7 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -23452,7 +23452,7 @@
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
@@ -23462,7 +23462,7 @@
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>Zeitkritische Kurierlogistik (Automotive- und Halbleiterlieferungen) .</t>
+          <t>Zeitkritische Kurierlogistik (Automotive- und Halbleiterlieferungen).</t>
         </is>
       </c>
       <c r="G62" s="11" t="inlineStr">
@@ -23499,7 +23499,7 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
@@ -23593,7 +23593,7 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -23640,7 +23640,7 @@
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
@@ -23650,7 +23650,7 @@
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>ALPHAPLAN ERP, "in-house development" der CVS Ingenieurgesellschaft, für Handel und mittelständische Fertiger .</t>
+          <t>ALPHAPLAN ERP, "in-house development" der CVS Ingenieurgesellschaft, für Handel und mittelständische Fertiger.</t>
         </is>
       </c>
       <c r="G66" s="11" t="inlineStr">
@@ -23687,7 +23687,7 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -23734,7 +23734,7 @@
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
@@ -23781,7 +23781,7 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
@@ -23838,7 +23838,7 @@
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>Embedded-Module, Single-Board-Computer, M2M-/Funkmodule, Router/Gateways, Software (Fernwartung, Cloud) laut Ausstellerprofilen .</t>
+          <t>Embedded-Module, Single-Board-Computer, M2M-/Funkmodule, Router/Gateways, Software (Fernwartung, Cloud) laut Ausstellerprofilen.</t>
         </is>
       </c>
       <c r="G70" s="11" t="inlineStr">
@@ -23875,7 +23875,7 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -23922,7 +23922,7 @@
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
@@ -23932,7 +23932,7 @@
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>Vertrieb des DMC-Portfolios und Partnermarken (Ideal Industries, Astro Tool, Compaero), kundenspezifische Werkzeuge, Kalibrierung, Wartung, Reparatur .</t>
+          <t>Vertrieb des DMC-Portfolios und Partnermarken (Ideal Industries, Astro Tool, Compaero), kundenspezifische Werkzeuge, Kalibrierung, Wartung, Reparatur.</t>
         </is>
       </c>
       <c r="G72" s="11" t="inlineStr">
@@ -23969,7 +23969,7 @@
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -24016,7 +24016,7 @@
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
@@ -24063,7 +24063,7 @@
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -24120,7 +24120,7 @@
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>Mobilfunkmodule (LTE/5G) für IoT und Automotive, WLAN-/Bluetooth-Module, Antennen, SoC-ICs .</t>
+          <t>Mobilfunkmodule (LTE/5G) für IoT und Automotive, WLAN-/Bluetooth-Module, Antennen, SoC-ICs.</t>
         </is>
       </c>
       <c r="G76" s="11" t="inlineStr">
@@ -24157,7 +24157,7 @@
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -24204,7 +24204,7 @@
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
@@ -24214,7 +24214,7 @@
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>Steckverbinder und Kabelkonfektionen, Fertigung in Taiwan/China, Vertrieb an deutsche Industrie-OEMs .</t>
+          <t>Steckverbinder und Kabelkonfektionen, Fertigung in Taiwan/China, Vertrieb an deutsche Industrie-OEMs.</t>
         </is>
       </c>
       <c r="G78" s="11" t="inlineStr">
@@ -24251,7 +24251,7 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -24298,7 +24298,7 @@
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
@@ -24308,7 +24308,7 @@
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>Fachzeitschrift ELEKTRONIKPRAXIS, Webportal und Events der Vogel-Gruppe .</t>
+          <t>Fachzeitschrift ELEKTRONIKPRAXIS, Webportal und Events der Vogel-Gruppe.</t>
         </is>
       </c>
       <c r="G80" s="11" t="inlineStr">
@@ -24345,7 +24345,7 @@
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -24355,7 +24355,7 @@
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>Distribution elektronischer Komponenten aus China an europäische Elektronikfirmen: Leiterplatten (starr, flex, Starrflex, IMS) und Displays (LCD, TFT, OLED) .</t>
+          <t>Distribution elektronischer Komponenten aus China an europäische Elektronikfirmen: Leiterplatten (starr, flex, Starrflex, IMS) und Displays (LCD, TFT, OLED).</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
@@ -24392,7 +24392,7 @@
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
@@ -24439,7 +24439,7 @@
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -24486,7 +24486,7 @@
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
@@ -24533,7 +24533,7 @@
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -24580,7 +24580,7 @@
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>Technische Kunststoff-Halbzeuge (Extrusion, Guss), Compounds, Spritzguss- und Zerspanteile, medizinische Kunststoffteile (Reinraum), Isolierstege .</t>
+          <t>Technische Kunststoff-Halbzeuge (Extrusion, Guss), Compounds, Spritzguss- und Zerspanteile, medizinische Kunststoffteile (Reinraum), Isolierstege.</t>
         </is>
       </c>
       <c r="G86" s="11" t="inlineStr">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -24637,7 +24637,7 @@
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>Leiterplatten in Standardtechnologie: einseitig, doppelseitig, starre Multilayer, Power- und IMS-Leiterplatten (Prototypen bis Großserie), ISO 9001/14001/50001 .</t>
+          <t>Leiterplatten in Standardtechnologie: einseitig, doppelseitig, starre Multilayer, Power- und IMS-Leiterplatten (Prototypen bis Großserie), ISO 9001/14001/50001.</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
@@ -24674,7 +24674,7 @@
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
@@ -24721,7 +24721,7 @@
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -24731,7 +24731,7 @@
       </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>Kunststoffverarbeiter: SMD-Verpackungsmaterial für die Elektronik (Gurtband/Carrier Tape, Reels, Deckband, Stangenmagazine, Tubes) sowie Profile und Formteile .</t>
+          <t>Kunststoffverarbeiter: SMD-Verpackungsmaterial für die Elektronik (Gurtband/Carrier Tape, Reels, Deckband, Stangenmagazine, Tubes) sowie Profile und Formteile.</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
@@ -24768,7 +24768,7 @@
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
@@ -24815,7 +24815,7 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -24862,7 +24862,7 @@
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
@@ -24909,7 +24909,7 @@
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -24956,7 +24956,7 @@
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
@@ -25003,7 +25003,7 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -25050,7 +25050,7 @@
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
@@ -25097,7 +25097,7 @@
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
@@ -25154,7 +25154,7 @@
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>nichts, Distributor von elektronischen Bauelementen .</t>
+          <t>nichts, Distributor von elektronischen Bauelementen.</t>
         </is>
       </c>
       <c r="G98" s="11" t="inlineStr">
@@ -25191,7 +25191,7 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -25238,7 +25238,7 @@
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
@@ -25285,7 +25285,7 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -25332,7 +25332,7 @@
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
@@ -25379,7 +25379,7 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -25389,7 +25389,7 @@
       </c>
       <c r="F103" s="8" t="inlineStr">
         <is>
-          <t>Leiterplatten werden über "über 25 zertifizierte Fertigungsstätten" (Partnerfabriken China/Taiwan/Europa) bezogen und vertrieben .</t>
+          <t>Leiterplatten werden über "über 25 zertifizierte Fertigungsstätten" (Partnerfabriken China/Taiwan/Europa) bezogen und vertrieben.</t>
         </is>
       </c>
       <c r="G103" s="8" t="inlineStr">
@@ -25426,7 +25426,7 @@
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
@@ -25436,7 +25436,7 @@
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>kundenspezifische Messing-Präzisionsdrehteile in Großserie für Elektrotechnik, Automotive, Kommunikation, Sanitär/Hydraulik .</t>
+          <t>kundenspezifische Messing-Präzisionsdrehteile in Großserie für Elektrotechnik, Automotive, Kommunikation, Sanitär/Hydraulik.</t>
         </is>
       </c>
       <c r="G104" s="11" t="inlineStr">
@@ -25473,7 +25473,7 @@
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>Rohrverschraubungen, Instrumentierungsventile, Hochdruckventile, Probenahmesysteme, Manifolds, Filter, Druckregler .</t>
+          <t>Rohrverschraubungen, Instrumentierungsventile, Hochdruckventile, Probenahmesysteme, Manifolds, Filter, Druckregler.</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
@@ -25520,7 +25520,7 @@
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
@@ -25567,7 +25567,7 @@
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -25577,7 +25577,7 @@
       </c>
       <c r="F107" s="8" t="inlineStr">
         <is>
-          <t>SMT-Equipment: Bestückungsautomaten (placeALL-Reihe), Dosiersysteme (dispenseALL420 mit integrierten ViscoTec preeflow eco-PEN600), Schablonendrucker, Reflow-Öfen .</t>
+          <t>SMT-Equipment: Bestückungsautomaten (placeALL-Reihe), Dosiersysteme (dispenseALL420 mit integrierten ViscoTec preeflow eco-PEN600), Schablonendrucker, Reflow-Öfen.</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr">
@@ -25614,7 +25614,7 @@
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
@@ -25661,7 +25661,7 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -25671,7 +25671,7 @@
       </c>
       <c r="F109" s="8" t="inlineStr">
         <is>
-          <t>Motoröle, Getriebeöle, Hydrauliköle, Industrieschmierstoffe, Metallbearbeitungsflüssigkeiten, Reiniger/Korrosionsschutz .</t>
+          <t>Motoröle, Getriebeöle, Hydrauliköle, Industrieschmierstoffe, Metallbearbeitungsflüssigkeiten, Reiniger/Korrosionsschutz.</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr">
@@ -25708,7 +25708,7 @@
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
@@ -25755,7 +25755,7 @@
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -25765,7 +25765,7 @@
       </c>
       <c r="F111" s="8" t="inlineStr">
         <is>
-          <t>unbekannt .</t>
+          <t>unbekannt.</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr">
@@ -25802,7 +25802,7 @@
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
@@ -25812,7 +25812,7 @@
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>ERP-Software TimeLine für mittelständische Industrieunternehmen .</t>
+          <t>ERP-Software TimeLine für mittelständische Industrieunternehmen.</t>
         </is>
       </c>
       <c r="G112" s="11" t="inlineStr">
@@ -25849,7 +25849,7 @@
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -25859,7 +25859,7 @@
       </c>
       <c r="F113" s="8" t="inlineStr">
         <is>
-          <t>GF Piping Systems: Rohre, Fittings, Ventile, Durchflussmessgeräte und Sensorik/Messtechnik (Signet, Sitz Irwindale USA) .</t>
+          <t>GF Piping Systems: Rohre, Fittings, Ventile, Durchflussmessgeräte und Sensorik/Messtechnik (Signet, Sitz Irwindale USA).</t>
         </is>
       </c>
       <c r="G113" s="8" t="inlineStr">
@@ -25896,7 +25896,7 @@
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
@@ -25906,7 +25906,7 @@
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
-          <t>Galvanische Oberflächenbearbeitung und Beschichtung von Metallen für Automotive, E-Mobility, Medizintechnik, Telekommunikation .</t>
+          <t>Galvanische Oberflächenbearbeitung und Beschichtung von Metallen für Automotive, E-Mobility, Medizintechnik, Telekommunikation.</t>
         </is>
       </c>
       <c r="G114" s="11" t="inlineStr">
@@ -25943,7 +25943,7 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="F115" s="8" t="inlineStr">
         <is>
-          <t>Fabless-Hersteller von SPI-NOR/NAND-Flash, Mikrocontrollern und Sensorprodukten .</t>
+          <t>Fabless-Hersteller von SPI-NOR/NAND-Flash, Mikrocontrollern und Sensorprodukten.</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr">
@@ -25990,7 +25990,7 @@
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
@@ -26000,7 +26000,7 @@
       </c>
       <c r="F116" s="11" t="inlineStr">
         <is>
-          <t>Spezialist für den Vertrieb elektronischer Bauelemente (Distribution), gegründet 1980, etwa 200 Mitarbeitende .</t>
+          <t>Spezialist für den Vertrieb elektronischer Bauelemente (Distribution), gegründet 1980, etwa 200 Mitarbeitende.</t>
         </is>
       </c>
       <c r="G116" s="11" t="inlineStr">
@@ -26037,7 +26037,7 @@
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="F117" s="8" t="inlineStr">
         <is>
-          <t>Laut Dealroom-Snippet (UK-Firma, Beziehung zur Siegener GmbH nicht belegt) "flexible laminates and insulation" .</t>
+          <t>Laut Dealroom-Snippet (UK-Firma, Beziehung zur Siegener GmbH nicht belegt) "flexible laminates and insulation".</t>
         </is>
       </c>
       <c r="G117" s="8" t="inlineStr">
@@ -26084,7 +26084,7 @@
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
@@ -26094,7 +26094,7 @@
       </c>
       <c r="F118" s="11" t="inlineStr">
         <is>
-          <t>Spezialgläser, dotierte Lampenrohre, Quarzglas-Hülsen/-Rohre/-Platten für Wasseraufbereitung, Filtration, Sterilisation, Laserschutzscheiben .</t>
+          <t>Spezialgläser, dotierte Lampenrohre, Quarzglas-Hülsen/-Rohre/-Platten für Wasseraufbereitung, Filtration, Sterilisation, Laserschutzscheiben.</t>
         </is>
       </c>
       <c r="G118" s="11" t="inlineStr">
@@ -26131,7 +26131,7 @@
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -26178,7 +26178,7 @@
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
@@ -26188,7 +26188,7 @@
       </c>
       <c r="F120" s="11" t="inlineStr">
         <is>
-          <t>Die deutsche GmbH vertreibt Photomultiplier, CCD/CMOS-Detektoren, Photo-ICs, Lichtquellen, Opto-Halbleiter .</t>
+          <t>Die deutsche GmbH vertreibt Photomultiplier, CCD/CMOS-Detektoren, Photo-ICs, Lichtquellen, Opto-Halbleiter.</t>
         </is>
       </c>
       <c r="G120" s="11" t="inlineStr">
@@ -26225,7 +26225,7 @@
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -26235,7 +26235,7 @@
       </c>
       <c r="F121" s="8" t="inlineStr">
         <is>
-          <t>Distributor von Steckverbindern, Relais, Sensoren, Schaltern, Thermal Management und Schutzbauteilen .</t>
+          <t>Distributor von Steckverbindern, Relais, Sensoren, Schaltern, Thermal Management und Schutzbauteilen.</t>
         </is>
       </c>
       <c r="G121" s="8" t="inlineStr">
@@ -26272,7 +26272,7 @@
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
@@ -26282,7 +26282,7 @@
       </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
-          <t>Metallbauteile im patentierten Metall-Pulver-Auftrag-Verfahren (MPA, thermisches Spritzen mit 5-Achs-Bearbeitung) als Lohn-/Entwicklungsleistung .</t>
+          <t>Metallbauteile im patentierten Metall-Pulver-Auftrag-Verfahren (MPA, thermisches Spritzen mit 5-Achs-Bearbeitung) als Lohn-/Entwicklungsleistung.</t>
         </is>
       </c>
       <c r="G122" s="11" t="inlineStr">
@@ -26319,7 +26319,7 @@
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -26366,7 +26366,7 @@
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
@@ -26413,7 +26413,7 @@
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -26460,7 +26460,7 @@
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
@@ -26507,7 +26507,7 @@
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -26554,7 +26554,7 @@
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr">
@@ -26601,7 +26601,7 @@
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -26648,7 +26648,7 @@
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
@@ -26695,7 +26695,7 @@
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -26742,7 +26742,7 @@
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
@@ -26789,7 +26789,7 @@
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -26799,7 +26799,7 @@
       </c>
       <c r="F133" s="8" t="inlineStr">
         <is>
-          <t>Die Mutter entwickelt und fertigt Board-to-Board-, FPC/FFC- und Floating-Steckverbinder für Automotive (Radar, Kamera, EV-Antriebsstrang) und Industrie .</t>
+          <t>Die Mutter entwickelt und fertigt Board-to-Board-, FPC/FFC- und Floating-Steckverbinder für Automotive (Radar, Kamera, EV-Antriebsstrang) und Industrie.</t>
         </is>
       </c>
       <c r="G133" s="8" t="inlineStr">
@@ -26836,7 +26836,7 @@
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr">
@@ -26883,7 +26883,7 @@
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -26893,7 +26893,7 @@
       </c>
       <c r="F135" s="8" t="inlineStr">
         <is>
-          <t>Verkauft Elektronenmikroskope (TEM, SEM, FIB) und Analysesysteme der Mutter .</t>
+          <t>Verkauft Elektronenmikroskope (TEM, SEM, FIB) und Analysesysteme der Mutter.</t>
         </is>
       </c>
       <c r="G135" s="8" t="inlineStr">
@@ -26930,7 +26930,7 @@
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
@@ -26977,7 +26977,7 @@
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -27024,7 +27024,7 @@
       </c>
       <c r="D138" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="F138" s="11" t="inlineStr">
         <is>
-          <t>Leiterplatten (PCB), Bestückung, 3D-Druck, CNC, Blechteile über die Gruppe .</t>
+          <t>Leiterplatten (PCB), Bestückung, 3D-Druck, CNC, Blechteile über die Gruppe.</t>
         </is>
       </c>
       <c r="G138" s="11" t="inlineStr">
@@ -27071,7 +27071,7 @@
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -27118,7 +27118,7 @@
       </c>
       <c r="D140" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E140" s="11" t="inlineStr">
@@ -27165,7 +27165,7 @@
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -27212,7 +27212,7 @@
       </c>
       <c r="D142" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E142" s="11" t="inlineStr">
@@ -27259,7 +27259,7 @@
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -27269,7 +27269,7 @@
       </c>
       <c r="F143" s="8" t="inlineStr">
         <is>
-          <t>trockene Mehrstufen-Rootspumpen (NeoDry-Serie, 7 bis 300 m³/h) des japanischen Herstellers .</t>
+          <t>trockene Mehrstufen-Rootspumpen (NeoDry-Serie, 7 bis 300 m³/h) des japanischen Herstellers.</t>
         </is>
       </c>
       <c r="G143" s="8" t="inlineStr">
@@ -27306,7 +27306,7 @@
       </c>
       <c r="D144" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E144" s="11" t="inlineStr">
@@ -27316,7 +27316,7 @@
       </c>
       <c r="F144" s="11" t="inlineStr">
         <is>
-          <t>Leiterplatten (PCB), gegründet 1965 als Christian Enzmann GmbH, 2018 umbenannt .</t>
+          <t>Leiterplatten (PCB), gegründet 1965 als Christian Enzmann GmbH, 2018 umbenannt.</t>
         </is>
       </c>
       <c r="G144" s="11" t="inlineStr">
@@ -27353,7 +27353,7 @@
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -27400,7 +27400,7 @@
       </c>
       <c r="D146" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E146" s="11" t="inlineStr">
@@ -27410,7 +27410,7 @@
       </c>
       <c r="F146" s="11" t="inlineStr">
         <is>
-          <t>Flash-Speicher, SSDs, Retail-Produkte .</t>
+          <t>Flash-Speicher, SSDs, Retail-Produkte.</t>
         </is>
       </c>
       <c r="G146" s="11" t="inlineStr">
@@ -27447,7 +27447,7 @@
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -27494,7 +27494,7 @@
       </c>
       <c r="D148" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E148" s="11" t="inlineStr">
@@ -27504,7 +27504,7 @@
       </c>
       <c r="F148" s="11" t="inlineStr">
         <is>
-          <t>Verkauf von Widerständen (Dickschicht, Shunt/Strommess, Hochspannung, Dünnschicht, Überspannungsschutz) für Automotive, Industrie, Medizin, Energie .</t>
+          <t>Verkauf von Widerständen (Dickschicht, Shunt/Strommess, Hochspannung, Dünnschicht, Überspannungsschutz) für Automotive, Industrie, Medizin, Energie.</t>
         </is>
       </c>
       <c r="G148" s="11" t="inlineStr">
@@ -27541,7 +27541,7 @@
       </c>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -27551,7 +27551,7 @@
       </c>
       <c r="F149" s="8" t="inlineStr">
         <is>
-          <t>Leiterplatten: HDI, Multilayer, Hochfrequenz, Dickkupfer, semiflexibel, starr-flexibel .</t>
+          <t>Leiterplatten: HDI, Multilayer, Hochfrequenz, Dickkupfer, semiflexibel, starr-flexibel.</t>
         </is>
       </c>
       <c r="G149" s="8" t="inlineStr">
@@ -27561,7 +27561,7 @@
       </c>
       <c r="H149" s="8" t="inlineStr">
         <is>
-          <t>Fertigung Gornsdorf mit aktueller Primärquelle (V) belegen und klären, ob Verklebung/Dichtung/Verguss (z. B. Embedding-Leiterplatten, Flex-Verstärkungen) vorkommt.</t>
+          <t>Fertigung Gornsdorf mit aktueller Primärquelle belegen und klären, ob Verklebung/Dichtung/Verguss (z. B. Embedding-Leiterplatten, Flex-Verstärkungen) vorkommt.</t>
         </is>
       </c>
       <c r="I149" s="8" t="inlineStr">
@@ -27588,7 +27588,7 @@
       </c>
       <c r="D150" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E150" s="11" t="inlineStr">
@@ -27598,7 +27598,7 @@
       </c>
       <c r="F150" s="11" t="inlineStr">
         <is>
-          <t>Leiterplatten (Prototypen bis 40-Lagen-Multilayer, starr-flex) .</t>
+          <t>Leiterplatten (Prototypen bis 40-Lagen-Multilayer, starr-flex).</t>
         </is>
       </c>
       <c r="G150" s="11" t="inlineStr">
@@ -27635,7 +27635,7 @@
       </c>
       <c r="D151" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
@@ -27682,7 +27682,7 @@
       </c>
       <c r="D152" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
@@ -27729,7 +27729,7 @@
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -27739,7 +27739,7 @@
       </c>
       <c r="F153" s="8" t="inlineStr">
         <is>
-          <t>Dreh- und Frästeile (Metall) als Zulieferer, laut Pressemeldung der IL Metronic Sensortechnik GmbH (Ilmenau) 2024 als Partner für "gedrehte und gefräste Teile" gewonnen .</t>
+          <t>Dreh- und Frästeile (Metall) als Zulieferer, laut Pressemeldung der IL Metronic Sensortechnik GmbH (Ilmenau) 2024 als Partner für "gedrehte und gefräste Teile" gewonnen.</t>
         </is>
       </c>
       <c r="G153" s="8" t="inlineStr">
@@ -27776,7 +27776,7 @@
       </c>
       <c r="D154" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
@@ -27823,7 +27823,7 @@
       </c>
       <c r="D155" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
@@ -27833,7 +27833,7 @@
       </c>
       <c r="F155" s="8" t="inlineStr">
         <is>
-          <t>B2B-Software für die Elektronik-Lieferkette (Angebots-/BOM-Tools für EMS, Bauteilbeschaffung) .</t>
+          <t>B2B-Software für die Elektronik-Lieferkette (Angebots-/BOM-Tools für EMS, Bauteilbeschaffung).</t>
         </is>
       </c>
       <c r="G155" s="8" t="inlineStr">
@@ -27870,7 +27870,7 @@
       </c>
       <c r="D156" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E156" s="11" t="inlineStr">
@@ -27917,7 +27917,7 @@
       </c>
       <c r="D157" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -27964,7 +27964,7 @@
       </c>
       <c r="D158" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E158" s="11" t="inlineStr">
@@ -28011,7 +28011,7 @@
       </c>
       <c r="D159" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -28058,7 +28058,7 @@
       </c>
       <c r="D160" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E160" s="11" t="inlineStr">
@@ -28105,7 +28105,7 @@
       </c>
       <c r="D161" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -28115,7 +28115,7 @@
       </c>
       <c r="F161" s="8" t="inlineStr">
         <is>
-          <t>Distributor für Speicher-ICs, Module und Flash-Produkte .</t>
+          <t>Distributor für Speicher-ICs, Module und Flash-Produkte.</t>
         </is>
       </c>
       <c r="G161" s="8" t="inlineStr">
@@ -28152,7 +28152,7 @@
       </c>
       <c r="D162" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E162" s="11" t="inlineStr">
@@ -28199,7 +28199,7 @@
       </c>
       <c r="D163" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -28246,7 +28246,7 @@
       </c>
       <c r="D164" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E164" s="11" t="inlineStr">
@@ -28293,7 +28293,7 @@
       </c>
       <c r="D165" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -28340,7 +28340,7 @@
       </c>
       <c r="D166" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E166" s="11" t="inlineStr">
@@ -28387,7 +28387,7 @@
       </c>
       <c r="D167" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="D168" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E168" s="11" t="inlineStr">
@@ -28481,7 +28481,7 @@
       </c>
       <c r="D169" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
@@ -28575,7 +28575,7 @@
       </c>
       <c r="D171" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
@@ -28622,7 +28622,7 @@
       </c>
       <c r="D172" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E172" s="11" t="inlineStr">
@@ -28632,7 +28632,7 @@
       </c>
       <c r="F172" s="11" t="inlineStr">
         <is>
-          <t>Multek ist ein Leiterplattenhersteller, Tochter von Flex/Flextronics .</t>
+          <t>Multek ist ein Leiterplattenhersteller, Tochter von Flex/Flextronics.</t>
         </is>
       </c>
       <c r="G172" s="11" t="inlineStr">
@@ -28669,7 +28669,7 @@
       </c>
       <c r="D173" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
@@ -28716,7 +28716,7 @@
       </c>
       <c r="D174" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E174" s="11" t="inlineStr">
@@ -28763,7 +28763,7 @@
       </c>
       <c r="D175" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
@@ -28810,7 +28810,7 @@
       </c>
       <c r="D176" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E176" s="11" t="inlineStr">
@@ -28857,7 +28857,7 @@
       </c>
       <c r="D177" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
@@ -28904,7 +28904,7 @@
       </c>
       <c r="D178" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E178" s="11" t="inlineStr">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="F178" s="11" t="inlineStr">
         <is>
-          <t>Vertrieb und Service von Nikon-Photolithografiesystemen (Stepper, KrF/ArF-Scanner, Inspektion) in Europa .</t>
+          <t>Vertrieb und Service von Nikon-Photolithografiesystemen (Stepper, KrF/ArF-Scanner, Inspektion) in Europa.</t>
         </is>
       </c>
       <c r="G178" s="11" t="inlineStr">
@@ -28951,7 +28951,7 @@
       </c>
       <c r="D179" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
@@ -28961,7 +28961,7 @@
       </c>
       <c r="F179" s="8" t="inlineStr">
         <is>
-          <t>Automatische und manuelle Röntgeninspektion (AXI/MXI, X#-, XS-, XCT-Serie) für Elektronik und zerstörungsfreie Prüfung .</t>
+          <t>Automatische und manuelle Röntgeninspektion (AXI/MXI, X#-, XS-, XCT-Serie) für Elektronik und zerstörungsfreie Prüfung.</t>
         </is>
       </c>
       <c r="G179" s="8" t="inlineStr">
@@ -28998,7 +28998,7 @@
       </c>
       <c r="D180" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E180" s="11" t="inlineStr">
@@ -29045,7 +29045,7 @@
       </c>
       <c r="D181" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -29092,7 +29092,7 @@
       </c>
       <c r="D182" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E182" s="11" t="inlineStr">
@@ -29139,7 +29139,7 @@
       </c>
       <c r="D183" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
@@ -29186,7 +29186,7 @@
       </c>
       <c r="D184" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E184" s="11" t="inlineStr">
@@ -29233,7 +29233,7 @@
       </c>
       <c r="D185" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
@@ -29243,7 +29243,7 @@
       </c>
       <c r="F185" s="8" t="inlineStr">
         <is>
-          <t>Werkerassistenzsystem "Der Schlaue Klaus" (industrielle Bildverarbeitung plus Datenbank) für die manuelle Fertigung .</t>
+          <t>Werkerassistenzsystem "Der Schlaue Klaus" (industrielle Bildverarbeitung plus Datenbank) für die manuelle Fertigung.</t>
         </is>
       </c>
       <c r="G185" s="8" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="D186" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E186" s="11" t="inlineStr">
@@ -29327,7 +29327,7 @@
       </c>
       <c r="D187" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
@@ -29337,7 +29337,7 @@
       </c>
       <c r="F187" s="8" t="inlineStr">
         <is>
-          <t>Konzern: Hochtechnologie-Werkzeuge (AFM, NMR, Elektronenmikroskop-Nanoanalyse, Raman, Plasmaätzen/-abscheidung) .</t>
+          <t>Konzern: Hochtechnologie-Werkzeuge (AFM, NMR, Elektronenmikroskop-Nanoanalyse, Raman, Plasmaätzen/-abscheidung).</t>
         </is>
       </c>
       <c r="G187" s="8" t="inlineStr">
@@ -29374,7 +29374,7 @@
       </c>
       <c r="D188" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E188" s="11" t="inlineStr">
@@ -29384,7 +29384,7 @@
       </c>
       <c r="F188" s="11" t="inlineStr">
         <is>
-          <t>Verzeichnis: "PCB partner" mit "network of high-tech production partners", 11 bis 50 Mitarbeiter, gegründet 1989 .</t>
+          <t>Verzeichnis: "PCB partner" mit "network of high-tech production partners", 11 bis 50 Mitarbeiter, gegründet 1989.</t>
         </is>
       </c>
       <c r="G188" s="11" t="inlineStr">
@@ -29421,7 +29421,7 @@
       </c>
       <c r="D189" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
@@ -29431,7 +29431,7 @@
       </c>
       <c r="F189" s="8" t="inlineStr">
         <is>
-          <t>Hersteller (USA): programmierbare AC-/DC-Quellen, rückspeisefähige Netzsimulatoren, elektronische Lasten .</t>
+          <t>Hersteller (USA): programmierbare AC-/DC-Quellen, rückspeisefähige Netzsimulatoren, elektronische Lasten.</t>
         </is>
       </c>
       <c r="G189" s="8" t="inlineStr">
@@ -29468,7 +29468,7 @@
       </c>
       <c r="D190" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E190" s="11" t="inlineStr">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="D191" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
@@ -29562,7 +29562,7 @@
       </c>
       <c r="D192" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E192" s="11" t="inlineStr">
@@ -29572,7 +29572,7 @@
       </c>
       <c r="F192" s="11" t="inlineStr">
         <is>
-          <t>Konzern: Rasterkraftmikroskope (AFM, Modelle FX200, FX40), Weißlichtinterferometrie, Infrarotspektroskopie, Ellipsometrie .</t>
+          <t>Konzern: Rasterkraftmikroskope (AFM, Modelle FX200, FX40), Weißlichtinterferometrie, Infrarotspektroskopie, Ellipsometrie.</t>
         </is>
       </c>
       <c r="G192" s="11" t="inlineStr">
@@ -29609,7 +29609,7 @@
       </c>
       <c r="D193" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
@@ -29619,7 +29619,7 @@
       </c>
       <c r="F193" s="8" t="inlineStr">
         <is>
-          <t>Partikelzähler (flüssig, Luft), Reinraum-Kontaminationsüberwachung .</t>
+          <t>Partikelzähler (flüssig, Luft), Reinraum-Kontaminationsüberwachung.</t>
         </is>
       </c>
       <c r="G193" s="8" t="inlineStr">
@@ -29656,7 +29656,7 @@
       </c>
       <c r="D194" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E194" s="11" t="inlineStr">
@@ -29703,7 +29703,7 @@
       </c>
       <c r="D195" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
@@ -29797,7 +29797,7 @@
       </c>
       <c r="D197" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
@@ -29844,7 +29844,7 @@
       </c>
       <c r="D198" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E198" s="11" t="inlineStr">
@@ -29891,7 +29891,7 @@
       </c>
       <c r="D199" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
@@ -29901,7 +29901,7 @@
       </c>
       <c r="F199" s="8" t="inlineStr">
         <is>
-          <t>Leiterplatten (PCB), elektrische Prüfung mit Gardien-Testsystem Kaima GUDAA, 500 bis 600 Platinen pro Stunde .</t>
+          <t>Leiterplatten (PCB), elektrische Prüfung mit Gardien-Testsystem Kaima GUDAA, 500 bis 600 Platinen pro Stunde.</t>
         </is>
       </c>
       <c r="G199" s="8" t="inlineStr">
@@ -29938,7 +29938,7 @@
       </c>
       <c r="D200" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E200" s="11" t="inlineStr">
@@ -29948,7 +29948,7 @@
       </c>
       <c r="F200" s="11" t="inlineStr">
         <is>
-          <t>ERP-Software für mittelständische Industrie .</t>
+          <t>ERP-Software für mittelständische Industrie.</t>
         </is>
       </c>
       <c r="G200" s="11" t="inlineStr">
@@ -29985,7 +29985,7 @@
       </c>
       <c r="D201" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
@@ -29995,7 +29995,7 @@
       </c>
       <c r="F201" s="8" t="inlineStr">
         <is>
-          <t>webbasierte Projektmanagement-Software Projektron BCS .</t>
+          <t>webbasierte Projektmanagement-Software Projektron BCS.</t>
         </is>
       </c>
       <c r="G201" s="8" t="inlineStr">
@@ -30032,7 +30032,7 @@
       </c>
       <c r="D202" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E202" s="11" t="inlineStr">
@@ -30079,7 +30079,7 @@
       </c>
       <c r="D203" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
@@ -30126,7 +30126,7 @@
       </c>
       <c r="D204" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E204" s="11" t="inlineStr">
@@ -30136,7 +30136,7 @@
       </c>
       <c r="F204" s="11" t="inlineStr">
         <is>
-          <t>"complete gas engineering solutions" mit Wartungsservice und Lieferung zugehöriger Gassystem-Produkte .</t>
+          <t>"complete gas engineering solutions" mit Wartungsservice und Lieferung zugehöriger Gassystem-Produkte.</t>
         </is>
       </c>
       <c r="G204" s="11" t="inlineStr">
@@ -30267,7 +30267,7 @@
       </c>
       <c r="D207" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E207" s="8" t="inlineStr">
@@ -30314,7 +30314,7 @@
       </c>
       <c r="D208" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E208" s="11" t="inlineStr">
@@ -30361,7 +30361,7 @@
       </c>
       <c r="D209" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
@@ -30408,7 +30408,7 @@
       </c>
       <c r="D210" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E210" s="11" t="inlineStr">
@@ -30455,7 +30455,7 @@
       </c>
       <c r="D211" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
@@ -30502,7 +30502,7 @@
       </c>
       <c r="D212" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E212" s="11" t="inlineStr">
@@ -30549,7 +30549,7 @@
       </c>
       <c r="D213" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E213" s="8" t="inlineStr">
@@ -30596,7 +30596,7 @@
       </c>
       <c r="D214" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E214" s="11" t="inlineStr">
@@ -30643,7 +30643,7 @@
       </c>
       <c r="D215" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
@@ -30690,7 +30690,7 @@
       </c>
       <c r="D216" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E216" s="11" t="inlineStr">
@@ -30737,7 +30737,7 @@
       </c>
       <c r="D217" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
@@ -30747,7 +30747,7 @@
       </c>
       <c r="F217" s="8" t="inlineStr">
         <is>
-          <t>Die Mutter baut Oszilloskope, Funktionsgeneratoren, Spektrumanalysatoren, HF-Signalgeneratoren, Netzgeräte, Multimeter .</t>
+          <t>Die Mutter baut Oszilloskope, Funktionsgeneratoren, Spektrumanalysatoren, HF-Signalgeneratoren, Netzgeräte, Multimeter.</t>
         </is>
       </c>
       <c r="G217" s="8" t="inlineStr">
@@ -30784,7 +30784,7 @@
       </c>
       <c r="D218" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E218" s="11" t="inlineStr">
@@ -30794,7 +30794,7 @@
       </c>
       <c r="F218" s="11" t="inlineStr">
         <is>
-          <t>Tochter für Vertrieb/Service von Gasmessgeräten und Gaswarnanlagen (Planung, Wartung) in Europa außer UK .</t>
+          <t>Tochter für Vertrieb/Service von Gasmessgeräten und Gaswarnanlagen (Planung, Wartung) in Europa außer UK.</t>
         </is>
       </c>
       <c r="G218" s="11" t="inlineStr">
@@ -30831,7 +30831,7 @@
       </c>
       <c r="D219" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
@@ -30878,7 +30878,7 @@
       </c>
       <c r="D220" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E220" s="11" t="inlineStr">
@@ -30925,7 +30925,7 @@
       </c>
       <c r="D221" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
@@ -30972,7 +30972,7 @@
       </c>
       <c r="D222" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E222" s="11" t="inlineStr">
@@ -31019,7 +31019,7 @@
       </c>
       <c r="D223" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
@@ -31066,7 +31066,7 @@
       </c>
       <c r="D224" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E224" s="11" t="inlineStr">
@@ -31113,7 +31113,7 @@
       </c>
       <c r="D225" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
@@ -31160,7 +31160,7 @@
       </c>
       <c r="D226" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E226" s="11" t="inlineStr">
@@ -31207,7 +31207,7 @@
       </c>
       <c r="D227" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
@@ -31254,7 +31254,7 @@
       </c>
       <c r="D228" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E228" s="11" t="inlineStr">
@@ -31301,7 +31301,7 @@
       </c>
       <c r="D229" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E229" s="8" t="inlineStr">
@@ -31348,7 +31348,7 @@
       </c>
       <c r="D230" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E230" s="11" t="inlineStr">
@@ -31395,7 +31395,7 @@
       </c>
       <c r="D231" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
@@ -31405,7 +31405,7 @@
       </c>
       <c r="F231" s="8" t="inlineStr">
         <is>
-          <t>Kaltfließpressteile aus Stahl, 2 bis 250 g, für Automobil-, Möbel- und Textilindustrie .</t>
+          <t>Kaltfließpressteile aus Stahl, 2 bis 250 g, für Automobil-, Möbel- und Textilindustrie.</t>
         </is>
       </c>
       <c r="G231" s="8" t="inlineStr">
@@ -31442,7 +31442,7 @@
       </c>
       <c r="D232" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E232" s="11" t="inlineStr">
@@ -31489,7 +31489,7 @@
       </c>
       <c r="D233" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E233" s="8" t="inlineStr">
@@ -31536,7 +31536,7 @@
       </c>
       <c r="D234" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E234" s="11" t="inlineStr">
@@ -31546,7 +31546,7 @@
       </c>
       <c r="F234" s="11" t="inlineStr">
         <is>
-          <t>Software (embOS, emWin, Embedded Studio) und Hardware-Tools (J-Link-Debugprobes, Flasher-Programmiergeräte) .</t>
+          <t>Software (embOS, emWin, Embedded Studio) und Hardware-Tools (J-Link-Debugprobes, Flasher-Programmiergeräte).</t>
         </is>
       </c>
       <c r="G234" s="11" t="inlineStr">
@@ -31583,7 +31583,7 @@
       </c>
       <c r="D235" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E235" s="8" t="inlineStr">
@@ -31630,7 +31630,7 @@
       </c>
       <c r="D236" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E236" s="11" t="inlineStr">
@@ -31640,7 +31640,7 @@
       </c>
       <c r="F236" s="11" t="inlineStr">
         <is>
-          <t>nicht ermittelbar .</t>
+          <t>nicht ermittelbar.</t>
         </is>
       </c>
       <c r="G236" s="11" t="inlineStr">
@@ -31677,7 +31677,7 @@
       </c>
       <c r="D237" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E237" s="8" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="D238" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E238" s="11" t="inlineStr">
@@ -31771,7 +31771,7 @@
       </c>
       <c r="D239" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E239" s="8" t="inlineStr">
@@ -31818,7 +31818,7 @@
       </c>
       <c r="D240" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E240" s="11" t="inlineStr">
@@ -31865,7 +31865,7 @@
       </c>
       <c r="D241" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E241" s="8" t="inlineStr">
@@ -31912,7 +31912,7 @@
       </c>
       <c r="D242" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E242" s="11" t="inlineStr">
@@ -31959,7 +31959,7 @@
       </c>
       <c r="D243" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E243" s="8" t="inlineStr">
@@ -31969,7 +31969,7 @@
       </c>
       <c r="F243" s="8" t="inlineStr">
         <is>
-          <t>Gasversorgungsanlagen von Gasflaschenschränken und Manifolds bis zu vollautomatischen Gasschränken für Halbleitergase, Alarm- und Steuersysteme, Gasreinigung .</t>
+          <t>Gasversorgungsanlagen von Gasflaschenschränken und Manifolds bis zu vollautomatischen Gasschränken für Halbleitergase, Alarm- und Steuersysteme, Gasreinigung.</t>
         </is>
       </c>
       <c r="G243" s="8" t="inlineStr">
@@ -32006,7 +32006,7 @@
       </c>
       <c r="D244" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E244" s="11" t="inlineStr">
@@ -32016,7 +32016,7 @@
       </c>
       <c r="F244" s="11" t="inlineStr">
         <is>
-          <t>Sprühdüsen und Sprühsysteme für Industrie .</t>
+          <t>Sprühdüsen und Sprühsysteme für Industrie.</t>
         </is>
       </c>
       <c r="G244" s="11" t="inlineStr">
@@ -32053,7 +32053,7 @@
       </c>
       <c r="D245" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E245" s="8" t="inlineStr">
@@ -32063,7 +32063,7 @@
       </c>
       <c r="F245" s="8" t="inlineStr">
         <is>
-          <t>nicht ermittelt .</t>
+          <t>nicht ermittelt.</t>
         </is>
       </c>
       <c r="G245" s="8" t="inlineStr">
@@ -32110,7 +32110,7 @@
       </c>
       <c r="F246" s="11" t="inlineStr">
         <is>
-          <t>OSAT und EMS (Leiterplatten, Faseroptik-Bauelemente) in Thailand .</t>
+          <t>OSAT und EMS (Leiterplatten, Faseroptik-Bauelemente) in Thailand.</t>
         </is>
       </c>
       <c r="G246" s="11" t="inlineStr">
@@ -32147,7 +32147,7 @@
       </c>
       <c r="D247" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E247" s="8" t="inlineStr">
@@ -32157,7 +32157,7 @@
       </c>
       <c r="F247" s="8" t="inlineStr">
         <is>
-          <t>Phytron: Schrittmotoren und elektronische Steuerungen für Industrie, Forschung, Medizintechnik, extreme Umgebungen .</t>
+          <t>Phytron: Schrittmotoren und elektronische Steuerungen für Industrie, Forschung, Medizintechnik, extreme Umgebungen.</t>
         </is>
       </c>
       <c r="G247" s="8" t="inlineStr">
@@ -32194,7 +32194,7 @@
       </c>
       <c r="D248" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E248" s="11" t="inlineStr">
@@ -32204,7 +32204,7 @@
       </c>
       <c r="F248" s="11" t="inlineStr">
         <is>
-          <t>Vertrieb von Kameras, Objektiven, Beleuchtung, Kabeln, PCs, Bildverarbeitungssoftware (Common Vision Blox), Systemlösungen .</t>
+          <t>Vertrieb von Kameras, Objektiven, Beleuchtung, Kabeln, PCs, Bildverarbeitungssoftware (Common Vision Blox), Systemlösungen.</t>
         </is>
       </c>
       <c r="G248" s="11" t="inlineStr">
@@ -32241,7 +32241,7 @@
       </c>
       <c r="D249" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E249" s="8" t="inlineStr">
@@ -32288,7 +32288,7 @@
       </c>
       <c r="D250" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E250" s="11" t="inlineStr">
@@ -32335,7 +32335,7 @@
       </c>
       <c r="D251" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E251" s="8" t="inlineStr">
@@ -32382,7 +32382,7 @@
       </c>
       <c r="D252" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E252" s="11" t="inlineStr">
@@ -32429,7 +32429,7 @@
       </c>
       <c r="D253" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E253" s="8" t="inlineStr">
@@ -32439,7 +32439,7 @@
       </c>
       <c r="F253" s="8" t="inlineStr">
         <is>
-          <t>Die Firma stellt sich selbst als Distributor und Vertretung vor, der Hersteller aus HF-, Mikrowellen- und Hochfrequenztechnik an Kunden in DACH bringt .</t>
+          <t>Die Firma stellt sich selbst als Distributor und Vertretung vor, der Hersteller aus HF-, Mikrowellen- und Hochfrequenztechnik an Kunden in DACH bringt.</t>
         </is>
       </c>
       <c r="G253" s="8" t="inlineStr">
@@ -32476,7 +32476,7 @@
       </c>
       <c r="D254" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E254" s="11" t="inlineStr">
@@ -32486,7 +32486,7 @@
       </c>
       <c r="F254" s="11" t="inlineStr">
         <is>
-          <t>elektrolytisch beschichtetes (vernickeltes, auch verkupfertes/vermessingtes) kaltgewalztes Stahlband, Markenname HIBRITE .</t>
+          <t>elektrolytisch beschichtetes (vernickeltes, auch verkupfertes/vermessingtes) kaltgewalztes Stahlband, Markenname HIBRITE.</t>
         </is>
       </c>
       <c r="G254" s="11" t="inlineStr">
@@ -32523,7 +32523,7 @@
       </c>
       <c r="D255" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E255" s="8" t="inlineStr">
@@ -32570,7 +32570,7 @@
       </c>
       <c r="D256" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E256" s="11" t="inlineStr">
@@ -32580,7 +32580,7 @@
       </c>
       <c r="F256" s="11" t="inlineStr">
         <is>
-          <t>Vertrieb von Funk-ICs, Quarzen und Oszillatoren, Power-Management-ICs, Sensor-/Testmodulen und Funkmodulen .</t>
+          <t>Vertrieb von Funk-ICs, Quarzen und Oszillatoren, Power-Management-ICs, Sensor-/Testmodulen und Funkmodulen.</t>
         </is>
       </c>
       <c r="G256" s="11" t="inlineStr">
@@ -32617,7 +32617,7 @@
       </c>
       <c r="D257" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E257" s="8" t="inlineStr">
@@ -32664,7 +32664,7 @@
       </c>
       <c r="D258" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E258" s="11" t="inlineStr">
@@ -32674,7 +32674,7 @@
       </c>
       <c r="F258" s="11" t="inlineStr">
         <is>
-          <t>Oszilloskope, Protokollanalysatoren, Testgeräte .</t>
+          <t>Oszilloskope, Protokollanalysatoren, Testgeräte.</t>
         </is>
       </c>
       <c r="G258" s="11" t="inlineStr">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="H258" s="11" t="inlineStr">
         <is>
-          <t>Impressum teledynelecroy.com/support/legal-notice-imprint im Browser lesen (V für Identität). Karriereseite Heidelberg: Entwicklung/Vertrieb/Fertigung? Fertigt die LeCroy Division in DE (Tastköpfe, Geräte)?</t>
+          <t>Impressum teledynelecroy.com/support/legal-notice-imprint im Browser lesen. Karriereseite Heidelberg: Entwicklung/Vertrieb/Fertigung? Fertigt die LeCroy Division in DE (Tastköpfe, Geräte)?</t>
         </is>
       </c>
       <c r="I258" s="11" t="inlineStr">
@@ -32711,7 +32711,7 @@
       </c>
       <c r="D259" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E259" s="8" t="inlineStr">
@@ -32758,7 +32758,7 @@
       </c>
       <c r="D260" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E260" s="11" t="inlineStr">
@@ -32805,7 +32805,7 @@
       </c>
       <c r="D261" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E261" s="8" t="inlineStr">
@@ -32852,7 +32852,7 @@
       </c>
       <c r="D262" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E262" s="11" t="inlineStr">
@@ -32899,7 +32899,7 @@
       </c>
       <c r="D263" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E263" s="8" t="inlineStr">
@@ -32946,7 +32946,7 @@
       </c>
       <c r="D264" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E264" s="11" t="inlineStr">
@@ -32993,7 +32993,7 @@
       </c>
       <c r="D265" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E265" s="8" t="inlineStr">
@@ -33040,7 +33040,7 @@
       </c>
       <c r="D266" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E266" s="11" t="inlineStr">
@@ -33087,7 +33087,7 @@
       </c>
       <c r="D267" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E267" s="8" t="inlineStr">
@@ -33097,7 +33097,7 @@
       </c>
       <c r="F267" s="8" t="inlineStr">
         <is>
-          <t>Konzernsortiment passive Bauteile (magnetische und elektrokeramische Produkte, Widerstände, SMD-Induktivitäten) und Sensoren .</t>
+          <t>Konzernsortiment passive Bauteile (magnetische und elektrokeramische Produkte, Widerstände, SMD-Induktivitäten) und Sensoren.</t>
         </is>
       </c>
       <c r="G267" s="8" t="inlineStr">
@@ -33134,7 +33134,7 @@
       </c>
       <c r="D268" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E268" s="11" t="inlineStr">
@@ -33181,7 +33181,7 @@
       </c>
       <c r="D269" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E269" s="8" t="inlineStr">
@@ -33228,7 +33228,7 @@
       </c>
       <c r="D270" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E270" s="11" t="inlineStr">
@@ -33238,7 +33238,7 @@
       </c>
       <c r="F270" s="11" t="inlineStr">
         <is>
-          <t>Elektronische Messgeräte der Marke UNI-T .</t>
+          <t>Elektronische Messgeräte der Marke UNI-T.</t>
         </is>
       </c>
       <c r="G270" s="11" t="inlineStr">
@@ -33275,7 +33275,7 @@
       </c>
       <c r="D271" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E271" s="8" t="inlineStr">
@@ -33322,7 +33322,7 @@
       </c>
       <c r="D272" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E272" s="11" t="inlineStr">
@@ -33369,7 +33369,7 @@
       </c>
       <c r="D273" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E273" s="8" t="inlineStr">
@@ -33379,7 +33379,7 @@
       </c>
       <c r="F273" s="8" t="inlineStr">
         <is>
-          <t>Maschinen und Prozesse für 3D-Nanodruck von Photonic Wire Bonds, Photonic Integration und Packaging .</t>
+          <t>Maschinen und Prozesse für 3D-Nanodruck von Photonic Wire Bonds, Photonic Integration und Packaging.</t>
         </is>
       </c>
       <c r="G273" s="8" t="inlineStr">
@@ -33416,7 +33416,7 @@
       </c>
       <c r="D274" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E274" s="11" t="inlineStr">
@@ -33426,7 +33426,7 @@
       </c>
       <c r="F274" s="11" t="inlineStr">
         <is>
-          <t>Vakuumventile, Membranbälge, laut Mitgliederprofil auch "Ultra-Clean-Produktion" .</t>
+          <t>Vakuumventile, Membranbälge, laut Mitgliederprofil auch "Ultra-Clean-Produktion".</t>
         </is>
       </c>
       <c r="G274" s="11" t="inlineStr">
@@ -33463,7 +33463,7 @@
       </c>
       <c r="D275" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E275" s="8" t="inlineStr">
@@ -33510,7 +33510,7 @@
       </c>
       <c r="D276" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E276" s="11" t="inlineStr">
@@ -33557,7 +33557,7 @@
       </c>
       <c r="D277" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E277" s="8" t="inlineStr">
@@ -33567,7 +33567,7 @@
       </c>
       <c r="F277" s="8" t="inlineStr">
         <is>
-          <t>unbekannt .</t>
+          <t>unbekannt.</t>
         </is>
       </c>
       <c r="G277" s="8" t="inlineStr">
@@ -33604,7 +33604,7 @@
       </c>
       <c r="D278" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E278" s="11" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="F278" s="11" t="inlineStr">
         <is>
-          <t>Lautsprecher (Koaxial-, Horn- und wasserdichte Modelle) und Zubehör nach Händlerlisten .</t>
+          <t>Lautsprecher (Koaxial-, Horn- und wasserdichte Modelle) und Zubehör nach Händlerlisten.</t>
         </is>
       </c>
       <c r="G278" s="11" t="inlineStr">
@@ -33651,7 +33651,7 @@
       </c>
       <c r="D279" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E279" s="8" t="inlineStr">
@@ -33698,7 +33698,7 @@
       </c>
       <c r="D280" s="11" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E280" s="11" t="inlineStr">
@@ -33708,7 +33708,7 @@
       </c>
       <c r="F280" s="11" t="inlineStr">
         <is>
-          <t>Kaltfließpressteile aus Stahl, 2 bis 250 g, für Automobil-, Möbel- und Textilindustrie .</t>
+          <t>Kaltfließpressteile aus Stahl, 2 bis 250 g, für Automobil-, Möbel- und Textilindustrie.</t>
         </is>
       </c>
       <c r="G280" s="11" t="inlineStr">
@@ -33745,7 +33745,7 @@
       </c>
       <c r="D281" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E281" s="8" t="inlineStr">
@@ -33792,7 +33792,7 @@
       </c>
       <c r="D282" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E282" s="11" t="inlineStr">
@@ -33839,7 +33839,7 @@
       </c>
       <c r="D283" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E283" s="8" t="inlineStr">
@@ -33886,7 +33886,7 @@
       </c>
       <c r="D284" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E284" s="11" t="inlineStr">
@@ -33896,7 +33896,7 @@
       </c>
       <c r="F284" s="11" t="inlineStr">
         <is>
-          <t>Selbstbeschreibung "Design-In distributor" für Passive, Elektromechanik, Halbleiter, Taster/Schalter, Batterien .</t>
+          <t>Selbstbeschreibung "Design-In distributor" für Passive, Elektromechanik, Halbleiter, Taster/Schalter, Batterien.</t>
         </is>
       </c>
       <c r="G284" s="11" t="inlineStr">
@@ -33933,7 +33933,7 @@
       </c>
       <c r="D285" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E285" s="8" t="inlineStr">
@@ -33980,7 +33980,7 @@
       </c>
       <c r="D286" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E286" s="11" t="inlineStr">
@@ -34027,7 +34027,7 @@
       </c>
       <c r="D287" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E287" s="8" t="inlineStr">
@@ -34074,7 +34074,7 @@
       </c>
       <c r="D288" s="11" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E288" s="11" t="inlineStr">
@@ -34084,7 +34084,7 @@
       </c>
       <c r="F288" s="11" t="inlineStr">
         <is>
-          <t>Komponenten für die Halbleiterfertigung, Prozesstemperierung, kundenspezifische Lösungen, Lieferung von Produkten und technischen Spezialflüssigkeiten .</t>
+          <t>Komponenten für die Halbleiterfertigung, Prozesstemperierung, kundenspezifische Lösungen, Lieferung von Produkten und technischen Spezialflüssigkeiten.</t>
         </is>
       </c>
       <c r="G288" s="11" t="inlineStr">
@@ -34121,7 +34121,7 @@
       </c>
       <c r="D289" s="8" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E289" s="8" t="inlineStr">
@@ -34131,7 +34131,7 @@
       </c>
       <c r="F289" s="8" t="inlineStr">
         <is>
-          <t>Test&amp;Measurement-Geräte (Oszilloskope, Leistungsmessgeräte, Datenerfassung), Produktliste am Standort nicht belegt .</t>
+          <t>Test&amp;Measurement-Geräte (Oszilloskope, Leistungsmessgeräte, Datenerfassung), Produktliste am Standort nicht belegt.</t>
         </is>
       </c>
       <c r="G289" s="8" t="inlineStr">
@@ -34168,7 +34168,7 @@
       </c>
       <c r="D290" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E290" s="11" t="inlineStr">
@@ -34178,7 +34178,7 @@
       </c>
       <c r="F290" s="11" t="inlineStr">
         <is>
-          <t>Spezial-DRAM und Flash (Design-House), Herstellung durch Partner-Foundries (Powerchip, Giant Crystal) in Asien .</t>
+          <t>Spezial-DRAM und Flash (Design-House), Herstellung durch Partner-Foundries (Powerchip, Giant Crystal) in Asien.</t>
         </is>
       </c>
       <c r="G290" s="11" t="inlineStr">
@@ -34215,7 +34215,7 @@
       </c>
       <c r="D291" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E291" s="8" t="inlineStr">
@@ -34262,7 +34262,7 @@
       </c>
       <c r="D292" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E292" s="11" t="inlineStr">
@@ -34309,7 +34309,7 @@
       </c>
       <c r="D293" s="8" t="inlineStr">
         <is>
-          <t>Rest DE / NL</t>
+          <t>Rest DE / NL (Manuel)</t>
         </is>
       </c>
       <c r="E293" s="8" t="inlineStr">
@@ -34356,7 +34356,7 @@
       </c>
       <c r="D294" s="11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bayern (Dietmar)</t>
         </is>
       </c>
       <c r="E294" s="11" t="inlineStr">
@@ -34403,7 +34403,7 @@
       </c>
       <c r="D295" s="8" t="inlineStr">
         <is>
-          <t>Baden-Württemberg</t>
+          <t>Baden-Württemberg (Stefan)</t>
         </is>
       </c>
       <c r="E295" s="8" t="inlineStr">
@@ -34413,7 +34413,7 @@
       </c>
       <c r="F295" s="8" t="inlineStr">
         <is>
-          <t>Fotochemisch geätzte Metallteile (Muster und Serie, Konturätzteile, Rolle-zu-Rolle, Federn), Branchen Medizintechnik, Automotive, Elektronik, Optik, Sensorik .</t>
+          <t>Fotochemisch geätzte Metallteile (Muster und Serie, Konturätzteile, Rolle-zu-Rolle, Federn), Branchen Medizintechnik, Automotive, Elektronik, Optik, Sensorik.</t>
         </is>
       </c>
       <c r="G295" s="8" t="inlineStr">
@@ -34595,7 +34595,7 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Wafer-Prober, Grinder, Dicer, CMP, industrielle Messtechnik (Rauheit, Kontur, Form), Batterie-Testtechnik .</t>
+          <t>Wafer-Prober, Grinder, Dicer, CMP, industrielle Messtechnik (Rauheit, Kontur, Form), Batterie-Testtechnik.</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -34642,7 +34642,7 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Flying-Probe-Tester (Scorpion), In-Line-MDA, Prüfsoftware X-matic .</t>
+          <t>Flying-Probe-Tester (Scorpion), In-Line-MDA, Prüfsoftware X-matic.</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -34689,7 +34689,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Handling-Equipment für Wafer/Panel: Load Ports, Roboter, Pre-Aligner, EFEM/iFEM-Komplettsysteme, Auto-Teaching .</t>
+          <t>Handling-Equipment für Wafer/Panel: Load Ports, Roboter, Pre-Aligner, EFEM/iFEM-Komplettsysteme, Auto-Teaching.</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -34970,7 +34970,7 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>manuelle, halb- und vollautomatische Nassprozessanlagen (Reinigen, Ätzen, Trocknen) und Chemikalienversorgung für Halbleiter, MEMS, Optoelektronik bis 300 mm Wafer .</t>
+          <t>manuelle, halb- und vollautomatische Nassprozessanlagen (Reinigen, Ätzen, Trocknen) und Chemikalienversorgung für Halbleiter, MEMS, Optoelektronik bis 300 mm Wafer.</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -35150,7 +35150,7 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>Ultrahochpräzise Die-Attach- und Flip-Chip-Bonder (NANO, NOVA Pro, CoS Die Bonder), Wafer-Inking, High-Speed-Dispense-System .</t>
+          <t>Ultrahochpräzise Die-Attach- und Flip-Chip-Bonder (NANO, NOVA Pro, CoS Die Bonder), Wafer-Inking, High-Speed-Dispense-System.</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -35619,7 +35619,7 @@
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>Röntgenfluoreszenz-Analysegeräte (Mikro-RFA, TXRF, Handheld-RFA), BioAFM .</t>
+          <t>Röntgenfluoreszenz-Analysegeräte (Mikro-RFA, TXRF, Handheld-RFA), BioAFM.</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
@@ -35713,7 +35713,7 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>Metrologie- und Inspektionsanlagen für Halbleiter (Advanced Packaging, Memory, CMOS-Sensoren, MEMS), Konzern Camtek Ltd .</t>
+          <t>Metrologie- und Inspektionsanlagen für Halbleiter (Advanced Packaging, Memory, CMOS-Sensoren, MEMS), Konzern Camtek Ltd.</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
@@ -35760,7 +35760,7 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>Licht-, Ionen- und Elektronenmikroskope, Fluoreszenz-Lichtschnittsysteme, Röntgenmikroskope .</t>
+          <t>Licht-, Ionen- und Elektronenmikroskope, Fluoreszenz-Lichtschnittsysteme, Röntgenmikroskope.</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -35807,7 +35807,7 @@
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>Licht-, Ionen- und Elektronenmikroskope, Fluoreszenz-Lichtschnittsysteme, Röntgenmikroskope .</t>
+          <t>Licht-, Ionen- und Elektronenmikroskope, Fluoreszenz-Lichtschnittsysteme, Röntgenmikroskope.</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
@@ -35901,7 +35901,7 @@
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>Pneumatikzylinder, Wegeventile, Fluid-Control-Komponenten, elektrische Aktoren, Sensoren, Automatisierungsmaschinen für Halbleiter, Automotive, Sekundärbatterien .</t>
+          <t>Pneumatikzylinder, Wegeventile, Fluid-Control-Komponenten, elektrische Aktoren, Sensoren, Automatisierungsmaschinen für Halbleiter, Automotive, Sekundärbatterien.</t>
         </is>
       </c>
       <c r="G36" s="11" t="inlineStr">
@@ -36347,7 +36347,7 @@
       </c>
       <c r="F46" s="11" t="inlineStr">
         <is>
-          <t>Gleichrichter (Brücken-, Hochspannungs-, schnelle), Schottky-, Zener-, TVS-Dioden, Transistoren, MOSFETs .</t>
+          <t>Gleichrichter (Brücken-, Hochspannungs-, schnelle), Schottky-, Zener-, TVS-Dioden, Transistoren, MOSFETs.</t>
         </is>
       </c>
       <c r="G46" s="11" t="inlineStr">
@@ -36605,7 +36605,7 @@
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>Drahtlacke, Tränkharze und -lacke, Gieß- und Vergussmassen (Epoxid, PU, Silikon), Schutzlacke, Klebstoffe, flexible Isolierstoffe .</t>
+          <t>Drahtlacke, Tränkharze und -lacke, Gieß- und Vergussmassen (Epoxid, PU, Silikon), Schutzlacke, Klebstoffe, flexible Isolierstoffe.</t>
         </is>
       </c>
       <c r="G52" s="11" t="inlineStr">
@@ -36691,7 +36691,7 @@
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>Epitaxie- und Plasmasysteme sowie Ionen-/Plasmaquellen für Chiphersteller, AlN-Beschichtungsanlage .</t>
+          <t>Epitaxie- und Plasmasysteme sowie Ionen-/Plasmaquellen für Chiphersteller, AlN-Beschichtungsanlage.</t>
         </is>
       </c>
       <c r="G54" s="11" t="inlineStr">
@@ -36738,7 +36738,7 @@
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>Maschinen für Halbleiter-Test (esmo semicon: Handling-/Testsysteme) und Sondermaschinenbau/Automatisierung (esmo automation), Schaltschrankbau und Verdrahtung .</t>
+          <t>Maschinen für Halbleiter-Test (esmo semicon: Handling-/Testsysteme) und Sondermaschinenbau/Automatisierung (esmo automation), Schaltschrankbau und Verdrahtung.</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
@@ -36832,7 +36832,7 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>Gasversorgungs- und Chemieversorgungssysteme, Wassertechnik, Tanks mit Tankauskleidung, Elektro-, Mess- und Regelungstechnik, OEM-Lohnfertigung, HighQ-Recyclinganlagen .</t>
+          <t>Gasversorgungs- und Chemieversorgungssysteme, Wassertechnik, Tanks mit Tankauskleidung, Elektro-, Mess- und Regelungstechnik, OEM-Lohnfertigung, HighQ-Recyclinganlagen.</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
@@ -36918,7 +36918,7 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>Hochpräzisions-Die-Bonder und Flip-Chip-Bonder (FINEPLACER, FiNEXT), SMD-Rework-Systeme .</t>
+          <t>Hochpräzisions-Die-Bonder und Flip-Chip-Bonder (FINEPLACER, FiNEXT), SMD-Rework-Systeme.</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
@@ -37012,7 +37012,7 @@
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>Federkontaktstifte/Prüfstifte (über 8000 Standardartikel), kundenspezifische Federkontakte, Batterie-Kontaktstifte, Hochstrom-Kontaktstifte .</t>
+          <t>Federkontaktstifte/Prüfstifte (über 8000 Standardartikel), kundenspezifische Federkontakte, Batterie-Kontaktstifte, Hochstrom-Kontaktstifte.</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
@@ -37513,7 +37513,7 @@
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>Branchenverband: Standards (IPC-A-610, J-STD-001), Schulungen, Zertifizierung für die Elektronikfertigung .</t>
+          <t>Branchenverband: Standards (IPC-A-610, J-STD-001), Schulungen, Zertifizierung für die Elektronikfertigung.</t>
         </is>
       </c>
       <c r="G72" s="11" t="inlineStr">
@@ -37888,7 +37888,7 @@
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>in Krefeld Vertrieb, Service und Applikationslabor (XRF, LIBS, OES, Thermoanalyse, REM, FIB) .</t>
+          <t>in Krefeld Vertrieb, Service und Applikationslabor (XRF, LIBS, OES, Thermoanalyse, REM, FIB).</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
@@ -37974,7 +37974,7 @@
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>Abgasmesssysteme, Antriebsstrang-, Fahrzeug-, Bremsen- und Batterieprüfstände, Windkanalwaagen, Sensoren für F&amp;E (Entwicklung, Installation, Service) .</t>
+          <t>Abgasmesssysteme, Antriebsstrang-, Fahrzeug-, Bremsen- und Batterieprüfstände, Windkanalwaagen, Sensoren für F&amp;E (Entwicklung, Installation, Service).</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
@@ -38767,7 +38767,7 @@
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>"Design, Installation, Test und Inbetriebnahme" von Ultrahochreinheits-Gas- und Chemikalienverteilungen sowie Lieferung von Gasschränken, Gaspanels, Ventilmanifolds .</t>
+          <t>"Design, Installation, Test und Inbetriebnahme" von Ultrahochreinheits-Gas- und Chemikalienverteilungen sowie Lieferung von Gasschränken, Gaspanels, Ventilmanifolds.</t>
         </is>
       </c>
       <c r="G102" s="11" t="inlineStr">
@@ -38900,7 +38900,7 @@
       </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>3D-Inspektionssysteme SPI/AOI (True3D) für SMT-Linien .</t>
+          <t>3D-Inspektionssysteme SPI/AOI (True3D) für SMT-Linien.</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
@@ -38994,7 +38994,7 @@
       </c>
       <c r="F107" s="8" t="inlineStr">
         <is>
-          <t>Automatisierungssoftware und Leitsysteme (VAC NT/32) für Halbleiter, Photovoltaik, Automotive, Pharma, Bahn .</t>
+          <t>Automatisierungssoftware und Leitsysteme (VAC NT/32) für Halbleiter, Photovoltaik, Automotive, Pharma, Bahn.</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr">
@@ -39174,7 +39174,7 @@
       </c>
       <c r="F111" s="8" t="inlineStr">
         <is>
-          <t>Einkammer-Beschichtungssysteme und Cluster-Tools mit Robotertransfer für Produktion und Forschung .</t>
+          <t>Einkammer-Beschichtungssysteme und Cluster-Tools mit Robotertransfer für Produktion und Forschung.</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr">
@@ -39221,7 +39221,7 @@
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>Vakuumlötsysteme für Halbleiter und Mikroelektronik, Serienanlage SRO i-LINE mit Infrarotheizung .</t>
+          <t>Vakuumlötsysteme für Halbleiter und Mikroelektronik, Serienanlage SRO i-LINE mit Infrarotheizung.</t>
         </is>
       </c>
       <c r="G112" s="11" t="inlineStr">
@@ -39268,7 +39268,7 @@
       </c>
       <c r="F113" s="8" t="inlineStr">
         <is>
-          <t>Vakuumlötsysteme für Halbleiter und Mikroelektronik, Serienanlage SRO i-LINE mit Infrarotheizung .</t>
+          <t>Vakuumlötsysteme für Halbleiter und Mikroelektronik, Serienanlage SRO i-LINE mit Infrarotheizung.</t>
         </is>
       </c>
       <c r="G113" s="8" t="inlineStr">
@@ -39315,7 +39315,7 @@
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
-          <t>technische Keramik (über 200 Keramikwerkstoffe), Systemkomponenten für Elektro- und Sensortechnik, Analytik, Medizintechnik und Halbleiter .</t>
+          <t>technische Keramik (über 200 Keramikwerkstoffe), Systemkomponenten für Elektro- und Sensortechnik, Analytik, Medizintechnik und Halbleiter.</t>
         </is>
       </c>
       <c r="G114" s="11" t="inlineStr">
@@ -39362,7 +39362,7 @@
       </c>
       <c r="F115" s="8" t="inlineStr">
         <is>
-          <t>Die Gruppe wird als "high-tech companies specializing in nanofabrication, microfabrication and surface analysis" beschrieben .</t>
+          <t>Die Gruppe wird als "high-tech companies specializing in nanofabrication, microfabrication and surface analysis" beschrieben.</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr">
@@ -40484,7 +40484,7 @@
       </c>
       <c r="F141" s="8" t="inlineStr">
         <is>
-          <t>Piezokeramik-Komponenten (Röhren, Platten, Biegeelemente, Multilayer-Chip-Aktoren), Ultraschallwandler, piezoelektrische Sensoren, DuraAct-Patch-Wandler .</t>
+          <t>Piezokeramik-Komponenten (Röhren, Platten, Biegeelemente, Multilayer-Chip-Aktoren), Ultraschallwandler, piezoelektrische Sensoren, DuraAct-Patch-Wandler.</t>
         </is>
       </c>
       <c r="G141" s="8" t="inlineStr">
@@ -41375,7 +41375,7 @@
       </c>
       <c r="F162" s="11" t="inlineStr">
         <is>
-          <t>Plasmaprozessanlagen (Ätzen, Abscheiden, ALD) und Dünnschicht-Messtechnik (Ellipsometer, Reflektometer) .</t>
+          <t>Plasmaprozessanlagen (Ätzen, Abscheiden, ALD) und Dünnschicht-Messtechnik (Ellipsometer, Reflektometer).</t>
         </is>
       </c>
       <c r="G162" s="11" t="inlineStr">
@@ -41422,7 +41422,7 @@
       </c>
       <c r="F163" s="8" t="inlineStr">
         <is>
-          <t>Software (Simulation, Test, Engineering, Simcenter), keine Hardwarefertigung belegt .</t>
+          <t>Software (Simulation, Test, Engineering, Simcenter), keine Hardwarefertigung belegt.</t>
         </is>
       </c>
       <c r="G163" s="8" t="inlineStr">
@@ -41563,7 +41563,7 @@
       </c>
       <c r="F166" s="11" t="inlineStr">
         <is>
-          <t>Vakuumbeschichtungs- und nasschemische Produktionsanlagen (MEDLINE, SILEX III Solar-Fertigungssystem), Sonderanlagenbau .</t>
+          <t>Vakuumbeschichtungs- und nasschemische Produktionsanlagen (MEDLINE, SILEX III Solar-Fertigungssystem), Sonderanlagenbau.</t>
         </is>
       </c>
       <c r="G166" s="11" t="inlineStr">
@@ -41735,7 +41735,7 @@
       </c>
       <c r="F170" s="11" t="inlineStr">
         <is>
-          <t>Steckverbinder mit MULTILAM-Kontakttechnik, MC4-PV-Steckverbinder, Speicher-/Batteriesteckverbinder, Messtechnik-Steckverbinder .</t>
+          <t>Steckverbinder mit MULTILAM-Kontakttechnik, MC4-PV-Steckverbinder, Speicher-/Batteriesteckverbinder, Messtechnik-Steckverbinder.</t>
         </is>
       </c>
       <c r="G170" s="11" t="inlineStr">
@@ -41962,7 +41962,7 @@
       </c>
       <c r="F175" s="8" t="inlineStr">
         <is>
-          <t>in Darmstadt keine Fertigung erkennbar .</t>
+          <t>in Darmstadt keine Fertigung erkennbar.</t>
         </is>
       </c>
       <c r="G175" s="8" t="inlineStr">
@@ -42009,7 +42009,7 @@
       </c>
       <c r="F176" s="11" t="inlineStr">
         <is>
-          <t>Lithographiesysteme (Mask Aligner, Coater, Developer) und Bondersysteme für MEMS, Verbindungshalbleiter und 3D-Integration .</t>
+          <t>Lithographiesysteme (Mask Aligner, Coater, Developer) und Bondersysteme für MEMS, Verbindungshalbleiter und 3D-Integration.</t>
         </is>
       </c>
       <c r="G176" s="11" t="inlineStr">
@@ -42392,7 +42392,7 @@
       </c>
       <c r="F185" s="8" t="inlineStr">
         <is>
-          <t>Halbleiter-Wafer und integrierte Schaltungen (Freising: Wafer-Fab, Kilby Labs F&amp;E, Europazentrale) .</t>
+          <t>Halbleiter-Wafer und integrierte Schaltungen (Freising: Wafer-Fab, Kilby Labs F&amp;E, Europazentrale).</t>
         </is>
       </c>
       <c r="G185" s="8" t="inlineStr">
@@ -42697,7 +42697,7 @@
       </c>
       <c r="F192" s="11" t="inlineStr">
         <is>
-          <t>Vakuumpumpen, Vakuum- und Beschichtungsanlagen der Gruppe, in Kirchheim Vertrieb/Service .</t>
+          <t>Vakuumpumpen, Vakuum- und Beschichtungsanlagen der Gruppe, in Kirchheim Vertrieb/Service.</t>
         </is>
       </c>
       <c r="G192" s="11" t="inlineStr">
@@ -42744,7 +42744,7 @@
       </c>
       <c r="F193" s="8" t="inlineStr">
         <is>
-          <t>Rapid-Thermal-Annealing-Anlagen, Reflow-Lötöfen, Präzisions-Heizplatten, vor allem für Labore und Kleinserien .</t>
+          <t>Rapid-Thermal-Annealing-Anlagen, Reflow-Lötöfen, Präzisions-Heizplatten, vor allem für Labore und Kleinserien.</t>
         </is>
       </c>
       <c r="G193" s="8" t="inlineStr">
@@ -42877,7 +42877,7 @@
       </c>
       <c r="F196" s="11" t="inlineStr">
         <is>
-          <t>Dünnschicht-Prozessanlagen für Halbleiter, LED, Leistungselektronik, MEMS .</t>
+          <t>Dünnschicht-Prozessanlagen für Halbleiter, LED, Leistungselektronik, MEMS.</t>
         </is>
       </c>
       <c r="G196" s="11" t="inlineStr">
@@ -42924,7 +42924,7 @@
       </c>
       <c r="F197" s="8" t="inlineStr">
         <is>
-          <t>automatische Inspektionssysteme für Lotpaste, Optik (AOI), Röntgen (AXI), Schutzlack, Batterie, Bonds und Software .</t>
+          <t>automatische Inspektionssysteme für Lotpaste, Optik (AOI), Röntgen (AXI), Schutzlack, Batterie, Bonds und Software.</t>
         </is>
       </c>
       <c r="G197" s="8" t="inlineStr">
@@ -43143,7 +43143,7 @@
       </c>
       <c r="F202" s="11" t="inlineStr">
         <is>
-          <t>Anlagen für Leiterplatten- und Oberflächentechnik (chemische Prozessanlagen, Galvanik, Belichtungsgeräte für Leiterplatten) aus Kunststoffen wie PVC, PP, PE, PVDF .</t>
+          <t>Anlagen für Leiterplatten- und Oberflächentechnik (chemische Prozessanlagen, Galvanik, Belichtungsgeräte für Leiterplatten) aus Kunststoffen wie PVC, PP, PE, PVDF.</t>
         </is>
       </c>
       <c r="G202" s="11" t="inlineStr">
@@ -43229,7 +43229,7 @@
       </c>
       <c r="F204" s="11" t="inlineStr">
         <is>
-          <t>Automatisierungslösungen für Halbleiter und Leistungselektronik: EFEM (Equipment Front End Modules), Load Ports, Substrat-Handlingkomponenten, Lader- und Tray-Systeme .</t>
+          <t>Automatisierungslösungen für Halbleiter und Leistungselektronik: EFEM (Equipment Front End Modules), Load Ports, Substrat-Handlingkomponenten, Lader- und Tray-Systeme.</t>
         </is>
       </c>
       <c r="G204" s="11" t="inlineStr">
@@ -43448,7 +43448,7 @@
       </c>
       <c r="F209" s="8" t="inlineStr">
         <is>
-          <t>AC- und DC-USV-Systeme, Schaltnetzteile, Transformatoren, Energiespeichersysteme, kundenspezifische Lösungen .</t>
+          <t>AC- und DC-USV-Systeme, Schaltnetzteile, Transformatoren, Energiespeichersysteme, kundenspezifische Lösungen.</t>
         </is>
       </c>
       <c r="G209" s="8" t="inlineStr">
@@ -43534,7 +43534,7 @@
       </c>
       <c r="F211" s="8" t="inlineStr">
         <is>
-          <t>Leiterplatten 4 bis 20 Lagen, HDI-Microvia, Flex und Starrflex, Wärmemanagement .</t>
+          <t>Leiterplatten 4 bis 20 Lagen, HDI-Microvia, Flex und Starrflex, Wärmemanagement.</t>
         </is>
       </c>
       <c r="G211" s="8" t="inlineStr">
@@ -43581,7 +43581,7 @@
       </c>
       <c r="F212" s="11" t="inlineStr">
         <is>
-          <t>Leiterplatten 4 bis 20 Lagen, HDI-Microvia, Flex und Starrflex, Wärmemanagement .</t>
+          <t>Leiterplatten 4 bis 20 Lagen, HDI-Microvia, Flex und Starrflex, Wärmemanagement.</t>
         </is>
       </c>
       <c r="G212" s="11" t="inlineStr">

--- a/aussendienst/electronica_2026_Aussendienst.xlsx
+++ b/aussendienst/electronica_2026_Aussendienst.xlsx
@@ -4452,7 +4452,7 @@
       </c>
       <c r="J74" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K74" s="11" t="inlineStr"/>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="J85" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K85" s="8" t="inlineStr"/>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="J135" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K135" s="8" t="inlineStr"/>
@@ -11683,12 +11683,12 @@
       </c>
       <c r="I208" s="11" t="inlineStr">
         <is>
-          <t>Jey: Ist die CRM-Zeile "alfatec GmbH &amp; Co. KG" (Zeile 72) bzw. "alfatec" (Zeile 71) dieselbe Gruppe/Anschrift wie ai-energy (Meckenloher Str. 11)? Und welche Rolle hat Hitachi/Eigene Harze (Bestandskontakt)? Wo: CRM-Datensatz …</t>
+          <t>Intern klären: Ist die CRM-Zeile "alfatec GmbH &amp; Co. KG" (Zeile 72) bzw. "alfatec" (Zeile 71) dieselbe Gruppe/Anschrift wie ai-energy (Meckenloher Str. 11)? Und welche Rolle hat Hitachi/Eigene Harze (Bestandskontakt)? Wo: CRM-Datensatz …</t>
         </is>
       </c>
       <c r="J208" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K208" s="11" t="inlineStr"/>
@@ -11899,12 +11899,12 @@
       </c>
       <c r="I212" s="11" t="inlineStr">
         <is>
-          <t>Jey: Ist AUMOVIO Germany GmbH Rechtsnachfolgerin/umfirmierte Einheit der CRM-Zeile "Continental Automotive Technologies GmbH" bzw. steht "Continental" (Zeile 442) für dieselbe Gruppe?</t>
+          <t>Intern klären: Ist AUMOVIO Germany GmbH Rechtsnachfolgerin/umfirmierte Einheit der CRM-Zeile "Continental Automotive Technologies GmbH" bzw. steht "Continental" (Zeile 442) für dieselbe Gruppe?</t>
         </is>
       </c>
       <c r="J212" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K212" s="11" t="inlineStr"/>
@@ -11953,7 +11953,7 @@
       </c>
       <c r="I213" s="8" t="inlineStr">
         <is>
-          <t>Jey: Gehört BDT Pfronten heute noch zur AdCapital AG, und ist der CRM-Bestandskontakt (Erich Jaeger, EW HOF, FRAKO oder TALLER) für Pfronten ohne Bedeutung (eigene Gesellschaft, anderer Ansprechpartner)?</t>
+          <t>Intern klären: Gehört BDT Pfronten heute noch zur AdCapital AG, und ist der CRM-Bestandskontakt (Erich Jaeger, EW HOF, FRAKO oder TALLER) für Pfronten ohne Bedeutung (eigene Gesellschaft, anderer Ansprechpartner)?</t>
         </is>
       </c>
       <c r="J213" s="8" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="I217" s="8" t="inlineStr">
         <is>
-          <t>Jey: Ist die CRM-Zeile "electronic concept GmbH" (bekannte_firmen, Z. 637) die Gaggenauer Gesellschaft, die jetzt zur elbe Gruppe gehört?</t>
+          <t>Intern klären: Ist die CRM-Zeile "electronic concept GmbH" (bekannte_firmen, Z. 637) die Gaggenauer Gesellschaft, die jetzt zur elbe Gruppe gehört?</t>
         </is>
       </c>
       <c r="J217" s="8" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="I219" s="8" t="inlineStr">
         <is>
-          <t>Jey: Ist CRM-Zeile 737 "ETS" (und 2036 "S.E. System Electronic") dieselbe Einheit wie ET System electronic GmbH, Altlußheim?</t>
+          <t>Intern klären: Ist CRM-Zeile 737 "ETS" (und 2036 "S.E. System Electronic") dieselbe Einheit wie ET System electronic GmbH, Altlußheim?</t>
         </is>
       </c>
       <c r="J219" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K219" s="8" t="inlineStr"/>
@@ -12385,7 +12385,7 @@
       </c>
       <c r="I221" s="8" t="inlineStr">
         <is>
-          <t>Jey: Ist die Bürkert GmbH &amp; Co. KG im CRM (Zeile 366) Bestandskontakt der Bürkert-Gruppe, und gilt die Fäth GmbH als Schwester/Beteiligung (Rot E5 nur bei derselben Einheit; sonst Neukontakt nach Jeys Entscheidung)?</t>
+          <t>Intern klären: Ist die Bürkert GmbH &amp; Co. KG im CRM (Zeile 366) Bestandskontakt der Bürkert-Gruppe, und gilt die Fäth GmbH als Schwester/Beteiligung (Rot E5 nur bei derselben Einheit; sonst Neukontakt nach interner Entscheidung)?</t>
         </is>
       </c>
       <c r="J221" s="8" t="inlineStr">
@@ -12547,12 +12547,12 @@
       </c>
       <c r="I224" s="11" t="inlineStr">
         <is>
-          <t>(a) Jey bestätigt, dass HEIDEN electronics GmbH (Amtsgericht Augsburg B15917) als Zielgesellschaft aufgenommen wird (HEIDEN power GmbH = Vertrieb). (b) Fertigung durch die electronics-GmbH in Pürgen mit eigener Quelle belegen …</t>
+          <t>(a) intern bestätigen, dass HEIDEN electronics GmbH (Amtsgericht Augsburg B15917) als Zielgesellschaft aufgenommen wird (HEIDEN power GmbH = Vertrieb). (b) Fertigung durch die electronics-GmbH in Pürgen mit eigener Quelle belegen …</t>
         </is>
       </c>
       <c r="J224" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K224" s="11" t="inlineStr"/>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="J225" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K225" s="8" t="inlineStr"/>
@@ -12763,12 +12763,12 @@
       </c>
       <c r="I228" s="11" t="inlineStr">
         <is>
-          <t>Jey: Steht im CRM die Bosch-Einheit "Bosch Security Systems/Building Technologies" (Grasbrunn/Straubing) oder nur andere Bosch-Gesellschaften (Robert Bosch GmbH, Rexroth, Power Tools)?</t>
+          <t>Intern klären: Steht im CRM die Bosch-Einheit "Bosch Security Systems/Building Technologies" (Grasbrunn/Straubing) oder nur andere Bosch-Gesellschaften (Robert Bosch GmbH, Rexroth, Power Tools)?</t>
         </is>
       </c>
       <c r="J228" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K228" s="11" t="inlineStr"/>
@@ -13038,7 +13038,7 @@
       </c>
       <c r="J233" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K233" s="8" t="inlineStr"/>
@@ -13087,12 +13087,12 @@
       </c>
       <c r="I234" s="11" t="inlineStr">
         <is>
-          <t>Jey: Ist MAIR Elektronik GmbH im CRM als Teil von RAWE Electronic GmbH (Zeile 1948) oder Demmel AG (Zeile 501) bereits betreut?</t>
+          <t>Intern klären: Ist MAIR Elektronik GmbH im CRM als Teil von RAWE Electronic GmbH (Zeile 1948) oder Demmel AG (Zeile 501) bereits betreut?</t>
         </is>
       </c>
       <c r="J234" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K234" s="11" t="inlineStr"/>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="I237" s="8" t="inlineStr">
         <is>
-          <t>An Jey: Ist die CRM-Zeile "J. Schneider Elektrotechnik" (Z. 1208, Offenburg?) die Offenburger Schwester der Huber SE? Wenn ja: Konzernbezug zu einem Bestandskunden, Vorgehen mit Jey/Vertrieb abstimmen (kein Neukunde im Sinne E5 …</t>
+          <t>Intern klären: Ist die CRM-Zeile "J. Schneider Elektrotechnik" (Z. 1208, Offenburg?) die Offenburger Schwester der Huber SE? Wenn ja: Konzernbezug zu einem Bestandskunden, Vorgehen mit dem Vertrieb abstimmen (kein Neukunde im Sinne E5 …</t>
         </is>
       </c>
       <c r="J237" s="8" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="I245" s="8" t="inlineStr">
         <is>
-          <t>Jey: Ist die CRM-Einheit "VON ARDENNE GmbH" (Dresden) Gesellschafterin/Muttergesellschaft der scia Systems GmbH, und gilt der Bestandskontakt auch für scia?</t>
+          <t>Intern klären: Ist die CRM-Einheit "VON ARDENNE GmbH" (Dresden) Gesellschafterin/Muttergesellschaft der scia Systems GmbH, und gilt der Bestandskontakt auch für scia?</t>
         </is>
       </c>
       <c r="J245" s="8" t="inlineStr">
@@ -13789,12 +13789,12 @@
       </c>
       <c r="I247" s="8" t="inlineStr">
         <is>
-          <t>Jey: Welche Gesellschaft steht hinter CRM-Zeilen "Sumitomo"/"SUMITOMO" (2273/2274)? Gehört sie zur Sumitomo-Electric-Gruppe?</t>
+          <t>Intern klären: Welche Gesellschaft steht hinter CRM-Zeilen "Sumitomo"/"SUMITOMO" (2273/2274)? Gehört sie zur Sumitomo-Electric-Gruppe?</t>
         </is>
       </c>
       <c r="J247" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K247" s="8" t="inlineStr"/>
@@ -17297,7 +17297,7 @@
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>Jey: Ist die CRM-Zeile "electronic concept GmbH" (bekannte_firmen, Z. 637) die Gaggenauer Gesellschaft, die jetzt zur elbe Gruppe gehört?</t>
+          <t>Intern klären: Ist die CRM-Zeile "electronic concept GmbH" (bekannte_firmen, Z. 637) die Gaggenauer Gesellschaft, die jetzt zur elbe Gruppe gehört?</t>
         </is>
       </c>
       <c r="J59" s="8" t="inlineStr">
@@ -17405,12 +17405,12 @@
       </c>
       <c r="I61" s="8" t="inlineStr">
         <is>
-          <t>Jey: Ist CRM-Zeile 737 "ETS" (und 2036 "S.E. System Electronic") dieselbe Einheit wie ET System electronic GmbH, Altlußheim?</t>
+          <t>Intern klären: Ist CRM-Zeile 737 "ETS" (und 2036 "S.E. System Electronic") dieselbe Einheit wie ET System electronic GmbH, Altlußheim?</t>
         </is>
       </c>
       <c r="J61" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K61" s="8" t="inlineStr"/>
@@ -17518,7 +17518,7 @@
       </c>
       <c r="J63" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K63" s="8" t="inlineStr"/>
@@ -17675,7 +17675,7 @@
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>An Jey: Ist die CRM-Zeile "J. Schneider Elektrotechnik" (Z. 1208, Offenburg?) die Offenburger Schwester der Huber SE? Wenn ja: Konzernbezug zu einem Bestandskunden, Vorgehen mit Jey/Vertrieb abstimmen (kein Neukunde im Sinne E5 …</t>
+          <t>Intern klären: Ist die CRM-Zeile "J. Schneider Elektrotechnik" (Z. 1208, Offenburg?) die Offenburger Schwester der Huber SE? Wenn ja: Konzernbezug zu einem Bestandskunden, Vorgehen mit dem Vertrieb abstimmen (kein Neukunde im Sinne E5 …</t>
         </is>
       </c>
       <c r="J66" s="11" t="inlineStr">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr"/>
@@ -19784,7 +19784,7 @@
       </c>
       <c r="J38" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K38" s="11" t="inlineStr"/>
@@ -20643,12 +20643,12 @@
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>Jey: Ist die CRM-Zeile "alfatec GmbH &amp; Co. KG" (Zeile 72) bzw. "alfatec" (Zeile 71) dieselbe Gruppe/Anschrift wie ai-energy (Meckenloher Str. 11)? Und welche Rolle hat Hitachi/Eigene Harze (Bestandskontakt)? Wo: CRM-Datensatz …</t>
+          <t>Intern klären: Ist die CRM-Zeile "alfatec GmbH &amp; Co. KG" (Zeile 72) bzw. "alfatec" (Zeile 71) dieselbe Gruppe/Anschrift wie ai-energy (Meckenloher Str. 11)? Und welche Rolle hat Hitachi/Eigene Harze (Bestandskontakt)? Wo: CRM-Datensatz …</t>
         </is>
       </c>
       <c r="J54" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K54" s="11" t="inlineStr"/>
@@ -20805,12 +20805,12 @@
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>Jey: Ist AUMOVIO Germany GmbH Rechtsnachfolgerin/umfirmierte Einheit der CRM-Zeile "Continental Automotive Technologies GmbH" bzw. steht "Continental" (Zeile 442) für dieselbe Gruppe?</t>
+          <t>Intern klären: Ist AUMOVIO Germany GmbH Rechtsnachfolgerin/umfirmierte Einheit der CRM-Zeile "Continental Automotive Technologies GmbH" bzw. steht "Continental" (Zeile 442) für dieselbe Gruppe?</t>
         </is>
       </c>
       <c r="J57" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K57" s="8" t="inlineStr"/>
@@ -20859,7 +20859,7 @@
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>Jey: Gehört BDT Pfronten heute noch zur AdCapital AG, und ist der CRM-Bestandskontakt (Erich Jaeger, EW HOF, FRAKO oder TALLER) für Pfronten ohne Bedeutung (eigene Gesellschaft, anderer Ansprechpartner)?</t>
+          <t>Intern klären: Gehört BDT Pfronten heute noch zur AdCapital AG, und ist der CRM-Bestandskontakt (Erich Jaeger, EW HOF, FRAKO oder TALLER) für Pfronten ohne Bedeutung (eigene Gesellschaft, anderer Ansprechpartner)?</t>
         </is>
       </c>
       <c r="J58" s="11" t="inlineStr">
@@ -20967,12 +20967,12 @@
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
-          <t>(a) Jey bestätigt, dass HEIDEN electronics GmbH (Amtsgericht Augsburg B15917) als Zielgesellschaft aufgenommen wird (HEIDEN power GmbH = Vertrieb). (b) Fertigung durch die electronics-GmbH in Pürgen mit eigener Quelle belegen …</t>
+          <t>(a) intern bestätigen, dass HEIDEN electronics GmbH (Amtsgericht Augsburg B15917) als Zielgesellschaft aufgenommen wird (HEIDEN power GmbH = Vertrieb). (b) Fertigung durch die electronics-GmbH in Pürgen mit eigener Quelle belegen …</t>
         </is>
       </c>
       <c r="J60" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K60" s="11" t="inlineStr"/>
@@ -21075,12 +21075,12 @@
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>Jey: Steht im CRM die Bosch-Einheit "Bosch Security Systems/Building Technologies" (Grasbrunn/Straubing) oder nur andere Bosch-Gesellschaften (Robert Bosch GmbH, Rexroth, Power Tools)?</t>
+          <t>Intern klären: Steht im CRM die Bosch-Einheit "Bosch Security Systems/Building Technologies" (Grasbrunn/Straubing) oder nur andere Bosch-Gesellschaften (Robert Bosch GmbH, Rexroth, Power Tools)?</t>
         </is>
       </c>
       <c r="J62" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K62" s="11" t="inlineStr"/>
@@ -21237,12 +21237,12 @@
       </c>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>Jey: Ist MAIR Elektronik GmbH im CRM als Teil von RAWE Electronic GmbH (Zeile 1948) oder Demmel AG (Zeile 501) bereits betreut?</t>
+          <t>Intern klären: Ist MAIR Elektronik GmbH im CRM als Teil von RAWE Electronic GmbH (Zeile 1948) oder Demmel AG (Zeile 501) bereits betreut?</t>
         </is>
       </c>
       <c r="J65" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K65" s="8" t="inlineStr"/>
@@ -23832,7 +23832,7 @@
       </c>
       <c r="J44" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K44" s="11" t="inlineStr"/>
@@ -27337,7 +27337,7 @@
       </c>
       <c r="I109" s="8" t="inlineStr">
         <is>
-          <t>Jey: Ist die Bürkert GmbH &amp; Co. KG im CRM (Zeile 366) Bestandskontakt der Bürkert-Gruppe, und gilt die Fäth GmbH als Schwester/Beteiligung (Rot E5 nur bei derselben Einheit; sonst Neukontakt nach Jeys Entscheidung)?</t>
+          <t>Intern klären: Ist die Bürkert GmbH &amp; Co. KG im CRM (Zeile 366) Bestandskontakt der Bürkert-Gruppe, und gilt die Fäth GmbH als Schwester/Beteiligung (Rot E5 nur bei derselben Einheit; sonst Neukontakt nach interner Entscheidung)?</t>
         </is>
       </c>
       <c r="J109" s="8" t="inlineStr">
@@ -27504,7 +27504,7 @@
       </c>
       <c r="J112" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K112" s="11" t="inlineStr"/>
@@ -27823,7 +27823,7 @@
       </c>
       <c r="I118" s="11" t="inlineStr">
         <is>
-          <t>Jey: Ist die CRM-Einheit "VON ARDENNE GmbH" (Dresden) Gesellschafterin/Muttergesellschaft der scia Systems GmbH, und gilt der Bestandskontakt auch für scia?</t>
+          <t>Intern klären: Ist die CRM-Einheit "VON ARDENNE GmbH" (Dresden) Gesellschafterin/Muttergesellschaft der scia Systems GmbH, und gilt der Bestandskontakt auch für scia?</t>
         </is>
       </c>
       <c r="J118" s="11" t="inlineStr">
@@ -27877,12 +27877,12 @@
       </c>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>Jey: Welche Gesellschaft steht hinter CRM-Zeilen "Sumitomo"/"SUMITOMO" (2273/2274)? Gehört sie zur Sumitomo-Electric-Gruppe?</t>
+          <t>Intern klären: Welche Gesellschaft steht hinter CRM-Zeilen "Sumitomo"/"SUMITOMO" (2273/2274)? Gehört sie zur Sumitomo-Electric-Gruppe?</t>
         </is>
       </c>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
       <c r="K119" s="8" t="inlineStr"/>
@@ -31992,7 +31992,7 @@
       </c>
       <c r="J75" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -35107,12 +35107,12 @@
       </c>
       <c r="I135" s="8" t="inlineStr">
         <is>
-          <t>Jey: Gilt die Bosch-Gruppe im CRM als Konzernbezug für die ITK Engineering GmbH (Tochter, eigener Sitz)? (2) Hat ITK in Rülzheim eine Hardware-/Gerätefertigung (Prototypen, Kleinserie, Medizingeräte) oder reine Entwicklung (E2 …</t>
+          <t>Intern klären: Gilt die Bosch-Gruppe im CRM als Konzernbezug für die ITK Engineering GmbH (Tochter, eigener Sitz)? (2) Hat ITK in Rülzheim eine Hardware-/Gerätefertigung (Prototypen, Kleinserie, Medizingeräte) oder reine Entwicklung (E2 …</t>
         </is>
       </c>
       <c r="J135" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -37447,7 +37447,7 @@
       </c>
       <c r="I180" s="11" t="inlineStr">
         <is>
-          <t>Jey: Greift E1 für die Nordson-Einheit Test &amp; Inspection (gleicher Konzern wie Dosier-Wettbewerber) oder wird sie als Kunde bewertet? (2) Falls Kunde: Wird in Feldkirchen gefertigt/montiert? Wo: Impressum nordson.com/de …</t>
+          <t>Intern klären: Greift E1 für die Nordson-Einheit Test &amp; Inspection (gleicher Konzern wie Dosier-Wettbewerber) oder wird sie als Kunde bewertet? (2) Falls Kunde: Wird in Feldkirchen gefertigt/montiert? Wo: Impressum nordson.com/de …</t>
         </is>
       </c>
       <c r="J180" s="11" t="inlineStr">
@@ -38024,7 +38024,7 @@
       </c>
       <c r="J191" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -38700,7 +38700,7 @@
       </c>
       <c r="J204" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -40255,12 +40255,12 @@
       </c>
       <c r="I234" s="11" t="inlineStr">
         <is>
-          <t>Jey: Ist CRM-Zeile 2030 "rtg electronics GmbH" dieselbe Gesellschaft wie die Tochter von SE Spezial-Electronic (Bückeburg)?</t>
+          <t>Intern klären: Ist CRM-Zeile 2030 "rtg electronics GmbH" dieselbe Gesellschaft wie die Tochter von SE Spezial-Electronic (Bückeburg)?</t>
         </is>
       </c>
       <c r="J234" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -40619,12 +40619,12 @@
       </c>
       <c r="I241" s="8" t="inlineStr">
         <is>
-          <t>Jey/Tina: Ist die CRM-Einheit "Robert Bosch GmbH" überhaupt die Einheit, aus der Immenstadt hervorging, und zählt der Altkonzern nach dem Verkauf an Sintokogio noch? Wo: Impressum und Handelsregister Sinto Advanced Ceramics …</t>
+          <t>Intern klären: Ist die CRM-Einheit "Robert Bosch GmbH" überhaupt die Einheit, aus der Immenstadt hervorging, und zählt der Altkonzern nach dem Verkauf an Sintokogio noch? Wo: Impressum und Handelsregister Sinto Advanced Ceramics …</t>
         </is>
       </c>
       <c r="J241" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -41035,12 +41035,12 @@
       </c>
       <c r="I249" s="8" t="inlineStr">
         <is>
-          <t>Jey/CRM: Ort der CRM-Einträge Phytron GmbH (Zeile 1821), FRANK Elektronik GmbH (826), EPS (715) gegen Gröbenzell, Traunstein bzw. EPS-Standort in Stemas-Gruppe abgleichen (Kundendatenbank/Registerauszug). (b) Beteiligungen ohne …</t>
+          <t>Intern klären: Ort der CRM-Einträge Phytron GmbH (Zeile 1821), FRANK Elektronik GmbH (826), EPS (715) gegen Gröbenzell, Traunstein bzw. EPS-Standort in Stemas-Gruppe abgleichen (Kundendatenbank/Registerauszug). (b) Beteiligungen ohne …</t>
         </is>
       </c>
       <c r="J249" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -42075,12 +42075,12 @@
       </c>
       <c r="I269" s="8" t="inlineStr">
         <is>
-          <t>Ist OPTEK [DE] im CRM die TT-Tochter Optek Technology oder eine andere Einheit? Wo: CRM-Datensatz (Jey/Excel), Ort der CRM-Einheit. (2) Gehört AB Elektronik GmbH Werne zu den Firmen, die auf der Messe unter "TT Electronics" …</t>
+          <t>Ist OPTEK [DE] im CRM die TT-Tochter Optek Technology oder eine andere Einheit? Wo: CRM-Datensatz (Excel), Ort der CRM-Einheit. (2) Gehört AB Elektronik GmbH Werne zu den Firmen, die auf der Messe unter "TT Electronics" …</t>
         </is>
       </c>
       <c r="J269" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -43677,12 +43677,12 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -43721,7 +43721,7 @@
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J6" s="11" t="inlineStr">
@@ -43765,7 +43765,7 @@
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -43809,7 +43809,7 @@
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J8" s="11" t="inlineStr">
@@ -43853,7 +43853,7 @@
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -43897,7 +43897,7 @@
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J10" s="11" t="inlineStr">
@@ -43941,7 +43941,7 @@
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
@@ -43985,7 +43985,7 @@
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J12" s="11" t="inlineStr">
@@ -44037,12 +44037,12 @@
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -44081,7 +44081,7 @@
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr">
@@ -44177,7 +44177,7 @@
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J16" s="11" t="inlineStr">
@@ -44221,7 +44221,7 @@
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -44265,7 +44265,7 @@
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J18" s="11" t="inlineStr">
@@ -44309,7 +44309,7 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -44353,7 +44353,7 @@
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J20" s="11" t="inlineStr">
@@ -44405,7 +44405,7 @@
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -44457,12 +44457,12 @@
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -44509,12 +44509,12 @@
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -44561,12 +44561,12 @@
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -44613,7 +44613,7 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
@@ -44665,7 +44665,7 @@
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J26" s="11" t="inlineStr">
@@ -44717,7 +44717,7 @@
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J27" s="8" t="inlineStr">
@@ -44761,7 +44761,7 @@
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J28" s="11" t="inlineStr">
@@ -44805,7 +44805,7 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr">
@@ -44857,7 +44857,7 @@
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J30" s="11" t="inlineStr">
@@ -44901,7 +44901,7 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -44953,12 +44953,12 @@
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -45005,7 +45005,7 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
@@ -45049,7 +45049,7 @@
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr">
@@ -45093,7 +45093,7 @@
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J35" s="8" t="inlineStr">
@@ -45137,7 +45137,7 @@
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J36" s="11" t="inlineStr">
@@ -45233,7 +45233,7 @@
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J38" s="11" t="inlineStr">
@@ -45285,7 +45285,7 @@
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J39" s="8" t="inlineStr">
@@ -45329,7 +45329,7 @@
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J40" s="11" t="inlineStr">
@@ -45381,12 +45381,12 @@
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -45433,7 +45433,7 @@
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J42" s="11" t="inlineStr">
@@ -45485,7 +45485,7 @@
       </c>
       <c r="I43" s="8" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J43" s="8" t="inlineStr">
@@ -45537,7 +45537,7 @@
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J44" s="11" t="inlineStr">
@@ -45589,7 +45589,7 @@
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J45" s="8" t="inlineStr">
@@ -45641,7 +45641,7 @@
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J46" s="11" t="inlineStr">
@@ -45693,7 +45693,7 @@
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
@@ -45745,7 +45745,7 @@
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J48" s="11" t="inlineStr">
@@ -45797,7 +45797,7 @@
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J49" s="8" t="inlineStr">
@@ -45841,7 +45841,7 @@
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J50" s="11" t="inlineStr">
@@ -45885,7 +45885,7 @@
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J51" s="8" t="inlineStr">
@@ -45937,7 +45937,7 @@
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J52" s="11" t="inlineStr">
@@ -45981,7 +45981,7 @@
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J53" s="8" t="inlineStr">
@@ -46025,7 +46025,7 @@
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J54" s="11" t="inlineStr">
@@ -46069,7 +46069,7 @@
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J55" s="8" t="inlineStr">
@@ -46121,12 +46121,12 @@
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J56" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -46165,7 +46165,7 @@
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J57" s="8" t="inlineStr">
@@ -46209,7 +46209,7 @@
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J58" s="11" t="inlineStr">
@@ -46253,7 +46253,7 @@
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J59" s="8" t="inlineStr">
@@ -46305,12 +46305,12 @@
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J60" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -46349,7 +46349,7 @@
       </c>
       <c r="I61" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J61" s="8" t="inlineStr">
@@ -46401,7 +46401,7 @@
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J62" s="11" t="inlineStr">
@@ -46453,12 +46453,12 @@
       </c>
       <c r="I63" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J63" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -46497,7 +46497,7 @@
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J64" s="11" t="inlineStr">
@@ -46541,7 +46541,7 @@
       </c>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J65" s="8" t="inlineStr">
@@ -46585,7 +46585,7 @@
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J66" s="11" t="inlineStr">
@@ -46629,7 +46629,7 @@
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J67" s="8" t="inlineStr">
@@ -46673,7 +46673,7 @@
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J68" s="11" t="inlineStr">
@@ -46717,7 +46717,7 @@
       </c>
       <c r="I69" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J69" s="8" t="inlineStr">
@@ -46761,7 +46761,7 @@
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J70" s="11" t="inlineStr">
@@ -46813,7 +46813,7 @@
       </c>
       <c r="I71" s="8" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J71" s="8" t="inlineStr">
@@ -46865,12 +46865,12 @@
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J72" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -46909,7 +46909,7 @@
       </c>
       <c r="I73" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J73" s="8" t="inlineStr">
@@ -46961,12 +46961,12 @@
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J74" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -47013,12 +47013,12 @@
       </c>
       <c r="I75" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J75" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -47053,7 +47053,7 @@
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr">
@@ -47097,7 +47097,7 @@
       </c>
       <c r="I77" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J77" s="8" t="inlineStr">
@@ -47141,7 +47141,7 @@
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J78" s="11" t="inlineStr">
@@ -47185,7 +47185,7 @@
       </c>
       <c r="I79" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J79" s="8" t="inlineStr">
@@ -47229,7 +47229,7 @@
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J80" s="11" t="inlineStr">
@@ -47281,12 +47281,12 @@
       </c>
       <c r="I81" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J81" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -47333,12 +47333,12 @@
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -47385,12 +47385,12 @@
       </c>
       <c r="I83" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J83" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -47429,7 +47429,7 @@
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr">
@@ -47481,12 +47481,12 @@
       </c>
       <c r="I85" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J85" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -47533,7 +47533,7 @@
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J86" s="11" t="inlineStr">
@@ -47585,12 +47585,12 @@
       </c>
       <c r="I87" s="8" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J87" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -47629,7 +47629,7 @@
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J88" s="11" t="inlineStr">
@@ -47673,7 +47673,7 @@
       </c>
       <c r="I89" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J89" s="8" t="inlineStr">
@@ -47717,7 +47717,7 @@
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr">
@@ -47769,12 +47769,12 @@
       </c>
       <c r="I91" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J91" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -47813,7 +47813,7 @@
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J92" s="11" t="inlineStr">
@@ -47865,7 +47865,7 @@
       </c>
       <c r="I93" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J93" s="8" t="inlineStr">
@@ -47909,7 +47909,7 @@
       </c>
       <c r="I94" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J94" s="11" t="inlineStr">
@@ -47953,7 +47953,7 @@
       </c>
       <c r="I95" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J95" s="8" t="inlineStr">
@@ -47997,7 +47997,7 @@
       </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J96" s="11" t="inlineStr">
@@ -48041,7 +48041,7 @@
       </c>
       <c r="I97" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J97" s="8" t="inlineStr">
@@ -48089,12 +48089,12 @@
       </c>
       <c r="I98" s="11" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J98" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -48141,12 +48141,12 @@
       </c>
       <c r="I99" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J99" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -48185,7 +48185,7 @@
       </c>
       <c r="I100" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J100" s="11" t="inlineStr">
@@ -48229,7 +48229,7 @@
       </c>
       <c r="I101" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J101" s="8" t="inlineStr">
@@ -48273,7 +48273,7 @@
       </c>
       <c r="I102" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J102" s="11" t="inlineStr">
@@ -48325,12 +48325,12 @@
       </c>
       <c r="I103" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J103" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -48369,7 +48369,7 @@
       </c>
       <c r="I104" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J104" s="11" t="inlineStr">
@@ -48421,7 +48421,7 @@
       </c>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J105" s="8" t="inlineStr">
@@ -48473,12 +48473,12 @@
       </c>
       <c r="I106" s="11" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J106" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -48517,7 +48517,7 @@
       </c>
       <c r="I107" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J107" s="8" t="inlineStr">
@@ -48561,7 +48561,7 @@
       </c>
       <c r="I108" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J108" s="11" t="inlineStr">
@@ -48605,7 +48605,7 @@
       </c>
       <c r="I109" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J109" s="8" t="inlineStr">
@@ -48649,7 +48649,7 @@
       </c>
       <c r="I110" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J110" s="11" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J111" s="8" t="inlineStr">
@@ -48737,7 +48737,7 @@
       </c>
       <c r="I112" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J112" s="11" t="inlineStr">
@@ -48781,7 +48781,7 @@
       </c>
       <c r="I113" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J113" s="8" t="inlineStr">
@@ -48825,7 +48825,7 @@
       </c>
       <c r="I114" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J114" s="11" t="inlineStr">
@@ -48869,7 +48869,7 @@
       </c>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J115" s="8" t="inlineStr">
@@ -48913,7 +48913,7 @@
       </c>
       <c r="I116" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J116" s="11" t="inlineStr">
@@ -48965,12 +48965,12 @@
       </c>
       <c r="I117" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J117" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -49009,7 +49009,7 @@
       </c>
       <c r="I118" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J118" s="11" t="inlineStr">
@@ -49053,7 +49053,7 @@
       </c>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J119" s="8" t="inlineStr">
@@ -49105,12 +49105,12 @@
       </c>
       <c r="I120" s="11" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J120" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -49157,7 +49157,7 @@
       </c>
       <c r="I121" s="8" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J121" s="8" t="inlineStr">
@@ -49209,7 +49209,7 @@
       </c>
       <c r="I122" s="11" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J122" s="11" t="inlineStr">
@@ -49261,7 +49261,7 @@
       </c>
       <c r="I123" s="8" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J123" s="8" t="inlineStr">
@@ -49305,7 +49305,7 @@
       </c>
       <c r="I124" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J124" s="11" t="inlineStr">
@@ -49349,7 +49349,7 @@
       </c>
       <c r="I125" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J125" s="8" t="inlineStr">
@@ -49401,12 +49401,12 @@
       </c>
       <c r="I126" s="11" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J126" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -49445,7 +49445,7 @@
       </c>
       <c r="I127" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J127" s="8" t="inlineStr">
@@ -49497,12 +49497,12 @@
       </c>
       <c r="I128" s="11" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J128" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -49549,12 +49549,12 @@
       </c>
       <c r="I129" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J129" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -49601,12 +49601,12 @@
       </c>
       <c r="I130" s="11" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J130" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -49653,12 +49653,12 @@
       </c>
       <c r="I131" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J131" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -49697,7 +49697,7 @@
       </c>
       <c r="I132" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J132" s="11" t="inlineStr">
@@ -49741,7 +49741,7 @@
       </c>
       <c r="I133" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J133" s="8" t="inlineStr">
@@ -49793,7 +49793,7 @@
       </c>
       <c r="I134" s="11" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J134" s="11" t="inlineStr">
@@ -49837,7 +49837,7 @@
       </c>
       <c r="I135" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J135" s="8" t="inlineStr">
@@ -49889,7 +49889,7 @@
       </c>
       <c r="I136" s="11" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J136" s="11" t="inlineStr">
@@ -49933,7 +49933,7 @@
       </c>
       <c r="I137" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J137" s="8" t="inlineStr">
@@ -49977,7 +49977,7 @@
       </c>
       <c r="I138" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J138" s="11" t="inlineStr">
@@ -50029,7 +50029,7 @@
       </c>
       <c r="I139" s="8" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J139" s="8" t="inlineStr">
@@ -50081,7 +50081,7 @@
       </c>
       <c r="I140" s="11" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J140" s="11" t="inlineStr">
@@ -50125,7 +50125,7 @@
       </c>
       <c r="I141" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J141" s="8" t="inlineStr">
@@ -50169,7 +50169,7 @@
       </c>
       <c r="I142" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J142" s="11" t="inlineStr">
@@ -50221,12 +50221,12 @@
       </c>
       <c r="I143" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J143" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -50265,7 +50265,7 @@
       </c>
       <c r="I144" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J144" s="11" t="inlineStr">
@@ -50317,7 +50317,7 @@
       </c>
       <c r="I145" s="8" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J145" s="8" t="inlineStr">
@@ -50369,7 +50369,7 @@
       </c>
       <c r="I146" s="11" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J146" s="11" t="inlineStr">
@@ -50413,7 +50413,7 @@
       </c>
       <c r="I147" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J147" s="8" t="inlineStr">
@@ -50465,7 +50465,7 @@
       </c>
       <c r="I148" s="11" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J148" s="11" t="inlineStr">
@@ -50517,12 +50517,12 @@
       </c>
       <c r="I149" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J149" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -50561,7 +50561,7 @@
       </c>
       <c r="I150" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J150" s="11" t="inlineStr">
@@ -50605,7 +50605,7 @@
       </c>
       <c r="I151" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J151" s="8" t="inlineStr">
@@ -50649,7 +50649,7 @@
       </c>
       <c r="I152" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J152" s="11" t="inlineStr">
@@ -50693,7 +50693,7 @@
       </c>
       <c r="I153" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J153" s="8" t="inlineStr">
@@ -50745,7 +50745,7 @@
       </c>
       <c r="I154" s="11" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J154" s="11" t="inlineStr">
@@ -50789,7 +50789,7 @@
       </c>
       <c r="I155" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J155" s="8" t="inlineStr">
@@ -50841,7 +50841,7 @@
       </c>
       <c r="I156" s="11" t="inlineStr">
         <is>
-          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+          <t>Verband / Prüfdienstleister / Forschung</t>
         </is>
       </c>
       <c r="J156" s="11" t="inlineStr">
@@ -50893,12 +50893,12 @@
       </c>
       <c r="I157" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J157" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -50937,7 +50937,7 @@
       </c>
       <c r="I158" s="11" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J158" s="11" t="inlineStr">
@@ -50989,12 +50989,12 @@
       </c>
       <c r="I159" s="8" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J159" s="8" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -51041,12 +51041,12 @@
       </c>
       <c r="I160" s="11" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J160" s="11" t="inlineStr">
         <is>
-          <t>Konzern/ähnlicher Name im CRM – Jey klären</t>
+          <t>Konzern-/ähnlicher Name im CRM – vor Kontakt intern klären</t>
         </is>
       </c>
     </row>
@@ -51085,7 +51085,7 @@
       </c>
       <c r="I161" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J161" s="8" t="inlineStr">
@@ -51137,7 +51137,7 @@
       </c>
       <c r="I162" s="11" t="inlineStr">
         <is>
-          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name)</t>
         </is>
       </c>
       <c r="J162" s="11" t="inlineStr">
@@ -51181,7 +51181,7 @@
       </c>
       <c r="I163" s="8" t="inlineStr">
         <is>
-          <t>Bestandskunde laut CRM-Abgleich (Namensabgleich, nicht durch Tom/Tina geprüft) – Zuständigen im Haus fragen</t>
+          <t>Bestandskunde laut CRM-Namensabgleich – nicht ansprechen, Zuständigen im Haus fragen</t>
         </is>
       </c>
       <c r="J163" s="8" t="inlineStr">
@@ -51257,7 +51257,7 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>Zuerst Identität oder CRM-Bezug klären (z. B. Konzern im CRM, Sitz unklar). Nicht ohne Rückmeldung von Jey kontaktieren.</t>
+          <t>Zuerst Identität oder CRM-Bezug klären (z. B. Konzern im CRM, Sitz unklar). Nicht ohne interne Rückmeldung kontaktieren.</t>
         </is>
       </c>
     </row>
@@ -51293,7 +51293,7 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Alles, was laut Jey rausfällt: (1) Firmen im CRM mit gleichem oder sehr ähnlichem Namen (88 Namensabgleich-Treffer plus Tom/Tina-Treffer inkl. Konzernname), (2) Verbände, Prüfdienstleister, Forschungsorganisationen, (3) Anlagenbauer ohne Verguss-/Demak-Anlage. Grund steht in Spalte "Vor dem Kontakt klären".</t>
+          <t>Alles, was nicht angesprochen wird: (1) Firmen im CRM mit gleichem oder sehr ähnlichem Namen (88 Namensabgleich-Treffer plus Treffer aus der Recherche inkl. Konzernname), (2) Verbände, Prüfdienstleister, Forschungsorganisationen, (3) Anlagenbauer ohne Verguss-/Demak-Anlage. Grund steht in Spalte "Vor dem Kontakt klären".</t>
         </is>
       </c>
     </row>
@@ -51341,7 +51341,7 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>Nicht geprüft. Eigenfertigung und Wettbewerbereinsatz im Gespräch erfragen.</t>
+          <t>Patente nur bei den 46 Browser-geprüften Firmen (Google Patents, Espacenet) gesucht. Eigenfertigung und Wettbewerbereinsatz im Gespräch erfragen.</t>
         </is>
       </c>
     </row>
@@ -51353,7 +51353,7 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>Pro Vertriebsgebiet ein Blatt (Baden-Württemberg, Bayern, Rest DE / NL, ggf. Österreich/außerhalb; nur Prio A/B/C). Gebiet nach Fertigungs- bzw. Firmensitz laut Tom/Tina. Zuständig: Stefan = Baden-Württemberg, Dietmar = Bayern, Manuel = Rest DE / NL. Das Blatt "Zielfirmen" enthält alle zusammen.</t>
+          <t>Pro Vertriebsgebiet ein Blatt (Baden-Württemberg, Bayern, Rest DE / NL, ggf. Österreich/außerhalb; nur Prio A/B/C). Gebiet nach Fertigungs- bzw. Firmensitz laut Recherche. Zuständig: Stefan = Baden-Württemberg, Dietmar = Bayern, Manuel = Rest DE / NL. Das Blatt "Zielfirmen" enthält alle zusammen.</t>
         </is>
       </c>
     </row>
